--- a/core/sample-data/Financial Template.xlsx
+++ b/core/sample-data/Financial Template.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="289">
   <si>
     <t>I captured data at month end balances</t>
   </si>
@@ -866,94 +866,40 @@
     <t>ZSCALER INC COM</t>
   </si>
   <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>property</t>
+    <t>Property</t>
   </si>
   <si>
     <t>330 Painted Woods</t>
   </si>
   <si>
-    <t>Display label for the loan</t>
-  </si>
-  <si>
-    <t>original_principal</t>
-  </si>
-  <si>
-    <t>Original loan amount in dollars</t>
-  </si>
-  <si>
-    <t>interest_rate</t>
-  </si>
-  <si>
-    <t>Annual interest rate (decimal)</t>
-  </si>
-  <si>
-    <t>term_months</t>
-  </si>
-  <si>
-    <t>Loan term in months (30 years = 360)</t>
-  </si>
-  <si>
-    <t>monthly_payment</t>
-  </si>
-  <si>
-    <t>Scheduled principal+interest payment (P&amp;I)</t>
-  </si>
-  <si>
-    <t>origination_date</t>
-  </si>
-  <si>
-    <t>2023-08-01</t>
-  </si>
-  <si>
-    <t>First scheduled payment date (YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>current_balance</t>
-  </si>
-  <si>
-    <t>Current online principal balance</t>
-  </si>
-  <si>
-    <t>principal_paid</t>
-  </si>
-  <si>
-    <t>Lifetime principal paid (incl. extras)</t>
-  </si>
-  <si>
-    <t>interest_paid</t>
-  </si>
-  <si>
-    <t>Lifetime interest paid (estimate)</t>
-  </si>
-  <si>
-    <t>as_of_date</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>Date the balance and totals are current as of</t>
+    <t>Principal</t>
+  </si>
+  <si>
+    <t>Origination Date</t>
+  </si>
+  <si>
+    <t>Term in years</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Payment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00_);[Red](&quot;$&quot;#,##0.00)"/>
     <numFmt numFmtId="166" formatCode="m/d/yy;@"/>
+    <numFmt numFmtId="167" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="m/d/yy"/>
+    <numFmt numFmtId="169" formatCode="($#,##0.00);($#,##0.00)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1019,9 +965,6 @@
       <family val="2"/>
       <sz val="10"/>
       <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -1113,7 +1056,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1171,7 +1114,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1518,133 +1463,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="B2:C7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
         <v>282</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="C2" t="s">
         <v>283</v>
       </c>
-      <c r="C1" s="33" t="s">
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C3" s="33">
+        <v>725000</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
         <v>285</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C4" s="34">
+        <v>45139</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>286</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C6" s="10">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>288</v>
       </c>
-      <c r="B3">
-        <v>725000</v>
-      </c>
-      <c r="C3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>290</v>
-      </c>
-      <c r="B4">
-        <v>0.06</v>
-      </c>
-      <c r="C4" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>292</v>
-      </c>
-      <c r="B5">
-        <v>360</v>
-      </c>
-      <c r="C5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>294</v>
-      </c>
-      <c r="B6">
-        <v>4346.74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>296</v>
-      </c>
-      <c r="B7" t="s">
-        <v>297</v>
-      </c>
-      <c r="C7" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>299</v>
-      </c>
-      <c r="B8">
-        <v>505359.96</v>
-      </c>
-      <c r="C8" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>301</v>
-      </c>
-      <c r="B9">
-        <v>223263.89</v>
-      </c>
-      <c r="C9" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>303</v>
-      </c>
-      <c r="B10">
-        <v>106829.78</v>
-      </c>
-      <c r="C10" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>305</v>
-      </c>
-      <c r="B11" t="s">
-        <v>306</v>
-      </c>
-      <c r="C11" t="s">
-        <v>307</v>
+      <c r="C7" s="35">
+        <v>-4346.74</v>
       </c>
     </row>
   </sheetData>

--- a/core/sample-data/Financial Template.xlsx
+++ b/core/sample-data/Financial Template.xlsx
@@ -3,21 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10419"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D08D68D0-330B-AF4D-B757-91DCB4267DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C139EB28-2D46-0E42-AC68-08019D845E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8080" yWindow="600" windowWidth="30320" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5040" yWindow="600" windowWidth="23760" windowHeight="14620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Accounts" sheetId="4" r:id="rId1"/>
-    <sheet name="Net Worth MoM" sheetId="2" r:id="rId2"/>
-    <sheet name="Mortgage" sheetId="1" r:id="rId3"/>
-    <sheet name="Education Savings" sheetId="7" r:id="rId4"/>
-    <sheet name="Brokerage Ledger" sheetId="3" r:id="rId5"/>
-    <sheet name="TICKERS" sheetId="5" r:id="rId6"/>
+    <sheet name="Lookup Tables" sheetId="8" r:id="rId1"/>
+    <sheet name="Accounts" sheetId="4" r:id="rId2"/>
+    <sheet name="Net Worth MoM" sheetId="2" r:id="rId3"/>
+    <sheet name="Mortgage" sheetId="1" r:id="rId4"/>
+    <sheet name="Education Savings" sheetId="7" r:id="rId5"/>
+    <sheet name="Brokerage Ledger" sheetId="3" r:id="rId6"/>
+    <sheet name="TICKERS" sheetId="5" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-  </externalReferences>
   <definedNames>
     <definedName name="APR">#REF!</definedName>
     <definedName name="Current_Debt_Total">#REF!</definedName>
@@ -49,7 +47,6 @@
     <definedName name="TotalSpent">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -67,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="317">
   <si>
     <t>I captured data at month end balances</t>
   </si>
@@ -204,9 +201,6 @@
     <t>Drew</t>
   </si>
   <si>
-    <t>IRA</t>
-  </si>
-  <si>
     <t>Shaun</t>
   </si>
   <si>
@@ -973,6 +967,54 @@
   </si>
   <si>
     <t>Etta</t>
+  </si>
+  <si>
+    <t>Subtype</t>
+  </si>
+  <si>
+    <t>Account Type Lookup</t>
+  </si>
+  <si>
+    <t>Trust</t>
+  </si>
+  <si>
+    <t>Custodial (UTMA/UGMA)</t>
+  </si>
+  <si>
+    <t>Traditional IRA</t>
+  </si>
+  <si>
+    <t>Roth IRA</t>
+  </si>
+  <si>
+    <t>Traditional 401k</t>
+  </si>
+  <si>
+    <t>Roth 401k</t>
+  </si>
+  <si>
+    <t>403b</t>
+  </si>
+  <si>
+    <t>SEP-IRA</t>
+  </si>
+  <si>
+    <t>SIMPLE IRA</t>
+  </si>
+  <si>
+    <t>Inherited IRA</t>
+  </si>
+  <si>
+    <t>Pension</t>
+  </si>
+  <si>
+    <t>ESA</t>
+  </si>
+  <si>
+    <t>Coverdell</t>
+  </si>
+  <si>
+    <t>RSU</t>
   </si>
 </sst>
 </file>
@@ -986,9 +1028,16 @@
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="\(\$#,##0.00\);\(\$#,##0.00\)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1072,13 +1121,25 @@
       <name val="Century Gothic"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9948118533890809E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="8">
@@ -1159,81 +1220,253 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{10CC939A-9C43-5A47-9CD6-66EBEC4B354C}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{EB8C820B-5C71-B145-A78B-69D5C661F67B}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </left>
+        <top style="thin">
+          <color theme="6" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Helvetica"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Helvetica"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Helvetica"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1246,45 +1479,33 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Net Worth MoM"/>
-      <sheetName val="Mortgage"/>
-      <sheetName val="Education Savings"/>
-      <sheetName val="Brokerage Ledger"/>
-      <sheetName val="Accounts"/>
-      <sheetName val="TICKERS"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{23417DED-0198-6143-B962-A0F5AD48A263}" name="Table3" displayName="Table3" ref="B2:C18" totalsRowShown="0" dataDxfId="8">
+  <autoFilter ref="B2:C18" xr:uid="{EE18B4AB-3C31-074B-A1AF-5770971F7EB4}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{6C8268AC-5A43-7348-9E49-D23B2435E709}" name="Subtype" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{D8D4C27C-BFF3-F042-8978-1BA496608353}" name="Account Type Lookup" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="B2:D5" headerRowCount="0">
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0D7E2D6C-8E1C-F24C-83A8-9E87B40A4569}" name="Table25" displayName="Table25" ref="B2:D5" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="3" tableBorderDxfId="4" headerRowCellStyle="Normal 2">
+  <autoFilter ref="B2:D5" xr:uid="{0D7E2D6C-8E1C-F24C-83A8-9E87B40A4569}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D18">
+    <sortCondition ref="B2:B18"/>
+  </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Account"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Account Type2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Owner"/>
+    <tableColumn id="1" xr3:uid="{72977136-617E-3D4C-816B-64DF4BBF921D}" name="Account" dataDxfId="2" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{338E490B-1E56-0F49-A92F-12E01D9C90B5}" name="Account Type2" dataDxfId="1" dataCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{016074AD-D643-FD4C-9370-CFB89011C724}" name="Owner" dataDxfId="0" dataCellStyle="Normal 3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table36" displayName="Table36" ref="B2:C123" headerRowCount="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Symbol"/>
@@ -1578,114 +1799,152 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F439092A-223E-9041-81FE-731F9A326330}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="B2:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:C18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="11" customWidth="1"/>
-    <col min="2" max="3" width="14.6640625" style="11" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="11" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="11"/>
+    <col min="2" max="2" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="16" t="s">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="C3" s="38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B4" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B5" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B6" s="38" t="s">
+        <v>305</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B7" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B8" s="38" t="s">
+        <v>307</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B9" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B10" s="38" t="s">
+        <v>309</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B11" s="38" t="s">
+        <v>310</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B12" s="38" t="s">
+        <v>311</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B13" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B14" s="38" t="s">
+        <v>313</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B15" s="38" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="26"/>
-      <c r="C6" s="16"/>
-    </row>
-    <row r="7" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="26"/>
-      <c r="C7" s="16"/>
-    </row>
-    <row r="8" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="26"/>
-      <c r="C8" s="16"/>
-    </row>
-    <row r="9" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="26"/>
-      <c r="C9" s="16"/>
-    </row>
-    <row r="10" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="26"/>
-      <c r="C10" s="16"/>
-    </row>
-    <row r="11" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="26"/>
-      <c r="C11" s="16"/>
-    </row>
-    <row r="12" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="26"/>
-      <c r="C12" s="16"/>
-    </row>
-    <row r="13" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="26"/>
-      <c r="C13" s="16"/>
-    </row>
-    <row r="14" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="26"/>
-      <c r="C14" s="16"/>
-    </row>
-    <row r="15" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="27"/>
-      <c r="C15" s="16"/>
-    </row>
-    <row r="16" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="27"/>
-      <c r="C16" s="16"/>
-    </row>
-    <row r="17" spans="2:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="27"/>
-      <c r="C17" s="16"/>
-    </row>
-    <row r="18" spans="2:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="27"/>
-      <c r="C18" s="16"/>
+      <c r="C15" s="38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B16" s="38">
+        <v>529</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B17" s="38" t="s">
+        <v>315</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="B18" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1696,6 +1955,123 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor theme="8"/>
+  </sheetPr>
+  <dimension ref="B2:D18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="41"/>
+    <col min="2" max="3" width="14.6640625" style="41" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="41"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B2" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B3" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B6" s="42"/>
+      <c r="C6" s="43"/>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" s="42"/>
+      <c r="C7" s="43"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B8" s="42"/>
+      <c r="C8" s="43"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" s="42"/>
+      <c r="C9" s="43"/>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B10" s="42"/>
+      <c r="C10" s="43"/>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B11" s="42"/>
+      <c r="C11" s="43"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B12" s="42"/>
+      <c r="C12" s="43"/>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B13" s="42"/>
+      <c r="C13" s="43"/>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B14" s="42"/>
+      <c r="C14" s="43"/>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="44"/>
+      <c r="C15" s="43"/>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="44"/>
+      <c r="C16" s="43"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B17" s="44"/>
+      <c r="C17" s="43"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B18" s="44"/>
+      <c r="C18" s="43"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -3003,7 +3379,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
@@ -3018,31 +3394,31 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2" t="s">
         <v>282</v>
-      </c>
-      <c r="C2" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C3" s="33">
+        <v>283</v>
+      </c>
+      <c r="C3" s="29">
         <v>725000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>285</v>
-      </c>
-      <c r="C4" s="34">
+        <v>284</v>
+      </c>
+      <c r="C4" s="30">
         <v>45139</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -3050,7 +3426,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C6" s="10">
         <v>0.06</v>
@@ -3058,9 +3434,9 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>288</v>
-      </c>
-      <c r="C7" s="35">
+        <v>287</v>
+      </c>
+      <c r="C7" s="31">
         <v>-4346.74</v>
       </c>
     </row>
@@ -3070,7 +3446,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB0E85D-0232-5647-9A75-FF64DBBA5AC5}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -3113,1855 +3489,1855 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:155" x14ac:dyDescent="0.2">
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="36"/>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
-      <c r="AD1" s="36"/>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="36"/>
-      <c r="AK1" s="36"/>
-      <c r="AL1" s="36"/>
-      <c r="AM1" s="36"/>
-      <c r="AN1" s="36"/>
-      <c r="AO1" s="36"/>
-      <c r="AP1" s="36"/>
-      <c r="AQ1" s="36"/>
-      <c r="AR1" s="36"/>
-      <c r="AS1" s="36"/>
-      <c r="AT1" s="36"/>
-      <c r="AU1" s="36"/>
-      <c r="AV1" s="36"/>
-      <c r="AW1" s="36"/>
-      <c r="AX1" s="36"/>
-      <c r="AY1" s="36"/>
-      <c r="AZ1" s="36"/>
-      <c r="BA1" s="36" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
+      <c r="Y1" s="32"/>
+      <c r="Z1" s="32"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="32"/>
+      <c r="AC1" s="32"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="32"/>
+      <c r="AF1" s="32"/>
+      <c r="AG1" s="32"/>
+      <c r="AH1" s="32"/>
+      <c r="AI1" s="32"/>
+      <c r="AJ1" s="32"/>
+      <c r="AK1" s="32"/>
+      <c r="AL1" s="32"/>
+      <c r="AM1" s="32"/>
+      <c r="AN1" s="32"/>
+      <c r="AO1" s="32"/>
+      <c r="AP1" s="32"/>
+      <c r="AQ1" s="32"/>
+      <c r="AR1" s="32"/>
+      <c r="AS1" s="32"/>
+      <c r="AT1" s="32"/>
+      <c r="AU1" s="32"/>
+      <c r="AV1" s="32"/>
+      <c r="AW1" s="32"/>
+      <c r="AX1" s="32"/>
+      <c r="AY1" s="32"/>
+      <c r="AZ1" s="32"/>
+      <c r="BA1" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="BB1" s="32"/>
+      <c r="BC1" s="32"/>
+      <c r="BD1" s="32"/>
+      <c r="BE1" s="32"/>
+      <c r="BF1" s="32"/>
+      <c r="BG1" s="32"/>
+      <c r="BH1" s="32"/>
+      <c r="BI1" s="32"/>
+      <c r="BJ1" s="32"/>
+      <c r="BK1" s="32"/>
+      <c r="BL1" s="32"/>
+      <c r="BM1" s="32"/>
+      <c r="BN1" s="32"/>
+      <c r="BO1" s="32"/>
+      <c r="BP1" s="32"/>
+      <c r="BQ1" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="BB1" s="36"/>
-      <c r="BC1" s="36"/>
-      <c r="BD1" s="36"/>
-      <c r="BE1" s="36"/>
-      <c r="BF1" s="36"/>
-      <c r="BG1" s="36"/>
-      <c r="BH1" s="36"/>
-      <c r="BI1" s="36"/>
-      <c r="BJ1" s="36"/>
-      <c r="BK1" s="36"/>
-      <c r="BL1" s="36"/>
-      <c r="BM1" s="36"/>
-      <c r="BN1" s="36"/>
-      <c r="BO1" s="36"/>
-      <c r="BP1" s="36"/>
-      <c r="BQ1" s="36" t="s">
+      <c r="BR1" s="32"/>
+      <c r="BS1" s="32"/>
+      <c r="BT1" s="32"/>
+      <c r="BU1" s="32"/>
+      <c r="BV1" s="32"/>
+      <c r="BW1" s="32"/>
+      <c r="BX1" s="32"/>
+      <c r="BY1" s="32"/>
+      <c r="BZ1" s="32"/>
+      <c r="CA1" s="32"/>
+      <c r="CB1" s="32"/>
+      <c r="CC1" s="32"/>
+      <c r="CD1" s="32"/>
+      <c r="CE1" s="32"/>
+      <c r="CF1" s="32"/>
+      <c r="CG1" s="32"/>
+      <c r="CH1" s="32"/>
+      <c r="CI1" s="32"/>
+      <c r="CJ1" s="32"/>
+      <c r="CK1" s="32"/>
+      <c r="CL1" s="32"/>
+      <c r="CM1" s="32"/>
+      <c r="CN1" s="32"/>
+      <c r="CO1" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="BR1" s="36"/>
-      <c r="BS1" s="36"/>
-      <c r="BT1" s="36"/>
-      <c r="BU1" s="36"/>
-      <c r="BV1" s="36"/>
-      <c r="BW1" s="36"/>
-      <c r="BX1" s="36"/>
-      <c r="BY1" s="36"/>
-      <c r="BZ1" s="36"/>
-      <c r="CA1" s="36"/>
-      <c r="CB1" s="36"/>
-      <c r="CC1" s="36"/>
-      <c r="CD1" s="36"/>
-      <c r="CE1" s="36"/>
-      <c r="CF1" s="36"/>
-      <c r="CG1" s="36"/>
-      <c r="CH1" s="36"/>
-      <c r="CI1" s="36"/>
-      <c r="CJ1" s="36"/>
-      <c r="CK1" s="36"/>
-      <c r="CL1" s="36"/>
-      <c r="CM1" s="36"/>
-      <c r="CN1" s="36"/>
-      <c r="CO1" s="36" t="s">
+      <c r="CP1" s="32"/>
+      <c r="CQ1" s="32"/>
+      <c r="CR1" s="32"/>
+      <c r="CS1" s="32"/>
+      <c r="CT1" s="32"/>
+      <c r="CU1" s="32"/>
+      <c r="CV1" s="32"/>
+      <c r="CW1" s="32"/>
+      <c r="CX1" s="32"/>
+      <c r="CY1" s="32"/>
+      <c r="CZ1" s="32"/>
+      <c r="DA1" s="32"/>
+      <c r="DB1" s="32"/>
+      <c r="DC1" s="32"/>
+      <c r="DD1" s="32"/>
+      <c r="DE1" s="32"/>
+      <c r="DF1" s="32"/>
+      <c r="DG1" s="32"/>
+      <c r="DH1" s="32"/>
+      <c r="DI1" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="CP1" s="36"/>
-      <c r="CQ1" s="36"/>
-      <c r="CR1" s="36"/>
-      <c r="CS1" s="36"/>
-      <c r="CT1" s="36"/>
-      <c r="CU1" s="36"/>
-      <c r="CV1" s="36"/>
-      <c r="CW1" s="36"/>
-      <c r="CX1" s="36"/>
-      <c r="CY1" s="36"/>
-      <c r="CZ1" s="36"/>
-      <c r="DA1" s="36"/>
-      <c r="DB1" s="36"/>
-      <c r="DC1" s="36"/>
-      <c r="DD1" s="36"/>
-      <c r="DE1" s="36"/>
-      <c r="DF1" s="36"/>
-      <c r="DG1" s="36"/>
-      <c r="DH1" s="36"/>
-      <c r="DI1" s="36" t="s">
+      <c r="DJ1" s="32"/>
+      <c r="DK1" s="32"/>
+      <c r="DL1" s="32"/>
+      <c r="DM1" s="32"/>
+      <c r="DN1" s="32"/>
+      <c r="DO1" s="32"/>
+      <c r="DP1" s="32"/>
+      <c r="DQ1" s="32"/>
+      <c r="DR1" s="32"/>
+      <c r="DS1" s="32"/>
+      <c r="DT1" s="32"/>
+      <c r="DU1" s="32"/>
+      <c r="DV1" s="32"/>
+      <c r="DW1" s="32"/>
+      <c r="DX1" s="32"/>
+      <c r="DY1" s="32"/>
+      <c r="DZ1" s="32"/>
+      <c r="EA1" s="32"/>
+      <c r="EB1" s="32"/>
+      <c r="EC1" s="32"/>
+      <c r="ED1" s="32"/>
+      <c r="EE1" s="32"/>
+      <c r="EF1" s="32"/>
+      <c r="EG1" s="32"/>
+      <c r="EH1" s="32"/>
+      <c r="EI1" s="32"/>
+      <c r="EJ1" s="32"/>
+      <c r="EK1" s="32"/>
+      <c r="EL1" s="32"/>
+      <c r="EM1" s="32"/>
+      <c r="EN1" s="32"/>
+      <c r="EO1" s="32"/>
+      <c r="EP1" s="32"/>
+      <c r="EQ1" s="32"/>
+      <c r="ER1" s="32"/>
+      <c r="ES1" s="32"/>
+      <c r="ET1" s="32"/>
+      <c r="EU1" s="32"/>
+      <c r="EV1" s="32"/>
+      <c r="EW1" s="32"/>
+      <c r="EX1" s="32" t="s">
         <v>292</v>
       </c>
-      <c r="DJ1" s="36"/>
-      <c r="DK1" s="36"/>
-      <c r="DL1" s="36"/>
-      <c r="DM1" s="36"/>
-      <c r="DN1" s="36"/>
-      <c r="DO1" s="36"/>
-      <c r="DP1" s="36"/>
-      <c r="DQ1" s="36"/>
-      <c r="DR1" s="36"/>
-      <c r="DS1" s="36"/>
-      <c r="DT1" s="36"/>
-      <c r="DU1" s="36"/>
-      <c r="DV1" s="36"/>
-      <c r="DW1" s="36"/>
-      <c r="DX1" s="36"/>
-      <c r="DY1" s="36"/>
-      <c r="DZ1" s="36"/>
-      <c r="EA1" s="36"/>
-      <c r="EB1" s="36"/>
-      <c r="EC1" s="36"/>
-      <c r="ED1" s="36"/>
-      <c r="EE1" s="36"/>
-      <c r="EF1" s="36"/>
-      <c r="EG1" s="36"/>
-      <c r="EH1" s="36"/>
-      <c r="EI1" s="36"/>
-      <c r="EJ1" s="36"/>
-      <c r="EK1" s="36"/>
-      <c r="EL1" s="36"/>
-      <c r="EM1" s="36"/>
-      <c r="EN1" s="36"/>
-      <c r="EO1" s="36"/>
-      <c r="EP1" s="36"/>
-      <c r="EQ1" s="36"/>
-      <c r="ER1" s="36"/>
-      <c r="ES1" s="36"/>
-      <c r="ET1" s="36"/>
-      <c r="EU1" s="36"/>
-      <c r="EV1" s="36"/>
-      <c r="EW1" s="36"/>
-      <c r="EX1" s="36" t="s">
+      <c r="EY1" s="32"/>
+    </row>
+    <row r="2" spans="2:155" x14ac:dyDescent="0.2">
+      <c r="B2" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="EY1" s="36"/>
-    </row>
-    <row r="2" spans="2:155" x14ac:dyDescent="0.2">
-      <c r="B2" s="37" t="s">
+      <c r="C2" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="D2" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="E2" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>297</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="G2" s="34">
+        <v>43831</v>
+      </c>
+      <c r="H2" s="34">
+        <v>44197</v>
+      </c>
+      <c r="I2" s="34">
+        <v>44562</v>
+      </c>
+      <c r="J2" s="34">
+        <v>44927</v>
+      </c>
+      <c r="K2" s="34">
+        <v>44958</v>
+      </c>
+      <c r="L2" s="34">
+        <v>44986</v>
+      </c>
+      <c r="M2" s="34">
+        <v>45017</v>
+      </c>
+      <c r="N2" s="34">
+        <v>45047</v>
+      </c>
+      <c r="O2" s="34">
+        <v>45078</v>
+      </c>
+      <c r="P2" s="34">
+        <v>45108</v>
+      </c>
+      <c r="Q2" s="34">
+        <v>45139</v>
+      </c>
+      <c r="R2" s="34">
+        <v>45170</v>
+      </c>
+      <c r="S2" s="34">
+        <v>45200</v>
+      </c>
+      <c r="T2" s="34">
+        <v>45231</v>
+      </c>
+      <c r="U2" s="34">
+        <v>45261</v>
+      </c>
+      <c r="V2" s="34">
+        <v>45292</v>
+      </c>
+      <c r="W2" s="34">
+        <v>45323</v>
+      </c>
+      <c r="X2" s="34">
+        <v>45352</v>
+      </c>
+      <c r="Y2" s="34">
+        <v>45383</v>
+      </c>
+      <c r="Z2" s="34">
+        <v>45413</v>
+      </c>
+      <c r="AA2" s="34">
+        <v>45444</v>
+      </c>
+      <c r="AB2" s="34">
+        <v>45474</v>
+      </c>
+      <c r="AC2" s="34">
+        <v>45505</v>
+      </c>
+      <c r="AD2" s="34">
+        <v>45536</v>
+      </c>
+      <c r="AE2" s="34">
+        <v>45566</v>
+      </c>
+      <c r="AF2" s="34">
+        <v>45597</v>
+      </c>
+      <c r="AG2" s="34">
+        <v>45627</v>
+      </c>
+      <c r="AH2" s="34">
+        <v>45658</v>
+      </c>
+      <c r="AI2" s="34">
+        <v>45689</v>
+      </c>
+      <c r="AJ2" s="34">
+        <v>45717</v>
+      </c>
+      <c r="AK2" s="34">
+        <v>45748</v>
+      </c>
+      <c r="AL2" s="34">
+        <v>45778</v>
+      </c>
+      <c r="AM2" s="34">
+        <v>45809</v>
+      </c>
+      <c r="AN2" s="34">
+        <v>45839</v>
+      </c>
+      <c r="AO2" s="34">
+        <v>45870</v>
+      </c>
+      <c r="AP2" s="34">
+        <v>45901</v>
+      </c>
+      <c r="AQ2" s="34">
+        <v>45931</v>
+      </c>
+      <c r="AR2" s="34">
+        <v>45962</v>
+      </c>
+      <c r="AS2" s="34">
+        <v>45992</v>
+      </c>
+      <c r="AT2" s="34">
+        <v>46023</v>
+      </c>
+      <c r="AU2" s="34">
+        <v>46054</v>
+      </c>
+      <c r="AV2" s="34">
+        <v>46082</v>
+      </c>
+      <c r="AW2" s="34">
+        <v>46113</v>
+      </c>
+      <c r="AX2" s="34">
+        <v>46143</v>
+      </c>
+      <c r="AY2" s="34">
+        <v>46174</v>
+      </c>
+      <c r="AZ2" s="34">
+        <v>46204</v>
+      </c>
+      <c r="BA2" s="34">
+        <v>46235</v>
+      </c>
+      <c r="BB2" s="34">
+        <v>46266</v>
+      </c>
+      <c r="BC2" s="34">
+        <v>46296</v>
+      </c>
+      <c r="BD2" s="34">
+        <v>46327</v>
+      </c>
+      <c r="BE2" s="34">
+        <v>46357</v>
+      </c>
+      <c r="BF2" s="34">
+        <v>46388</v>
+      </c>
+      <c r="BG2" s="34">
+        <v>46419</v>
+      </c>
+      <c r="BH2" s="34">
+        <v>46447</v>
+      </c>
+      <c r="BI2" s="34">
+        <v>46478</v>
+      </c>
+      <c r="BJ2" s="34">
+        <v>46508</v>
+      </c>
+      <c r="BK2" s="34">
+        <v>46539</v>
+      </c>
+      <c r="BL2" s="34">
+        <v>46569</v>
+      </c>
+      <c r="BM2" s="34">
+        <v>46600</v>
+      </c>
+      <c r="BN2" s="34">
+        <v>46631</v>
+      </c>
+      <c r="BO2" s="34">
+        <v>46661</v>
+      </c>
+      <c r="BP2" s="34">
+        <v>46692</v>
+      </c>
+      <c r="BQ2" s="34">
+        <v>46722</v>
+      </c>
+      <c r="BR2" s="34">
+        <v>46753</v>
+      </c>
+      <c r="BS2" s="34">
+        <v>46784</v>
+      </c>
+      <c r="BT2" s="34">
+        <v>46813</v>
+      </c>
+      <c r="BU2" s="34">
+        <v>46844</v>
+      </c>
+      <c r="BV2" s="34">
+        <v>46874</v>
+      </c>
+      <c r="BW2" s="34">
+        <v>46905</v>
+      </c>
+      <c r="BX2" s="34">
+        <v>46935</v>
+      </c>
+      <c r="BY2" s="34">
+        <v>46966</v>
+      </c>
+      <c r="BZ2" s="34">
+        <v>46997</v>
+      </c>
+      <c r="CA2" s="34">
+        <v>47027</v>
+      </c>
+      <c r="CB2" s="34">
+        <v>47058</v>
+      </c>
+      <c r="CC2" s="34">
+        <v>47088</v>
+      </c>
+      <c r="CD2" s="34">
+        <v>47119</v>
+      </c>
+      <c r="CE2" s="34">
+        <v>47150</v>
+      </c>
+      <c r="CF2" s="34">
+        <v>47178</v>
+      </c>
+      <c r="CG2" s="34">
+        <v>47209</v>
+      </c>
+      <c r="CH2" s="34">
+        <v>47239</v>
+      </c>
+      <c r="CI2" s="34">
+        <v>47270</v>
+      </c>
+      <c r="CJ2" s="34">
+        <v>47300</v>
+      </c>
+      <c r="CK2" s="34">
+        <v>47331</v>
+      </c>
+      <c r="CL2" s="34">
+        <v>47362</v>
+      </c>
+      <c r="CM2" s="34">
+        <v>47392</v>
+      </c>
+      <c r="CN2" s="34">
+        <v>47423</v>
+      </c>
+      <c r="CO2" s="34">
+        <v>47453</v>
+      </c>
+      <c r="CP2" s="34">
+        <v>10959</v>
+      </c>
+      <c r="CQ2" s="34">
+        <v>10990</v>
+      </c>
+      <c r="CR2" s="34">
+        <v>11018</v>
+      </c>
+      <c r="CS2" s="34">
+        <v>11049</v>
+      </c>
+      <c r="CT2" s="34">
+        <v>11079</v>
+      </c>
+      <c r="CU2" s="34">
+        <v>11110</v>
+      </c>
+      <c r="CV2" s="34">
+        <v>11140</v>
+      </c>
+      <c r="CW2" s="34">
+        <v>11171</v>
+      </c>
+      <c r="CX2" s="34">
+        <v>11202</v>
+      </c>
+      <c r="CY2" s="34">
+        <v>11232</v>
+      </c>
+      <c r="CZ2" s="34">
+        <v>11263</v>
+      </c>
+      <c r="DA2" s="34">
+        <v>11293</v>
+      </c>
+      <c r="DB2" s="34">
+        <v>11324</v>
+      </c>
+      <c r="DC2" s="34">
+        <v>11355</v>
+      </c>
+      <c r="DD2" s="34">
+        <v>11383</v>
+      </c>
+      <c r="DE2" s="34">
+        <v>11414</v>
+      </c>
+      <c r="DF2" s="34">
+        <v>11444</v>
+      </c>
+      <c r="DG2" s="34">
+        <v>11475</v>
+      </c>
+      <c r="DH2" s="34">
+        <v>11505</v>
+      </c>
+      <c r="DI2" s="34">
+        <v>11536</v>
+      </c>
+      <c r="DJ2" s="34">
+        <v>11567</v>
+      </c>
+      <c r="DK2" s="34">
+        <v>11597</v>
+      </c>
+      <c r="DL2" s="34">
+        <v>11628</v>
+      </c>
+      <c r="DM2" s="34">
+        <v>11658</v>
+      </c>
+      <c r="DN2" s="34">
+        <v>11689</v>
+      </c>
+      <c r="DO2" s="34">
+        <v>11720</v>
+      </c>
+      <c r="DP2" s="34">
+        <v>11749</v>
+      </c>
+      <c r="DQ2" s="34">
+        <v>11780</v>
+      </c>
+      <c r="DR2" s="34">
+        <v>11810</v>
+      </c>
+      <c r="DS2" s="34">
+        <v>11841</v>
+      </c>
+      <c r="DT2" s="34">
+        <v>11871</v>
+      </c>
+      <c r="DU2" s="34">
+        <v>11902</v>
+      </c>
+      <c r="DV2" s="34">
+        <v>11933</v>
+      </c>
+      <c r="DW2" s="34">
+        <v>11963</v>
+      </c>
+      <c r="DX2" s="34">
+        <v>11994</v>
+      </c>
+      <c r="DY2" s="34">
+        <v>12024</v>
+      </c>
+      <c r="DZ2" s="34">
+        <v>12055</v>
+      </c>
+      <c r="EA2" s="34">
+        <v>12086</v>
+      </c>
+      <c r="EB2" s="34">
+        <v>12114</v>
+      </c>
+      <c r="EC2" s="34">
+        <v>12145</v>
+      </c>
+      <c r="ED2" s="34">
+        <v>12175</v>
+      </c>
+      <c r="EE2" s="34">
+        <v>12206</v>
+      </c>
+      <c r="EF2" s="34">
+        <v>12236</v>
+      </c>
+      <c r="EG2" s="34">
+        <v>12267</v>
+      </c>
+      <c r="EH2" s="34">
+        <v>12298</v>
+      </c>
+      <c r="EI2" s="34">
+        <v>12328</v>
+      </c>
+      <c r="EJ2" s="34">
+        <v>12359</v>
+      </c>
+      <c r="EK2" s="34">
+        <v>12389</v>
+      </c>
+      <c r="EL2" s="34">
+        <v>12420</v>
+      </c>
+      <c r="EM2" s="34">
+        <v>12451</v>
+      </c>
+      <c r="EN2" s="34">
+        <v>12479</v>
+      </c>
+      <c r="EO2" s="34">
+        <v>12510</v>
+      </c>
+      <c r="EP2" s="34">
+        <v>12540</v>
+      </c>
+      <c r="EQ2" s="34">
+        <v>12571</v>
+      </c>
+      <c r="ER2" s="34">
+        <v>12601</v>
+      </c>
+      <c r="ES2" s="34">
+        <v>12632</v>
+      </c>
+      <c r="ET2" s="34">
+        <v>12663</v>
+      </c>
+      <c r="EU2" s="34">
+        <v>12693</v>
+      </c>
+      <c r="EV2" s="34">
+        <v>12724</v>
+      </c>
+      <c r="EW2" s="34">
+        <v>12754</v>
+      </c>
+      <c r="EX2" s="34">
+        <v>12785</v>
+      </c>
+      <c r="EY2" s="34">
+        <v>12816</v>
+      </c>
+    </row>
+    <row r="3" spans="2:155" x14ac:dyDescent="0.2">
+      <c r="B3" s="32" t="s">
         <v>298</v>
       </c>
-      <c r="G2" s="38">
-        <v>43831</v>
-      </c>
-      <c r="H2" s="38">
-        <v>44197</v>
-      </c>
-      <c r="I2" s="38">
-        <v>44562</v>
-      </c>
-      <c r="J2" s="38">
-        <v>44927</v>
-      </c>
-      <c r="K2" s="38">
-        <v>44958</v>
-      </c>
-      <c r="L2" s="38">
-        <v>44986</v>
-      </c>
-      <c r="M2" s="38">
-        <v>45017</v>
-      </c>
-      <c r="N2" s="38">
-        <v>45047</v>
-      </c>
-      <c r="O2" s="38">
-        <v>45078</v>
-      </c>
-      <c r="P2" s="38">
-        <v>45108</v>
-      </c>
-      <c r="Q2" s="38">
-        <v>45139</v>
-      </c>
-      <c r="R2" s="38">
-        <v>45170</v>
-      </c>
-      <c r="S2" s="38">
-        <v>45200</v>
-      </c>
-      <c r="T2" s="38">
-        <v>45231</v>
-      </c>
-      <c r="U2" s="38">
-        <v>45261</v>
-      </c>
-      <c r="V2" s="38">
-        <v>45292</v>
-      </c>
-      <c r="W2" s="38">
-        <v>45323</v>
-      </c>
-      <c r="X2" s="38">
-        <v>45352</v>
-      </c>
-      <c r="Y2" s="38">
-        <v>45383</v>
-      </c>
-      <c r="Z2" s="38">
-        <v>45413</v>
-      </c>
-      <c r="AA2" s="38">
-        <v>45444</v>
-      </c>
-      <c r="AB2" s="38">
-        <v>45474</v>
-      </c>
-      <c r="AC2" s="38">
-        <v>45505</v>
-      </c>
-      <c r="AD2" s="38">
-        <v>45536</v>
-      </c>
-      <c r="AE2" s="38">
-        <v>45566</v>
-      </c>
-      <c r="AF2" s="38">
-        <v>45597</v>
-      </c>
-      <c r="AG2" s="38">
-        <v>45627</v>
-      </c>
-      <c r="AH2" s="38">
-        <v>45658</v>
-      </c>
-      <c r="AI2" s="38">
-        <v>45689</v>
-      </c>
-      <c r="AJ2" s="38">
-        <v>45717</v>
-      </c>
-      <c r="AK2" s="38">
-        <v>45748</v>
-      </c>
-      <c r="AL2" s="38">
-        <v>45778</v>
-      </c>
-      <c r="AM2" s="38">
-        <v>45809</v>
-      </c>
-      <c r="AN2" s="38">
-        <v>45839</v>
-      </c>
-      <c r="AO2" s="38">
-        <v>45870</v>
-      </c>
-      <c r="AP2" s="38">
-        <v>45901</v>
-      </c>
-      <c r="AQ2" s="38">
-        <v>45931</v>
-      </c>
-      <c r="AR2" s="38">
-        <v>45962</v>
-      </c>
-      <c r="AS2" s="38">
-        <v>45992</v>
-      </c>
-      <c r="AT2" s="38">
-        <v>46023</v>
-      </c>
-      <c r="AU2" s="38">
-        <v>46054</v>
-      </c>
-      <c r="AV2" s="38">
-        <v>46082</v>
-      </c>
-      <c r="AW2" s="38">
-        <v>46113</v>
-      </c>
-      <c r="AX2" s="38">
-        <v>46143</v>
-      </c>
-      <c r="AY2" s="38">
-        <v>46174</v>
-      </c>
-      <c r="AZ2" s="38">
-        <v>46204</v>
-      </c>
-      <c r="BA2" s="38">
-        <v>46235</v>
-      </c>
-      <c r="BB2" s="38">
-        <v>46266</v>
-      </c>
-      <c r="BC2" s="38">
-        <v>46296</v>
-      </c>
-      <c r="BD2" s="38">
-        <v>46327</v>
-      </c>
-      <c r="BE2" s="38">
-        <v>46357</v>
-      </c>
-      <c r="BF2" s="38">
-        <v>46388</v>
-      </c>
-      <c r="BG2" s="38">
-        <v>46419</v>
-      </c>
-      <c r="BH2" s="38">
-        <v>46447</v>
-      </c>
-      <c r="BI2" s="38">
-        <v>46478</v>
-      </c>
-      <c r="BJ2" s="38">
-        <v>46508</v>
-      </c>
-      <c r="BK2" s="38">
-        <v>46539</v>
-      </c>
-      <c r="BL2" s="38">
-        <v>46569</v>
-      </c>
-      <c r="BM2" s="38">
-        <v>46600</v>
-      </c>
-      <c r="BN2" s="38">
-        <v>46631</v>
-      </c>
-      <c r="BO2" s="38">
-        <v>46661</v>
-      </c>
-      <c r="BP2" s="38">
-        <v>46692</v>
-      </c>
-      <c r="BQ2" s="38">
-        <v>46722</v>
-      </c>
-      <c r="BR2" s="38">
-        <v>46753</v>
-      </c>
-      <c r="BS2" s="38">
-        <v>46784</v>
-      </c>
-      <c r="BT2" s="38">
-        <v>46813</v>
-      </c>
-      <c r="BU2" s="38">
-        <v>46844</v>
-      </c>
-      <c r="BV2" s="38">
-        <v>46874</v>
-      </c>
-      <c r="BW2" s="38">
-        <v>46905</v>
-      </c>
-      <c r="BX2" s="38">
-        <v>46935</v>
-      </c>
-      <c r="BY2" s="38">
-        <v>46966</v>
-      </c>
-      <c r="BZ2" s="38">
-        <v>46997</v>
-      </c>
-      <c r="CA2" s="38">
-        <v>47027</v>
-      </c>
-      <c r="CB2" s="38">
-        <v>47058</v>
-      </c>
-      <c r="CC2" s="38">
-        <v>47088</v>
-      </c>
-      <c r="CD2" s="38">
-        <v>47119</v>
-      </c>
-      <c r="CE2" s="38">
-        <v>47150</v>
-      </c>
-      <c r="CF2" s="38">
-        <v>47178</v>
-      </c>
-      <c r="CG2" s="38">
-        <v>47209</v>
-      </c>
-      <c r="CH2" s="38">
-        <v>47239</v>
-      </c>
-      <c r="CI2" s="38">
-        <v>47270</v>
-      </c>
-      <c r="CJ2" s="38">
-        <v>47300</v>
-      </c>
-      <c r="CK2" s="38">
-        <v>47331</v>
-      </c>
-      <c r="CL2" s="38">
-        <v>47362</v>
-      </c>
-      <c r="CM2" s="38">
-        <v>47392</v>
-      </c>
-      <c r="CN2" s="38">
-        <v>47423</v>
-      </c>
-      <c r="CO2" s="38">
-        <v>47453</v>
-      </c>
-      <c r="CP2" s="38">
-        <v>10959</v>
-      </c>
-      <c r="CQ2" s="38">
-        <v>10990</v>
-      </c>
-      <c r="CR2" s="38">
-        <v>11018</v>
-      </c>
-      <c r="CS2" s="38">
-        <v>11049</v>
-      </c>
-      <c r="CT2" s="38">
-        <v>11079</v>
-      </c>
-      <c r="CU2" s="38">
-        <v>11110</v>
-      </c>
-      <c r="CV2" s="38">
-        <v>11140</v>
-      </c>
-      <c r="CW2" s="38">
-        <v>11171</v>
-      </c>
-      <c r="CX2" s="38">
-        <v>11202</v>
-      </c>
-      <c r="CY2" s="38">
-        <v>11232</v>
-      </c>
-      <c r="CZ2" s="38">
-        <v>11263</v>
-      </c>
-      <c r="DA2" s="38">
-        <v>11293</v>
-      </c>
-      <c r="DB2" s="38">
-        <v>11324</v>
-      </c>
-      <c r="DC2" s="38">
-        <v>11355</v>
-      </c>
-      <c r="DD2" s="38">
-        <v>11383</v>
-      </c>
-      <c r="DE2" s="38">
-        <v>11414</v>
-      </c>
-      <c r="DF2" s="38">
-        <v>11444</v>
-      </c>
-      <c r="DG2" s="38">
-        <v>11475</v>
-      </c>
-      <c r="DH2" s="38">
-        <v>11505</v>
-      </c>
-      <c r="DI2" s="38">
-        <v>11536</v>
-      </c>
-      <c r="DJ2" s="38">
-        <v>11567</v>
-      </c>
-      <c r="DK2" s="38">
-        <v>11597</v>
-      </c>
-      <c r="DL2" s="38">
-        <v>11628</v>
-      </c>
-      <c r="DM2" s="38">
-        <v>11658</v>
-      </c>
-      <c r="DN2" s="38">
-        <v>11689</v>
-      </c>
-      <c r="DO2" s="38">
-        <v>11720</v>
-      </c>
-      <c r="DP2" s="38">
-        <v>11749</v>
-      </c>
-      <c r="DQ2" s="38">
-        <v>11780</v>
-      </c>
-      <c r="DR2" s="38">
-        <v>11810</v>
-      </c>
-      <c r="DS2" s="38">
-        <v>11841</v>
-      </c>
-      <c r="DT2" s="38">
-        <v>11871</v>
-      </c>
-      <c r="DU2" s="38">
-        <v>11902</v>
-      </c>
-      <c r="DV2" s="38">
-        <v>11933</v>
-      </c>
-      <c r="DW2" s="38">
-        <v>11963</v>
-      </c>
-      <c r="DX2" s="38">
-        <v>11994</v>
-      </c>
-      <c r="DY2" s="38">
-        <v>12024</v>
-      </c>
-      <c r="DZ2" s="38">
-        <v>12055</v>
-      </c>
-      <c r="EA2" s="38">
-        <v>12086</v>
-      </c>
-      <c r="EB2" s="38">
-        <v>12114</v>
-      </c>
-      <c r="EC2" s="38">
-        <v>12145</v>
-      </c>
-      <c r="ED2" s="38">
-        <v>12175</v>
-      </c>
-      <c r="EE2" s="38">
-        <v>12206</v>
-      </c>
-      <c r="EF2" s="38">
-        <v>12236</v>
-      </c>
-      <c r="EG2" s="38">
-        <v>12267</v>
-      </c>
-      <c r="EH2" s="38">
-        <v>12298</v>
-      </c>
-      <c r="EI2" s="38">
-        <v>12328</v>
-      </c>
-      <c r="EJ2" s="38">
-        <v>12359</v>
-      </c>
-      <c r="EK2" s="38">
-        <v>12389</v>
-      </c>
-      <c r="EL2" s="38">
-        <v>12420</v>
-      </c>
-      <c r="EM2" s="38">
-        <v>12451</v>
-      </c>
-      <c r="EN2" s="38">
-        <v>12479</v>
-      </c>
-      <c r="EO2" s="38">
-        <v>12510</v>
-      </c>
-      <c r="EP2" s="38">
-        <v>12540</v>
-      </c>
-      <c r="EQ2" s="38">
-        <v>12571</v>
-      </c>
-      <c r="ER2" s="38">
-        <v>12601</v>
-      </c>
-      <c r="ES2" s="38">
-        <v>12632</v>
-      </c>
-      <c r="ET2" s="38">
-        <v>12663</v>
-      </c>
-      <c r="EU2" s="38">
-        <v>12693</v>
-      </c>
-      <c r="EV2" s="38">
-        <v>12724</v>
-      </c>
-      <c r="EW2" s="38">
-        <v>12754</v>
-      </c>
-      <c r="EX2" s="38">
-        <v>12785</v>
-      </c>
-      <c r="EY2" s="38">
-        <v>12816</v>
-      </c>
-    </row>
-    <row r="3" spans="2:155" x14ac:dyDescent="0.2">
-      <c r="B3" s="36" t="s">
-        <v>299</v>
-      </c>
-      <c r="C3" s="39">
+      <c r="C3" s="35">
         <v>-25250</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="35">
         <f>C3*2</f>
         <v>-50500</v>
       </c>
-      <c r="E3" s="40">
+      <c r="E3" s="36">
         <v>45519</v>
       </c>
-      <c r="F3" s="39">
+      <c r="F3" s="35">
         <v>0</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="37">
         <v>40256</v>
       </c>
-      <c r="H3" s="41">
+      <c r="H3" s="37">
         <v>57360</v>
       </c>
-      <c r="I3" s="41">
+      <c r="I3" s="37">
         <v>74280</v>
       </c>
-      <c r="J3" s="41">
+      <c r="J3" s="37">
         <v>61779</v>
       </c>
-      <c r="K3" s="41">
+      <c r="K3" s="37">
         <v>66034</v>
       </c>
-      <c r="L3" s="41">
+      <c r="L3" s="37">
         <v>65607</v>
       </c>
-      <c r="M3" s="41">
+      <c r="M3" s="37">
         <v>65660</v>
       </c>
-      <c r="N3" s="41">
+      <c r="N3" s="37">
         <v>67604</v>
       </c>
-      <c r="O3" s="41">
+      <c r="O3" s="37">
         <v>68098</v>
       </c>
-      <c r="P3" s="41">
+      <c r="P3" s="37">
         <v>70250</v>
       </c>
-      <c r="Q3" s="41">
+      <c r="Q3" s="37">
         <v>70250</v>
       </c>
-      <c r="R3" s="41">
+      <c r="R3" s="37">
         <v>71427</v>
       </c>
-      <c r="S3" s="41">
+      <c r="S3" s="37">
         <v>69603</v>
       </c>
-      <c r="T3" s="41">
+      <c r="T3" s="37">
         <v>70250</v>
       </c>
-      <c r="U3" s="41">
+      <c r="U3" s="37">
         <v>70250</v>
       </c>
-      <c r="V3" s="41">
+      <c r="V3" s="37">
         <v>72031</v>
       </c>
-      <c r="W3" s="41">
+      <c r="W3" s="37">
         <v>70250</v>
       </c>
-      <c r="X3" s="41">
+      <c r="X3" s="37">
         <v>70250</v>
       </c>
-      <c r="Y3" s="41">
+      <c r="Y3" s="37">
         <v>78310</v>
       </c>
-      <c r="Z3" s="41">
+      <c r="Z3" s="37">
         <v>70250</v>
       </c>
-      <c r="AA3" s="41">
+      <c r="AA3" s="37">
         <v>82354</v>
       </c>
-      <c r="AB3" s="41">
+      <c r="AB3" s="37">
         <v>82354</v>
       </c>
-      <c r="AC3" s="41">
+      <c r="AC3" s="37">
         <v>82354</v>
       </c>
-      <c r="AD3" s="41">
+      <c r="AD3" s="37">
         <v>82354</v>
       </c>
-      <c r="AE3" s="41">
+      <c r="AE3" s="37">
         <v>72795</v>
       </c>
-      <c r="AF3" s="41">
+      <c r="AF3" s="37">
         <v>74986</v>
       </c>
-      <c r="AG3" s="41">
+      <c r="AG3" s="37">
         <v>74986</v>
       </c>
-      <c r="AH3" s="41">
+      <c r="AH3" s="37">
         <v>73842</v>
       </c>
-      <c r="AI3" s="41">
+      <c r="AI3" s="37">
         <v>63700</v>
       </c>
-      <c r="AJ3" s="41">
+      <c r="AJ3" s="37">
         <v>63047</v>
       </c>
-      <c r="AK3" s="41">
+      <c r="AK3" s="37">
         <v>60227</v>
       </c>
-      <c r="AL3" s="41">
+      <c r="AL3" s="37">
         <v>59930</v>
       </c>
-      <c r="AM3" s="41">
+      <c r="AM3" s="37">
         <v>60203</v>
       </c>
-      <c r="AN3" s="41">
+      <c r="AN3" s="37">
         <v>62770</v>
       </c>
-      <c r="AO3" s="41">
+      <c r="AO3" s="37">
         <v>50875</v>
       </c>
-      <c r="AP3" s="41">
+      <c r="AP3" s="37">
         <v>52735</v>
       </c>
-      <c r="AQ3" s="41">
+      <c r="AQ3" s="37">
         <v>54831</v>
       </c>
-      <c r="AR3" s="41">
+      <c r="AR3" s="37">
         <v>55894</v>
       </c>
-      <c r="AS3" s="41">
+      <c r="AS3" s="37">
         <v>56016</v>
       </c>
-      <c r="AT3" s="41">
+      <c r="AT3" s="37">
         <v>56015</v>
       </c>
-      <c r="AU3" s="41">
+      <c r="AU3" s="37">
         <v>43211</v>
       </c>
-      <c r="AV3" s="41">
+      <c r="AV3" s="37">
         <v>42870</v>
       </c>
-      <c r="AW3" s="41"/>
-      <c r="AX3" s="41"/>
-      <c r="AY3" s="41"/>
-      <c r="AZ3" s="41"/>
-      <c r="BA3" s="41"/>
-      <c r="BB3" s="41"/>
-      <c r="BC3" s="41"/>
-      <c r="BD3" s="41"/>
-      <c r="BE3" s="41"/>
-      <c r="BF3" s="41"/>
-      <c r="BG3" s="41"/>
-      <c r="BH3" s="41"/>
-      <c r="BI3" s="41"/>
-      <c r="BJ3" s="41"/>
-      <c r="BK3" s="41"/>
-      <c r="BL3" s="41"/>
-      <c r="BM3" s="41"/>
-      <c r="BN3" s="41"/>
-      <c r="BO3" s="41"/>
-      <c r="BP3" s="41"/>
-      <c r="BQ3" s="41"/>
-      <c r="BR3" s="41"/>
-      <c r="BS3" s="41"/>
-      <c r="BT3" s="41"/>
-      <c r="BU3" s="41"/>
-      <c r="BV3" s="41"/>
-      <c r="BW3" s="41"/>
-      <c r="BX3" s="41"/>
-      <c r="BY3" s="41"/>
-      <c r="BZ3" s="41"/>
-      <c r="CA3" s="41"/>
-      <c r="CB3" s="41"/>
-      <c r="CC3" s="41"/>
-      <c r="CD3" s="41"/>
-      <c r="CE3" s="41"/>
-      <c r="CF3" s="41"/>
-      <c r="CG3" s="41"/>
-      <c r="CH3" s="41"/>
-      <c r="CI3" s="41"/>
-      <c r="CJ3" s="41"/>
-      <c r="CK3" s="41"/>
-      <c r="CL3" s="41"/>
-      <c r="CM3" s="41"/>
-      <c r="CN3" s="41"/>
-      <c r="CO3" s="41"/>
-      <c r="CP3" s="41"/>
-      <c r="CQ3" s="41"/>
-      <c r="CR3" s="41"/>
-      <c r="CS3" s="41"/>
-      <c r="CT3" s="41"/>
-      <c r="CU3" s="41"/>
-      <c r="CV3" s="41"/>
-      <c r="CW3" s="41"/>
-      <c r="CX3" s="41"/>
-      <c r="CY3" s="41"/>
-      <c r="CZ3" s="41"/>
-      <c r="DA3" s="41"/>
-      <c r="DB3" s="41"/>
-      <c r="DC3" s="41"/>
-      <c r="DD3" s="41"/>
-      <c r="DE3" s="41"/>
-      <c r="DF3" s="41"/>
-      <c r="DG3" s="41"/>
-      <c r="DH3" s="41"/>
-      <c r="DI3" s="41"/>
-      <c r="DJ3" s="41"/>
-      <c r="DK3" s="41"/>
-      <c r="DL3" s="41"/>
-      <c r="DM3" s="41"/>
-      <c r="DN3" s="41"/>
-      <c r="DO3" s="41"/>
-      <c r="DP3" s="41"/>
-      <c r="DQ3" s="41"/>
-      <c r="DR3" s="41"/>
-      <c r="DS3" s="41"/>
-      <c r="DT3" s="41"/>
-      <c r="DU3" s="41"/>
-      <c r="DV3" s="41"/>
-      <c r="DW3" s="41"/>
-      <c r="DX3" s="41"/>
-      <c r="DY3" s="41"/>
-      <c r="DZ3" s="41"/>
-      <c r="EA3" s="41"/>
-      <c r="EB3" s="41"/>
-      <c r="EC3" s="41"/>
-      <c r="ED3" s="41"/>
-      <c r="EE3" s="41"/>
-      <c r="EF3" s="41"/>
-      <c r="EG3" s="41"/>
-      <c r="EH3" s="41"/>
-      <c r="EI3" s="41"/>
-      <c r="EJ3" s="41"/>
-      <c r="EK3" s="41"/>
-      <c r="EL3" s="41"/>
-      <c r="EM3" s="41"/>
-      <c r="EN3" s="41"/>
-      <c r="EO3" s="41"/>
-      <c r="EP3" s="41"/>
-      <c r="EQ3" s="41"/>
-      <c r="ER3" s="41"/>
-      <c r="ES3" s="41"/>
-      <c r="ET3" s="41"/>
-      <c r="EU3" s="41"/>
-      <c r="EV3" s="41"/>
-      <c r="EW3" s="41"/>
-      <c r="EX3" s="41"/>
-      <c r="EY3" s="41"/>
+      <c r="AW3" s="37"/>
+      <c r="AX3" s="37"/>
+      <c r="AY3" s="37"/>
+      <c r="AZ3" s="37"/>
+      <c r="BA3" s="37"/>
+      <c r="BB3" s="37"/>
+      <c r="BC3" s="37"/>
+      <c r="BD3" s="37"/>
+      <c r="BE3" s="37"/>
+      <c r="BF3" s="37"/>
+      <c r="BG3" s="37"/>
+      <c r="BH3" s="37"/>
+      <c r="BI3" s="37"/>
+      <c r="BJ3" s="37"/>
+      <c r="BK3" s="37"/>
+      <c r="BL3" s="37"/>
+      <c r="BM3" s="37"/>
+      <c r="BN3" s="37"/>
+      <c r="BO3" s="37"/>
+      <c r="BP3" s="37"/>
+      <c r="BQ3" s="37"/>
+      <c r="BR3" s="37"/>
+      <c r="BS3" s="37"/>
+      <c r="BT3" s="37"/>
+      <c r="BU3" s="37"/>
+      <c r="BV3" s="37"/>
+      <c r="BW3" s="37"/>
+      <c r="BX3" s="37"/>
+      <c r="BY3" s="37"/>
+      <c r="BZ3" s="37"/>
+      <c r="CA3" s="37"/>
+      <c r="CB3" s="37"/>
+      <c r="CC3" s="37"/>
+      <c r="CD3" s="37"/>
+      <c r="CE3" s="37"/>
+      <c r="CF3" s="37"/>
+      <c r="CG3" s="37"/>
+      <c r="CH3" s="37"/>
+      <c r="CI3" s="37"/>
+      <c r="CJ3" s="37"/>
+      <c r="CK3" s="37"/>
+      <c r="CL3" s="37"/>
+      <c r="CM3" s="37"/>
+      <c r="CN3" s="37"/>
+      <c r="CO3" s="37"/>
+      <c r="CP3" s="37"/>
+      <c r="CQ3" s="37"/>
+      <c r="CR3" s="37"/>
+      <c r="CS3" s="37"/>
+      <c r="CT3" s="37"/>
+      <c r="CU3" s="37"/>
+      <c r="CV3" s="37"/>
+      <c r="CW3" s="37"/>
+      <c r="CX3" s="37"/>
+      <c r="CY3" s="37"/>
+      <c r="CZ3" s="37"/>
+      <c r="DA3" s="37"/>
+      <c r="DB3" s="37"/>
+      <c r="DC3" s="37"/>
+      <c r="DD3" s="37"/>
+      <c r="DE3" s="37"/>
+      <c r="DF3" s="37"/>
+      <c r="DG3" s="37"/>
+      <c r="DH3" s="37"/>
+      <c r="DI3" s="37"/>
+      <c r="DJ3" s="37"/>
+      <c r="DK3" s="37"/>
+      <c r="DL3" s="37"/>
+      <c r="DM3" s="37"/>
+      <c r="DN3" s="37"/>
+      <c r="DO3" s="37"/>
+      <c r="DP3" s="37"/>
+      <c r="DQ3" s="37"/>
+      <c r="DR3" s="37"/>
+      <c r="DS3" s="37"/>
+      <c r="DT3" s="37"/>
+      <c r="DU3" s="37"/>
+      <c r="DV3" s="37"/>
+      <c r="DW3" s="37"/>
+      <c r="DX3" s="37"/>
+      <c r="DY3" s="37"/>
+      <c r="DZ3" s="37"/>
+      <c r="EA3" s="37"/>
+      <c r="EB3" s="37"/>
+      <c r="EC3" s="37"/>
+      <c r="ED3" s="37"/>
+      <c r="EE3" s="37"/>
+      <c r="EF3" s="37"/>
+      <c r="EG3" s="37"/>
+      <c r="EH3" s="37"/>
+      <c r="EI3" s="37"/>
+      <c r="EJ3" s="37"/>
+      <c r="EK3" s="37"/>
+      <c r="EL3" s="37"/>
+      <c r="EM3" s="37"/>
+      <c r="EN3" s="37"/>
+      <c r="EO3" s="37"/>
+      <c r="EP3" s="37"/>
+      <c r="EQ3" s="37"/>
+      <c r="ER3" s="37"/>
+      <c r="ES3" s="37"/>
+      <c r="ET3" s="37"/>
+      <c r="EU3" s="37"/>
+      <c r="EV3" s="37"/>
+      <c r="EW3" s="37"/>
+      <c r="EX3" s="37"/>
+      <c r="EY3" s="37"/>
     </row>
     <row r="4" spans="2:155" x14ac:dyDescent="0.2">
-      <c r="B4" s="36" t="s">
-        <v>300</v>
-      </c>
-      <c r="C4" s="39">
+      <c r="B4" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="C4" s="35">
         <v>-27000</v>
       </c>
-      <c r="D4" s="39">
+      <c r="D4" s="35">
         <f>C4*4</f>
         <v>-108000</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="36">
         <v>46249</v>
       </c>
-      <c r="F4" s="39">
+      <c r="F4" s="35">
         <v>250</v>
       </c>
-      <c r="G4" s="41">
+      <c r="G4" s="37">
         <v>37359</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="37">
         <v>47034</v>
       </c>
-      <c r="I4" s="41">
+      <c r="I4" s="37">
         <v>57303</v>
       </c>
-      <c r="J4" s="41">
+      <c r="J4" s="37">
         <v>48159</v>
       </c>
-      <c r="K4" s="41">
+      <c r="K4" s="37">
         <v>51913</v>
       </c>
-      <c r="L4" s="41">
+      <c r="L4" s="37">
         <v>51412</v>
       </c>
-      <c r="M4" s="41">
+      <c r="M4" s="37">
         <v>51248</v>
       </c>
-      <c r="N4" s="41">
+      <c r="N4" s="37">
         <v>52583</v>
       </c>
-      <c r="O4" s="41">
+      <c r="O4" s="37">
         <v>52300</v>
       </c>
-      <c r="P4" s="41">
+      <c r="P4" s="37">
         <v>54350</v>
       </c>
-      <c r="Q4" s="41">
+      <c r="Q4" s="37">
         <v>54350</v>
       </c>
-      <c r="R4" s="41">
+      <c r="R4" s="37">
         <v>55860</v>
       </c>
-      <c r="S4" s="41">
+      <c r="S4" s="37">
         <v>53317</v>
       </c>
-      <c r="T4" s="41">
+      <c r="T4" s="37">
         <v>54350</v>
       </c>
-      <c r="U4" s="41">
+      <c r="U4" s="37">
         <v>54350</v>
       </c>
-      <c r="V4" s="41">
+      <c r="V4" s="37">
         <v>58954</v>
       </c>
-      <c r="W4" s="41">
+      <c r="W4" s="37">
         <v>54350</v>
       </c>
-      <c r="X4" s="41">
+      <c r="X4" s="37">
         <v>54350</v>
       </c>
-      <c r="Y4" s="41">
+      <c r="Y4" s="37">
         <v>62480</v>
       </c>
-      <c r="Z4" s="41">
+      <c r="Z4" s="37">
         <v>54350</v>
       </c>
-      <c r="AA4" s="41">
+      <c r="AA4" s="37">
         <v>65757</v>
       </c>
-      <c r="AB4" s="41">
+      <c r="AB4" s="37">
         <v>65757</v>
       </c>
-      <c r="AC4" s="41">
+      <c r="AC4" s="37">
         <v>65757</v>
       </c>
-      <c r="AD4" s="41">
+      <c r="AD4" s="37">
         <v>65757</v>
       </c>
-      <c r="AE4" s="41">
+      <c r="AE4" s="37">
         <v>70785</v>
       </c>
-      <c r="AF4" s="41">
+      <c r="AF4" s="37">
         <v>71420</v>
       </c>
-      <c r="AG4" s="41">
+      <c r="AG4" s="37">
         <v>71420</v>
       </c>
-      <c r="AH4" s="41">
+      <c r="AH4" s="37">
         <v>70072</v>
       </c>
-      <c r="AI4" s="41">
+      <c r="AI4" s="37">
         <v>72615</v>
       </c>
-      <c r="AJ4" s="41">
+      <c r="AJ4" s="37">
         <v>72665</v>
       </c>
-      <c r="AK4" s="41">
+      <c r="AK4" s="37">
         <v>70611</v>
       </c>
-      <c r="AL4" s="41">
+      <c r="AL4" s="37">
         <v>71644</v>
       </c>
-      <c r="AM4" s="41">
+      <c r="AM4" s="37">
         <v>75224</v>
       </c>
-      <c r="AN4" s="41">
+      <c r="AN4" s="37">
         <v>78907</v>
       </c>
-      <c r="AO4" s="41">
+      <c r="AO4" s="37">
         <v>77475</v>
       </c>
-      <c r="AP4" s="41">
+      <c r="AP4" s="37">
         <v>81472</v>
       </c>
-      <c r="AQ4" s="41">
+      <c r="AQ4" s="37">
         <v>84114</v>
       </c>
-      <c r="AR4" s="41">
+      <c r="AR4" s="37">
         <v>85950</v>
       </c>
-      <c r="AS4" s="41">
+      <c r="AS4" s="37">
         <v>86438</v>
       </c>
-      <c r="AT4" s="41">
+      <c r="AT4" s="37">
         <v>87649</v>
       </c>
-      <c r="AU4" s="41">
+      <c r="AU4" s="37">
         <v>87853</v>
       </c>
-      <c r="AV4" s="41">
+      <c r="AV4" s="37">
         <v>89506</v>
       </c>
-      <c r="AW4" s="41"/>
-      <c r="AX4" s="41"/>
-      <c r="AY4" s="41"/>
-      <c r="AZ4" s="41"/>
-      <c r="BA4" s="41"/>
-      <c r="BB4" s="41"/>
-      <c r="BC4" s="41"/>
-      <c r="BD4" s="41"/>
-      <c r="BE4" s="41"/>
-      <c r="BF4" s="41"/>
-      <c r="BG4" s="41"/>
-      <c r="BH4" s="41"/>
-      <c r="BI4" s="41"/>
-      <c r="BJ4" s="41"/>
-      <c r="BK4" s="41"/>
-      <c r="BL4" s="41"/>
-      <c r="BM4" s="41"/>
-      <c r="BN4" s="41"/>
-      <c r="BO4" s="41"/>
-      <c r="BP4" s="41"/>
-      <c r="BQ4" s="41"/>
-      <c r="BR4" s="41"/>
-      <c r="BS4" s="41"/>
-      <c r="BT4" s="41"/>
-      <c r="BU4" s="41"/>
-      <c r="BV4" s="41"/>
-      <c r="BW4" s="41"/>
-      <c r="BX4" s="41"/>
-      <c r="BY4" s="41"/>
-      <c r="BZ4" s="41"/>
-      <c r="CA4" s="41"/>
-      <c r="CB4" s="41"/>
-      <c r="CC4" s="41"/>
-      <c r="CD4" s="41"/>
-      <c r="CE4" s="41"/>
-      <c r="CF4" s="41"/>
-      <c r="CG4" s="41"/>
-      <c r="CH4" s="41"/>
-      <c r="CI4" s="41"/>
-      <c r="CJ4" s="41"/>
-      <c r="CK4" s="41"/>
-      <c r="CL4" s="41"/>
-      <c r="CM4" s="41"/>
-      <c r="CN4" s="41"/>
-      <c r="CO4" s="41"/>
-      <c r="CP4" s="41"/>
-      <c r="CQ4" s="41"/>
-      <c r="CR4" s="41"/>
-      <c r="CS4" s="41"/>
-      <c r="CT4" s="41"/>
-      <c r="CU4" s="41"/>
-      <c r="CV4" s="41"/>
-      <c r="CW4" s="41"/>
-      <c r="CX4" s="41"/>
-      <c r="CY4" s="41"/>
-      <c r="CZ4" s="41"/>
-      <c r="DA4" s="41"/>
-      <c r="DB4" s="41"/>
-      <c r="DC4" s="41"/>
-      <c r="DD4" s="41"/>
-      <c r="DE4" s="41"/>
-      <c r="DF4" s="41"/>
-      <c r="DG4" s="41"/>
-      <c r="DH4" s="41"/>
-      <c r="DI4" s="41"/>
-      <c r="DJ4" s="41"/>
-      <c r="DK4" s="41"/>
-      <c r="DL4" s="41"/>
-      <c r="DM4" s="41"/>
-      <c r="DN4" s="41"/>
-      <c r="DO4" s="41"/>
-      <c r="DP4" s="41"/>
-      <c r="DQ4" s="41"/>
-      <c r="DR4" s="41"/>
-      <c r="DS4" s="41"/>
-      <c r="DT4" s="41"/>
-      <c r="DU4" s="41"/>
-      <c r="DV4" s="41"/>
-      <c r="DW4" s="41"/>
-      <c r="DX4" s="41"/>
-      <c r="DY4" s="41"/>
-      <c r="DZ4" s="41"/>
-      <c r="EA4" s="41"/>
-      <c r="EB4" s="41"/>
-      <c r="EC4" s="41"/>
-      <c r="ED4" s="41"/>
-      <c r="EE4" s="41"/>
-      <c r="EF4" s="41"/>
-      <c r="EG4" s="41"/>
-      <c r="EH4" s="41"/>
-      <c r="EI4" s="41"/>
-      <c r="EJ4" s="41"/>
-      <c r="EK4" s="41"/>
-      <c r="EL4" s="41"/>
-      <c r="EM4" s="41"/>
-      <c r="EN4" s="41"/>
-      <c r="EO4" s="41"/>
-      <c r="EP4" s="41"/>
-      <c r="EQ4" s="41"/>
-      <c r="ER4" s="41"/>
-      <c r="ES4" s="41"/>
-      <c r="ET4" s="41"/>
-      <c r="EU4" s="41"/>
-      <c r="EV4" s="41"/>
-      <c r="EW4" s="41"/>
-      <c r="EX4" s="41"/>
-      <c r="EY4" s="41"/>
+      <c r="AW4" s="37"/>
+      <c r="AX4" s="37"/>
+      <c r="AY4" s="37"/>
+      <c r="AZ4" s="37"/>
+      <c r="BA4" s="37"/>
+      <c r="BB4" s="37"/>
+      <c r="BC4" s="37"/>
+      <c r="BD4" s="37"/>
+      <c r="BE4" s="37"/>
+      <c r="BF4" s="37"/>
+      <c r="BG4" s="37"/>
+      <c r="BH4" s="37"/>
+      <c r="BI4" s="37"/>
+      <c r="BJ4" s="37"/>
+      <c r="BK4" s="37"/>
+      <c r="BL4" s="37"/>
+      <c r="BM4" s="37"/>
+      <c r="BN4" s="37"/>
+      <c r="BO4" s="37"/>
+      <c r="BP4" s="37"/>
+      <c r="BQ4" s="37"/>
+      <c r="BR4" s="37"/>
+      <c r="BS4" s="37"/>
+      <c r="BT4" s="37"/>
+      <c r="BU4" s="37"/>
+      <c r="BV4" s="37"/>
+      <c r="BW4" s="37"/>
+      <c r="BX4" s="37"/>
+      <c r="BY4" s="37"/>
+      <c r="BZ4" s="37"/>
+      <c r="CA4" s="37"/>
+      <c r="CB4" s="37"/>
+      <c r="CC4" s="37"/>
+      <c r="CD4" s="37"/>
+      <c r="CE4" s="37"/>
+      <c r="CF4" s="37"/>
+      <c r="CG4" s="37"/>
+      <c r="CH4" s="37"/>
+      <c r="CI4" s="37"/>
+      <c r="CJ4" s="37"/>
+      <c r="CK4" s="37"/>
+      <c r="CL4" s="37"/>
+      <c r="CM4" s="37"/>
+      <c r="CN4" s="37"/>
+      <c r="CO4" s="37"/>
+      <c r="CP4" s="37"/>
+      <c r="CQ4" s="37"/>
+      <c r="CR4" s="37"/>
+      <c r="CS4" s="37"/>
+      <c r="CT4" s="37"/>
+      <c r="CU4" s="37"/>
+      <c r="CV4" s="37"/>
+      <c r="CW4" s="37"/>
+      <c r="CX4" s="37"/>
+      <c r="CY4" s="37"/>
+      <c r="CZ4" s="37"/>
+      <c r="DA4" s="37"/>
+      <c r="DB4" s="37"/>
+      <c r="DC4" s="37"/>
+      <c r="DD4" s="37"/>
+      <c r="DE4" s="37"/>
+      <c r="DF4" s="37"/>
+      <c r="DG4" s="37"/>
+      <c r="DH4" s="37"/>
+      <c r="DI4" s="37"/>
+      <c r="DJ4" s="37"/>
+      <c r="DK4" s="37"/>
+      <c r="DL4" s="37"/>
+      <c r="DM4" s="37"/>
+      <c r="DN4" s="37"/>
+      <c r="DO4" s="37"/>
+      <c r="DP4" s="37"/>
+      <c r="DQ4" s="37"/>
+      <c r="DR4" s="37"/>
+      <c r="DS4" s="37"/>
+      <c r="DT4" s="37"/>
+      <c r="DU4" s="37"/>
+      <c r="DV4" s="37"/>
+      <c r="DW4" s="37"/>
+      <c r="DX4" s="37"/>
+      <c r="DY4" s="37"/>
+      <c r="DZ4" s="37"/>
+      <c r="EA4" s="37"/>
+      <c r="EB4" s="37"/>
+      <c r="EC4" s="37"/>
+      <c r="ED4" s="37"/>
+      <c r="EE4" s="37"/>
+      <c r="EF4" s="37"/>
+      <c r="EG4" s="37"/>
+      <c r="EH4" s="37"/>
+      <c r="EI4" s="37"/>
+      <c r="EJ4" s="37"/>
+      <c r="EK4" s="37"/>
+      <c r="EL4" s="37"/>
+      <c r="EM4" s="37"/>
+      <c r="EN4" s="37"/>
+      <c r="EO4" s="37"/>
+      <c r="EP4" s="37"/>
+      <c r="EQ4" s="37"/>
+      <c r="ER4" s="37"/>
+      <c r="ES4" s="37"/>
+      <c r="ET4" s="37"/>
+      <c r="EU4" s="37"/>
+      <c r="EV4" s="37"/>
+      <c r="EW4" s="37"/>
+      <c r="EX4" s="37"/>
+      <c r="EY4" s="37"/>
     </row>
     <row r="5" spans="2:155" x14ac:dyDescent="0.2">
-      <c r="B5" s="36" t="s">
-        <v>301</v>
-      </c>
-      <c r="C5" s="39">
+      <c r="B5" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="C5" s="35">
         <v>-30000</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="35">
         <f>C5*4</f>
         <v>-120000</v>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="36">
         <v>48075</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="35">
         <v>100</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="37">
         <v>26592</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="37">
         <v>30603</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="37">
         <v>39149</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="37">
         <v>33091</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="37">
         <v>35475</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="37">
         <v>35278</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="37">
         <v>35332</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="37">
         <v>36383</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="37">
         <v>36565</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="37">
         <v>38219</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="37">
         <v>38219</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="37">
         <v>41449</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="37">
         <v>39640</v>
       </c>
-      <c r="T5" s="41">
+      <c r="T5" s="37">
         <v>38219</v>
       </c>
-      <c r="U5" s="41">
+      <c r="U5" s="37">
         <v>38219</v>
       </c>
-      <c r="V5" s="41">
+      <c r="V5" s="37">
         <v>44224</v>
       </c>
-      <c r="W5" s="41">
+      <c r="W5" s="37">
         <v>38219</v>
       </c>
-      <c r="X5" s="41">
+      <c r="X5" s="37">
         <v>38219</v>
       </c>
-      <c r="Y5" s="41">
+      <c r="Y5" s="37">
         <v>47525</v>
       </c>
-      <c r="Z5" s="41">
+      <c r="Z5" s="37">
         <v>38219</v>
       </c>
-      <c r="AA5" s="41">
+      <c r="AA5" s="37">
         <v>50514</v>
       </c>
-      <c r="AB5" s="41">
+      <c r="AB5" s="37">
         <v>50514</v>
       </c>
-      <c r="AC5" s="41">
+      <c r="AC5" s="37">
         <v>50514</v>
       </c>
-      <c r="AD5" s="41">
+      <c r="AD5" s="37">
         <v>50514</v>
       </c>
-      <c r="AE5" s="41">
+      <c r="AE5" s="37">
         <v>53978</v>
       </c>
-      <c r="AF5" s="41">
+      <c r="AF5" s="37">
         <v>55548</v>
       </c>
-      <c r="AG5" s="41">
+      <c r="AG5" s="37">
         <v>55548</v>
       </c>
-      <c r="AH5" s="41">
+      <c r="AH5" s="37">
         <v>54507</v>
       </c>
-      <c r="AI5" s="41">
+      <c r="AI5" s="37">
         <v>56132</v>
       </c>
-      <c r="AJ5" s="41">
+      <c r="AJ5" s="37">
         <v>55662</v>
       </c>
-      <c r="AK5" s="41">
+      <c r="AK5" s="37">
         <v>53208</v>
       </c>
-      <c r="AL5" s="41">
+      <c r="AL5" s="37">
         <v>53296</v>
       </c>
-      <c r="AM5" s="41">
+      <c r="AM5" s="37">
         <v>56454</v>
       </c>
-      <c r="AN5" s="41">
+      <c r="AN5" s="37">
         <v>59146</v>
       </c>
-      <c r="AO5" s="41">
+      <c r="AO5" s="37">
         <v>59242</v>
       </c>
-      <c r="AP5" s="41">
+      <c r="AP5" s="37">
         <v>61879</v>
       </c>
-      <c r="AQ5" s="41">
+      <c r="AQ5" s="37">
         <v>64101</v>
       </c>
-      <c r="AR5" s="41">
+      <c r="AR5" s="37">
         <v>65423</v>
       </c>
-      <c r="AS5" s="41">
+      <c r="AS5" s="37">
         <v>65687</v>
       </c>
-      <c r="AT5" s="41">
+      <c r="AT5" s="37">
         <v>66167</v>
       </c>
-      <c r="AU5" s="41">
+      <c r="AU5" s="37">
         <v>67892</v>
       </c>
-      <c r="AV5" s="41">
+      <c r="AV5" s="37">
         <v>68487</v>
       </c>
-      <c r="AW5" s="41"/>
-      <c r="AX5" s="41"/>
-      <c r="AY5" s="41"/>
-      <c r="AZ5" s="41"/>
-      <c r="BA5" s="41"/>
-      <c r="BB5" s="41"/>
-      <c r="BC5" s="41"/>
-      <c r="BD5" s="41"/>
-      <c r="BE5" s="41"/>
-      <c r="BF5" s="41"/>
-      <c r="BG5" s="41"/>
-      <c r="BH5" s="41"/>
-      <c r="BI5" s="41"/>
-      <c r="BJ5" s="41"/>
-      <c r="BK5" s="41"/>
-      <c r="BL5" s="41"/>
-      <c r="BM5" s="41"/>
-      <c r="BN5" s="41"/>
-      <c r="BO5" s="41"/>
-      <c r="BP5" s="41"/>
-      <c r="BQ5" s="41"/>
-      <c r="BR5" s="41"/>
-      <c r="BS5" s="41"/>
-      <c r="BT5" s="41"/>
-      <c r="BU5" s="41"/>
-      <c r="BV5" s="41"/>
-      <c r="BW5" s="41"/>
-      <c r="BX5" s="41"/>
-      <c r="BY5" s="41"/>
-      <c r="BZ5" s="41"/>
-      <c r="CA5" s="41"/>
-      <c r="CB5" s="41"/>
-      <c r="CC5" s="41"/>
-      <c r="CD5" s="41"/>
-      <c r="CE5" s="41"/>
-      <c r="CF5" s="41"/>
-      <c r="CG5" s="41"/>
-      <c r="CH5" s="41"/>
-      <c r="CI5" s="41"/>
-      <c r="CJ5" s="41"/>
-      <c r="CK5" s="41"/>
-      <c r="CL5" s="41"/>
-      <c r="CM5" s="41"/>
-      <c r="CN5" s="41"/>
-      <c r="CO5" s="41"/>
-      <c r="CP5" s="41"/>
-      <c r="CQ5" s="41"/>
-      <c r="CR5" s="41"/>
-      <c r="CS5" s="41"/>
-      <c r="CT5" s="41"/>
-      <c r="CU5" s="41"/>
-      <c r="CV5" s="41"/>
-      <c r="CW5" s="41"/>
-      <c r="CX5" s="41"/>
-      <c r="CY5" s="41"/>
-      <c r="CZ5" s="41"/>
-      <c r="DA5" s="41"/>
-      <c r="DB5" s="41"/>
-      <c r="DC5" s="41"/>
-      <c r="DD5" s="41"/>
-      <c r="DE5" s="41"/>
-      <c r="DF5" s="41"/>
-      <c r="DG5" s="41"/>
-      <c r="DH5" s="41"/>
-      <c r="DI5" s="41"/>
-      <c r="DJ5" s="41"/>
-      <c r="DK5" s="41"/>
-      <c r="DL5" s="41"/>
-      <c r="DM5" s="41"/>
-      <c r="DN5" s="41"/>
-      <c r="DO5" s="41"/>
-      <c r="DP5" s="41"/>
-      <c r="DQ5" s="41"/>
-      <c r="DR5" s="41"/>
-      <c r="DS5" s="41"/>
-      <c r="DT5" s="41"/>
-      <c r="DU5" s="41"/>
-      <c r="DV5" s="41"/>
-      <c r="DW5" s="41"/>
-      <c r="DX5" s="41"/>
-      <c r="DY5" s="41"/>
-      <c r="DZ5" s="41"/>
-      <c r="EA5" s="41"/>
-      <c r="EB5" s="41"/>
-      <c r="EC5" s="41"/>
-      <c r="ED5" s="41"/>
-      <c r="EE5" s="41"/>
-      <c r="EF5" s="41"/>
-      <c r="EG5" s="41"/>
-      <c r="EH5" s="41"/>
-      <c r="EI5" s="41"/>
-      <c r="EJ5" s="41"/>
-      <c r="EK5" s="41"/>
-      <c r="EL5" s="41"/>
-      <c r="EM5" s="41"/>
-      <c r="EN5" s="41"/>
-      <c r="EO5" s="41"/>
-      <c r="EP5" s="41"/>
-      <c r="EQ5" s="41"/>
-      <c r="ER5" s="41"/>
-      <c r="ES5" s="41"/>
-      <c r="ET5" s="41"/>
-      <c r="EU5" s="41"/>
-      <c r="EV5" s="41"/>
-      <c r="EW5" s="41"/>
-      <c r="EX5" s="41"/>
-      <c r="EY5" s="36"/>
+      <c r="AW5" s="37"/>
+      <c r="AX5" s="37"/>
+      <c r="AY5" s="37"/>
+      <c r="AZ5" s="37"/>
+      <c r="BA5" s="37"/>
+      <c r="BB5" s="37"/>
+      <c r="BC5" s="37"/>
+      <c r="BD5" s="37"/>
+      <c r="BE5" s="37"/>
+      <c r="BF5" s="37"/>
+      <c r="BG5" s="37"/>
+      <c r="BH5" s="37"/>
+      <c r="BI5" s="37"/>
+      <c r="BJ5" s="37"/>
+      <c r="BK5" s="37"/>
+      <c r="BL5" s="37"/>
+      <c r="BM5" s="37"/>
+      <c r="BN5" s="37"/>
+      <c r="BO5" s="37"/>
+      <c r="BP5" s="37"/>
+      <c r="BQ5" s="37"/>
+      <c r="BR5" s="37"/>
+      <c r="BS5" s="37"/>
+      <c r="BT5" s="37"/>
+      <c r="BU5" s="37"/>
+      <c r="BV5" s="37"/>
+      <c r="BW5" s="37"/>
+      <c r="BX5" s="37"/>
+      <c r="BY5" s="37"/>
+      <c r="BZ5" s="37"/>
+      <c r="CA5" s="37"/>
+      <c r="CB5" s="37"/>
+      <c r="CC5" s="37"/>
+      <c r="CD5" s="37"/>
+      <c r="CE5" s="37"/>
+      <c r="CF5" s="37"/>
+      <c r="CG5" s="37"/>
+      <c r="CH5" s="37"/>
+      <c r="CI5" s="37"/>
+      <c r="CJ5" s="37"/>
+      <c r="CK5" s="37"/>
+      <c r="CL5" s="37"/>
+      <c r="CM5" s="37"/>
+      <c r="CN5" s="37"/>
+      <c r="CO5" s="37"/>
+      <c r="CP5" s="37"/>
+      <c r="CQ5" s="37"/>
+      <c r="CR5" s="37"/>
+      <c r="CS5" s="37"/>
+      <c r="CT5" s="37"/>
+      <c r="CU5" s="37"/>
+      <c r="CV5" s="37"/>
+      <c r="CW5" s="37"/>
+      <c r="CX5" s="37"/>
+      <c r="CY5" s="37"/>
+      <c r="CZ5" s="37"/>
+      <c r="DA5" s="37"/>
+      <c r="DB5" s="37"/>
+      <c r="DC5" s="37"/>
+      <c r="DD5" s="37"/>
+      <c r="DE5" s="37"/>
+      <c r="DF5" s="37"/>
+      <c r="DG5" s="37"/>
+      <c r="DH5" s="37"/>
+      <c r="DI5" s="37"/>
+      <c r="DJ5" s="37"/>
+      <c r="DK5" s="37"/>
+      <c r="DL5" s="37"/>
+      <c r="DM5" s="37"/>
+      <c r="DN5" s="37"/>
+      <c r="DO5" s="37"/>
+      <c r="DP5" s="37"/>
+      <c r="DQ5" s="37"/>
+      <c r="DR5" s="37"/>
+      <c r="DS5" s="37"/>
+      <c r="DT5" s="37"/>
+      <c r="DU5" s="37"/>
+      <c r="DV5" s="37"/>
+      <c r="DW5" s="37"/>
+      <c r="DX5" s="37"/>
+      <c r="DY5" s="37"/>
+      <c r="DZ5" s="37"/>
+      <c r="EA5" s="37"/>
+      <c r="EB5" s="37"/>
+      <c r="EC5" s="37"/>
+      <c r="ED5" s="37"/>
+      <c r="EE5" s="37"/>
+      <c r="EF5" s="37"/>
+      <c r="EG5" s="37"/>
+      <c r="EH5" s="37"/>
+      <c r="EI5" s="37"/>
+      <c r="EJ5" s="37"/>
+      <c r="EK5" s="37"/>
+      <c r="EL5" s="37"/>
+      <c r="EM5" s="37"/>
+      <c r="EN5" s="37"/>
+      <c r="EO5" s="37"/>
+      <c r="EP5" s="37"/>
+      <c r="EQ5" s="37"/>
+      <c r="ER5" s="37"/>
+      <c r="ES5" s="37"/>
+      <c r="ET5" s="37"/>
+      <c r="EU5" s="37"/>
+      <c r="EV5" s="37"/>
+      <c r="EW5" s="37"/>
+      <c r="EX5" s="37"/>
+      <c r="EY5" s="32"/>
     </row>
     <row r="6" spans="2:155" x14ac:dyDescent="0.2">
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="36"/>
-      <c r="AB6" s="36"/>
-      <c r="AC6" s="36"/>
-      <c r="AD6" s="36"/>
-      <c r="AE6" s="36"/>
-      <c r="AF6" s="36"/>
-      <c r="AG6" s="36"/>
-      <c r="AH6" s="36"/>
-      <c r="AI6" s="36"/>
-      <c r="AJ6" s="36"/>
-      <c r="AK6" s="36"/>
-      <c r="AL6" s="36"/>
-      <c r="AM6" s="36"/>
-      <c r="AN6" s="36"/>
-      <c r="AO6" s="36"/>
-      <c r="AP6" s="36"/>
-      <c r="AQ6" s="36"/>
-      <c r="AR6" s="36"/>
-      <c r="AS6" s="36"/>
-      <c r="AT6" s="36"/>
-      <c r="AU6" s="36"/>
-      <c r="AV6" s="36"/>
-      <c r="AW6" s="36"/>
-      <c r="AX6" s="36"/>
-      <c r="AY6" s="36"/>
-      <c r="AZ6" s="36"/>
-      <c r="BA6" s="36"/>
-      <c r="BB6" s="36"/>
-      <c r="BC6" s="36"/>
-      <c r="BD6" s="36"/>
-      <c r="BE6" s="36"/>
-      <c r="BF6" s="36"/>
-      <c r="BG6" s="36"/>
-      <c r="BH6" s="36"/>
-      <c r="BI6" s="36"/>
-      <c r="BJ6" s="36"/>
-      <c r="BK6" s="36"/>
-      <c r="BL6" s="36"/>
-      <c r="BM6" s="36"/>
-      <c r="BN6" s="36"/>
-      <c r="BO6" s="36"/>
-      <c r="BP6" s="36"/>
-      <c r="BQ6" s="36"/>
-      <c r="BR6" s="36"/>
-      <c r="BS6" s="36"/>
-      <c r="BT6" s="36"/>
-      <c r="BU6" s="36"/>
-      <c r="BV6" s="36"/>
-      <c r="BW6" s="36"/>
-      <c r="BX6" s="36"/>
-      <c r="BY6" s="36"/>
-      <c r="BZ6" s="36"/>
-      <c r="CA6" s="36"/>
-      <c r="CB6" s="36"/>
-      <c r="CC6" s="36"/>
-      <c r="CD6" s="36"/>
-      <c r="CE6" s="36"/>
-      <c r="CF6" s="36"/>
-      <c r="CG6" s="36"/>
-      <c r="CH6" s="36"/>
-      <c r="CI6" s="36"/>
-      <c r="CJ6" s="36"/>
-      <c r="CK6" s="36"/>
-      <c r="CL6" s="36"/>
-      <c r="CM6" s="36"/>
-      <c r="CN6" s="36"/>
-      <c r="CO6" s="36"/>
-      <c r="CP6" s="36"/>
-      <c r="CQ6" s="36"/>
-      <c r="CR6" s="36"/>
-      <c r="CS6" s="36"/>
-      <c r="CT6" s="36"/>
-      <c r="CU6" s="36"/>
-      <c r="CV6" s="36"/>
-      <c r="CW6" s="36"/>
-      <c r="CX6" s="36"/>
-      <c r="CY6" s="36"/>
-      <c r="CZ6" s="36"/>
-      <c r="DA6" s="36"/>
-      <c r="DB6" s="36"/>
-      <c r="DC6" s="36"/>
-      <c r="DD6" s="36"/>
-      <c r="DE6" s="36"/>
-      <c r="DF6" s="36"/>
-      <c r="DG6" s="36"/>
-      <c r="DH6" s="36"/>
-      <c r="DI6" s="36"/>
-      <c r="DJ6" s="36"/>
-      <c r="DK6" s="36"/>
-      <c r="DL6" s="36"/>
-      <c r="DM6" s="36"/>
-      <c r="DN6" s="36"/>
-      <c r="DO6" s="36"/>
-      <c r="DP6" s="36"/>
-      <c r="DQ6" s="36"/>
-      <c r="DR6" s="36"/>
-      <c r="DS6" s="36"/>
-      <c r="DT6" s="36"/>
-      <c r="DU6" s="36"/>
-      <c r="DV6" s="36"/>
-      <c r="DW6" s="36"/>
-      <c r="DX6" s="36"/>
-      <c r="DY6" s="36"/>
-      <c r="DZ6" s="36"/>
-      <c r="EA6" s="36"/>
-      <c r="EB6" s="36"/>
-      <c r="EC6" s="36"/>
-      <c r="ED6" s="36"/>
-      <c r="EE6" s="36"/>
-      <c r="EF6" s="36"/>
-      <c r="EG6" s="36"/>
-      <c r="EH6" s="36"/>
-      <c r="EI6" s="36"/>
-      <c r="EJ6" s="36"/>
-      <c r="EK6" s="36"/>
-      <c r="EL6" s="36"/>
-      <c r="EM6" s="36"/>
-      <c r="EN6" s="36"/>
-      <c r="EO6" s="36"/>
-      <c r="EP6" s="36"/>
-      <c r="EQ6" s="36"/>
-      <c r="ER6" s="36"/>
-      <c r="ES6" s="36"/>
-      <c r="ET6" s="36"/>
-      <c r="EU6" s="36"/>
-      <c r="EV6" s="36"/>
-      <c r="EW6" s="36"/>
-      <c r="EX6" s="36"/>
-      <c r="EY6" s="36"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="32"/>
+      <c r="AE6" s="32"/>
+      <c r="AF6" s="32"/>
+      <c r="AG6" s="32"/>
+      <c r="AH6" s="32"/>
+      <c r="AI6" s="32"/>
+      <c r="AJ6" s="32"/>
+      <c r="AK6" s="32"/>
+      <c r="AL6" s="32"/>
+      <c r="AM6" s="32"/>
+      <c r="AN6" s="32"/>
+      <c r="AO6" s="32"/>
+      <c r="AP6" s="32"/>
+      <c r="AQ6" s="32"/>
+      <c r="AR6" s="32"/>
+      <c r="AS6" s="32"/>
+      <c r="AT6" s="32"/>
+      <c r="AU6" s="32"/>
+      <c r="AV6" s="32"/>
+      <c r="AW6" s="32"/>
+      <c r="AX6" s="32"/>
+      <c r="AY6" s="32"/>
+      <c r="AZ6" s="32"/>
+      <c r="BA6" s="32"/>
+      <c r="BB6" s="32"/>
+      <c r="BC6" s="32"/>
+      <c r="BD6" s="32"/>
+      <c r="BE6" s="32"/>
+      <c r="BF6" s="32"/>
+      <c r="BG6" s="32"/>
+      <c r="BH6" s="32"/>
+      <c r="BI6" s="32"/>
+      <c r="BJ6" s="32"/>
+      <c r="BK6" s="32"/>
+      <c r="BL6" s="32"/>
+      <c r="BM6" s="32"/>
+      <c r="BN6" s="32"/>
+      <c r="BO6" s="32"/>
+      <c r="BP6" s="32"/>
+      <c r="BQ6" s="32"/>
+      <c r="BR6" s="32"/>
+      <c r="BS6" s="32"/>
+      <c r="BT6" s="32"/>
+      <c r="BU6" s="32"/>
+      <c r="BV6" s="32"/>
+      <c r="BW6" s="32"/>
+      <c r="BX6" s="32"/>
+      <c r="BY6" s="32"/>
+      <c r="BZ6" s="32"/>
+      <c r="CA6" s="32"/>
+      <c r="CB6" s="32"/>
+      <c r="CC6" s="32"/>
+      <c r="CD6" s="32"/>
+      <c r="CE6" s="32"/>
+      <c r="CF6" s="32"/>
+      <c r="CG6" s="32"/>
+      <c r="CH6" s="32"/>
+      <c r="CI6" s="32"/>
+      <c r="CJ6" s="32"/>
+      <c r="CK6" s="32"/>
+      <c r="CL6" s="32"/>
+      <c r="CM6" s="32"/>
+      <c r="CN6" s="32"/>
+      <c r="CO6" s="32"/>
+      <c r="CP6" s="32"/>
+      <c r="CQ6" s="32"/>
+      <c r="CR6" s="32"/>
+      <c r="CS6" s="32"/>
+      <c r="CT6" s="32"/>
+      <c r="CU6" s="32"/>
+      <c r="CV6" s="32"/>
+      <c r="CW6" s="32"/>
+      <c r="CX6" s="32"/>
+      <c r="CY6" s="32"/>
+      <c r="CZ6" s="32"/>
+      <c r="DA6" s="32"/>
+      <c r="DB6" s="32"/>
+      <c r="DC6" s="32"/>
+      <c r="DD6" s="32"/>
+      <c r="DE6" s="32"/>
+      <c r="DF6" s="32"/>
+      <c r="DG6" s="32"/>
+      <c r="DH6" s="32"/>
+      <c r="DI6" s="32"/>
+      <c r="DJ6" s="32"/>
+      <c r="DK6" s="32"/>
+      <c r="DL6" s="32"/>
+      <c r="DM6" s="32"/>
+      <c r="DN6" s="32"/>
+      <c r="DO6" s="32"/>
+      <c r="DP6" s="32"/>
+      <c r="DQ6" s="32"/>
+      <c r="DR6" s="32"/>
+      <c r="DS6" s="32"/>
+      <c r="DT6" s="32"/>
+      <c r="DU6" s="32"/>
+      <c r="DV6" s="32"/>
+      <c r="DW6" s="32"/>
+      <c r="DX6" s="32"/>
+      <c r="DY6" s="32"/>
+      <c r="DZ6" s="32"/>
+      <c r="EA6" s="32"/>
+      <c r="EB6" s="32"/>
+      <c r="EC6" s="32"/>
+      <c r="ED6" s="32"/>
+      <c r="EE6" s="32"/>
+      <c r="EF6" s="32"/>
+      <c r="EG6" s="32"/>
+      <c r="EH6" s="32"/>
+      <c r="EI6" s="32"/>
+      <c r="EJ6" s="32"/>
+      <c r="EK6" s="32"/>
+      <c r="EL6" s="32"/>
+      <c r="EM6" s="32"/>
+      <c r="EN6" s="32"/>
+      <c r="EO6" s="32"/>
+      <c r="EP6" s="32"/>
+      <c r="EQ6" s="32"/>
+      <c r="ER6" s="32"/>
+      <c r="ES6" s="32"/>
+      <c r="ET6" s="32"/>
+      <c r="EU6" s="32"/>
+      <c r="EV6" s="32"/>
+      <c r="EW6" s="32"/>
+      <c r="EX6" s="32"/>
+      <c r="EY6" s="32"/>
     </row>
     <row r="7" spans="2:155" x14ac:dyDescent="0.2">
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="36"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="36"/>
-      <c r="V7" s="36"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="36"/>
-      <c r="AB7" s="36"/>
-      <c r="AC7" s="36"/>
-      <c r="AD7" s="36"/>
-      <c r="AE7" s="36"/>
-      <c r="AF7" s="36"/>
-      <c r="AG7" s="36"/>
-      <c r="AH7" s="36"/>
-      <c r="AI7" s="36"/>
-      <c r="AJ7" s="36"/>
-      <c r="AK7" s="36"/>
-      <c r="AL7" s="36"/>
-      <c r="AM7" s="36"/>
-      <c r="AN7" s="36"/>
-      <c r="AO7" s="36"/>
-      <c r="AP7" s="36"/>
-      <c r="AQ7" s="36"/>
-      <c r="AR7" s="36"/>
-      <c r="AS7" s="36"/>
-      <c r="AT7" s="36"/>
-      <c r="AU7" s="36"/>
-      <c r="AV7" s="36"/>
-      <c r="AW7" s="36"/>
-      <c r="AX7" s="36"/>
-      <c r="AY7" s="36"/>
-      <c r="AZ7" s="36"/>
-      <c r="BA7" s="36"/>
-      <c r="BB7" s="36"/>
-      <c r="BC7" s="36"/>
-      <c r="BD7" s="36"/>
-      <c r="BE7" s="36"/>
-      <c r="BF7" s="36"/>
-      <c r="BG7" s="36"/>
-      <c r="BH7" s="36"/>
-      <c r="BI7" s="36"/>
-      <c r="BJ7" s="36"/>
-      <c r="BK7" s="36"/>
-      <c r="BL7" s="36"/>
-      <c r="BM7" s="36"/>
-      <c r="BN7" s="36"/>
-      <c r="BO7" s="36"/>
-      <c r="BP7" s="36"/>
-      <c r="BQ7" s="36"/>
-      <c r="BR7" s="36"/>
-      <c r="BS7" s="36"/>
-      <c r="BT7" s="36"/>
-      <c r="BU7" s="36"/>
-      <c r="BV7" s="36"/>
-      <c r="BW7" s="36"/>
-      <c r="BX7" s="36"/>
-      <c r="BY7" s="36"/>
-      <c r="BZ7" s="36"/>
-      <c r="CA7" s="36"/>
-      <c r="CB7" s="36"/>
-      <c r="CC7" s="36"/>
-      <c r="CD7" s="36"/>
-      <c r="CE7" s="36"/>
-      <c r="CF7" s="36"/>
-      <c r="CG7" s="36"/>
-      <c r="CH7" s="36"/>
-      <c r="CI7" s="36"/>
-      <c r="CJ7" s="36"/>
-      <c r="CK7" s="36"/>
-      <c r="CL7" s="36"/>
-      <c r="CM7" s="36"/>
-      <c r="CN7" s="36"/>
-      <c r="CO7" s="36"/>
-      <c r="CP7" s="36"/>
-      <c r="CQ7" s="36"/>
-      <c r="CR7" s="36"/>
-      <c r="CS7" s="36"/>
-      <c r="CT7" s="36"/>
-      <c r="CU7" s="36"/>
-      <c r="CV7" s="36"/>
-      <c r="CW7" s="36"/>
-      <c r="CX7" s="36"/>
-      <c r="CY7" s="36"/>
-      <c r="CZ7" s="36"/>
-      <c r="DA7" s="36"/>
-      <c r="DB7" s="36"/>
-      <c r="DC7" s="36"/>
-      <c r="DD7" s="36"/>
-      <c r="DE7" s="36"/>
-      <c r="DF7" s="36"/>
-      <c r="DG7" s="36"/>
-      <c r="DH7" s="36"/>
-      <c r="DI7" s="36"/>
-      <c r="DJ7" s="36"/>
-      <c r="DK7" s="36"/>
-      <c r="DL7" s="36"/>
-      <c r="DM7" s="36"/>
-      <c r="DN7" s="36"/>
-      <c r="DO7" s="36"/>
-      <c r="DP7" s="36"/>
-      <c r="DQ7" s="36"/>
-      <c r="DR7" s="36"/>
-      <c r="DS7" s="36"/>
-      <c r="DT7" s="36"/>
-      <c r="DU7" s="36"/>
-      <c r="DV7" s="36"/>
-      <c r="DW7" s="36"/>
-      <c r="DX7" s="36"/>
-      <c r="DY7" s="36"/>
-      <c r="DZ7" s="36"/>
-      <c r="EA7" s="36"/>
-      <c r="EB7" s="36"/>
-      <c r="EC7" s="36"/>
-      <c r="ED7" s="36"/>
-      <c r="EE7" s="36"/>
-      <c r="EF7" s="36"/>
-      <c r="EG7" s="36"/>
-      <c r="EH7" s="36"/>
-      <c r="EI7" s="36"/>
-      <c r="EJ7" s="36"/>
-      <c r="EK7" s="36"/>
-      <c r="EL7" s="36"/>
-      <c r="EM7" s="36"/>
-      <c r="EN7" s="36"/>
-      <c r="EO7" s="36"/>
-      <c r="EP7" s="36"/>
-      <c r="EQ7" s="36"/>
-      <c r="ER7" s="36"/>
-      <c r="ES7" s="36"/>
-      <c r="ET7" s="36"/>
-      <c r="EU7" s="36"/>
-      <c r="EV7" s="36"/>
-      <c r="EW7" s="36"/>
-      <c r="EX7" s="36"/>
-      <c r="EY7" s="36"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="32"/>
+      <c r="T7" s="32"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="32"/>
+      <c r="W7" s="32"/>
+      <c r="X7" s="32"/>
+      <c r="Y7" s="32"/>
+      <c r="Z7" s="32"/>
+      <c r="AA7" s="32"/>
+      <c r="AB7" s="32"/>
+      <c r="AC7" s="32"/>
+      <c r="AD7" s="32"/>
+      <c r="AE7" s="32"/>
+      <c r="AF7" s="32"/>
+      <c r="AG7" s="32"/>
+      <c r="AH7" s="32"/>
+      <c r="AI7" s="32"/>
+      <c r="AJ7" s="32"/>
+      <c r="AK7" s="32"/>
+      <c r="AL7" s="32"/>
+      <c r="AM7" s="32"/>
+      <c r="AN7" s="32"/>
+      <c r="AO7" s="32"/>
+      <c r="AP7" s="32"/>
+      <c r="AQ7" s="32"/>
+      <c r="AR7" s="32"/>
+      <c r="AS7" s="32"/>
+      <c r="AT7" s="32"/>
+      <c r="AU7" s="32"/>
+      <c r="AV7" s="32"/>
+      <c r="AW7" s="32"/>
+      <c r="AX7" s="32"/>
+      <c r="AY7" s="32"/>
+      <c r="AZ7" s="32"/>
+      <c r="BA7" s="32"/>
+      <c r="BB7" s="32"/>
+      <c r="BC7" s="32"/>
+      <c r="BD7" s="32"/>
+      <c r="BE7" s="32"/>
+      <c r="BF7" s="32"/>
+      <c r="BG7" s="32"/>
+      <c r="BH7" s="32"/>
+      <c r="BI7" s="32"/>
+      <c r="BJ7" s="32"/>
+      <c r="BK7" s="32"/>
+      <c r="BL7" s="32"/>
+      <c r="BM7" s="32"/>
+      <c r="BN7" s="32"/>
+      <c r="BO7" s="32"/>
+      <c r="BP7" s="32"/>
+      <c r="BQ7" s="32"/>
+      <c r="BR7" s="32"/>
+      <c r="BS7" s="32"/>
+      <c r="BT7" s="32"/>
+      <c r="BU7" s="32"/>
+      <c r="BV7" s="32"/>
+      <c r="BW7" s="32"/>
+      <c r="BX7" s="32"/>
+      <c r="BY7" s="32"/>
+      <c r="BZ7" s="32"/>
+      <c r="CA7" s="32"/>
+      <c r="CB7" s="32"/>
+      <c r="CC7" s="32"/>
+      <c r="CD7" s="32"/>
+      <c r="CE7" s="32"/>
+      <c r="CF7" s="32"/>
+      <c r="CG7" s="32"/>
+      <c r="CH7" s="32"/>
+      <c r="CI7" s="32"/>
+      <c r="CJ7" s="32"/>
+      <c r="CK7" s="32"/>
+      <c r="CL7" s="32"/>
+      <c r="CM7" s="32"/>
+      <c r="CN7" s="32"/>
+      <c r="CO7" s="32"/>
+      <c r="CP7" s="32"/>
+      <c r="CQ7" s="32"/>
+      <c r="CR7" s="32"/>
+      <c r="CS7" s="32"/>
+      <c r="CT7" s="32"/>
+      <c r="CU7" s="32"/>
+      <c r="CV7" s="32"/>
+      <c r="CW7" s="32"/>
+      <c r="CX7" s="32"/>
+      <c r="CY7" s="32"/>
+      <c r="CZ7" s="32"/>
+      <c r="DA7" s="32"/>
+      <c r="DB7" s="32"/>
+      <c r="DC7" s="32"/>
+      <c r="DD7" s="32"/>
+      <c r="DE7" s="32"/>
+      <c r="DF7" s="32"/>
+      <c r="DG7" s="32"/>
+      <c r="DH7" s="32"/>
+      <c r="DI7" s="32"/>
+      <c r="DJ7" s="32"/>
+      <c r="DK7" s="32"/>
+      <c r="DL7" s="32"/>
+      <c r="DM7" s="32"/>
+      <c r="DN7" s="32"/>
+      <c r="DO7" s="32"/>
+      <c r="DP7" s="32"/>
+      <c r="DQ7" s="32"/>
+      <c r="DR7" s="32"/>
+      <c r="DS7" s="32"/>
+      <c r="DT7" s="32"/>
+      <c r="DU7" s="32"/>
+      <c r="DV7" s="32"/>
+      <c r="DW7" s="32"/>
+      <c r="DX7" s="32"/>
+      <c r="DY7" s="32"/>
+      <c r="DZ7" s="32"/>
+      <c r="EA7" s="32"/>
+      <c r="EB7" s="32"/>
+      <c r="EC7" s="32"/>
+      <c r="ED7" s="32"/>
+      <c r="EE7" s="32"/>
+      <c r="EF7" s="32"/>
+      <c r="EG7" s="32"/>
+      <c r="EH7" s="32"/>
+      <c r="EI7" s="32"/>
+      <c r="EJ7" s="32"/>
+      <c r="EK7" s="32"/>
+      <c r="EL7" s="32"/>
+      <c r="EM7" s="32"/>
+      <c r="EN7" s="32"/>
+      <c r="EO7" s="32"/>
+      <c r="EP7" s="32"/>
+      <c r="EQ7" s="32"/>
+      <c r="ER7" s="32"/>
+      <c r="ES7" s="32"/>
+      <c r="ET7" s="32"/>
+      <c r="EU7" s="32"/>
+      <c r="EV7" s="32"/>
+      <c r="EW7" s="32"/>
+      <c r="EX7" s="32"/>
+      <c r="EY7" s="32"/>
     </row>
     <row r="8" spans="2:155" x14ac:dyDescent="0.2">
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="36"/>
-      <c r="S8" s="36"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="36"/>
-      <c r="V8" s="36"/>
-      <c r="W8" s="36"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="36"/>
-      <c r="AB8" s="36"/>
-      <c r="AC8" s="36"/>
-      <c r="AD8" s="36"/>
-      <c r="AE8" s="36"/>
-      <c r="AF8" s="36"/>
-      <c r="AG8" s="36"/>
-      <c r="AH8" s="36"/>
-      <c r="AI8" s="36"/>
-      <c r="AJ8" s="36"/>
-      <c r="AK8" s="36"/>
-      <c r="AL8" s="36"/>
-      <c r="AM8" s="36"/>
-      <c r="AN8" s="36"/>
-      <c r="AO8" s="36"/>
-      <c r="AP8" s="36"/>
-      <c r="AQ8" s="36"/>
-      <c r="AR8" s="36"/>
-      <c r="AS8" s="36"/>
-      <c r="AT8" s="36"/>
-      <c r="AU8" s="36"/>
-      <c r="AV8" s="36"/>
-      <c r="AW8" s="36"/>
-      <c r="AX8" s="36"/>
-      <c r="AY8" s="36"/>
-      <c r="AZ8" s="36"/>
-      <c r="BA8" s="36"/>
-      <c r="BB8" s="36"/>
-      <c r="BC8" s="36"/>
-      <c r="BD8" s="36"/>
-      <c r="BE8" s="36"/>
-      <c r="BF8" s="36"/>
-      <c r="BG8" s="36"/>
-      <c r="BH8" s="36"/>
-      <c r="BI8" s="36"/>
-      <c r="BJ8" s="36"/>
-      <c r="BK8" s="36"/>
-      <c r="BL8" s="36"/>
-      <c r="BM8" s="36"/>
-      <c r="BN8" s="36"/>
-      <c r="BO8" s="36"/>
-      <c r="BP8" s="36"/>
-      <c r="BQ8" s="36"/>
-      <c r="BR8" s="36"/>
-      <c r="BS8" s="36"/>
-      <c r="BT8" s="36"/>
-      <c r="BU8" s="36"/>
-      <c r="BV8" s="36"/>
-      <c r="BW8" s="36"/>
-      <c r="BX8" s="36"/>
-      <c r="BY8" s="36"/>
-      <c r="BZ8" s="36"/>
-      <c r="CA8" s="36"/>
-      <c r="CB8" s="36"/>
-      <c r="CC8" s="36"/>
-      <c r="CD8" s="36"/>
-      <c r="CE8" s="36"/>
-      <c r="CF8" s="36"/>
-      <c r="CG8" s="36"/>
-      <c r="CH8" s="36"/>
-      <c r="CI8" s="36"/>
-      <c r="CJ8" s="36"/>
-      <c r="CK8" s="36"/>
-      <c r="CL8" s="36"/>
-      <c r="CM8" s="36"/>
-      <c r="CN8" s="36"/>
-      <c r="CO8" s="36"/>
-      <c r="CP8" s="36"/>
-      <c r="CQ8" s="36"/>
-      <c r="CR8" s="36"/>
-      <c r="CS8" s="36"/>
-      <c r="CT8" s="36"/>
-      <c r="CU8" s="36"/>
-      <c r="CV8" s="36"/>
-      <c r="CW8" s="36"/>
-      <c r="CX8" s="36"/>
-      <c r="CY8" s="36"/>
-      <c r="CZ8" s="36"/>
-      <c r="DA8" s="36"/>
-      <c r="DB8" s="36"/>
-      <c r="DC8" s="36"/>
-      <c r="DD8" s="36"/>
-      <c r="DE8" s="36"/>
-      <c r="DF8" s="36"/>
-      <c r="DG8" s="36"/>
-      <c r="DH8" s="36"/>
-      <c r="DI8" s="36"/>
-      <c r="DJ8" s="36"/>
-      <c r="DK8" s="36"/>
-      <c r="DL8" s="36"/>
-      <c r="DM8" s="36"/>
-      <c r="DN8" s="36"/>
-      <c r="DO8" s="36"/>
-      <c r="DP8" s="36"/>
-      <c r="DQ8" s="36"/>
-      <c r="DR8" s="36"/>
-      <c r="DS8" s="36"/>
-      <c r="DT8" s="36"/>
-      <c r="DU8" s="36"/>
-      <c r="DV8" s="36"/>
-      <c r="DW8" s="36"/>
-      <c r="DX8" s="36"/>
-      <c r="DY8" s="36"/>
-      <c r="DZ8" s="36"/>
-      <c r="EA8" s="36"/>
-      <c r="EB8" s="36"/>
-      <c r="EC8" s="36"/>
-      <c r="ED8" s="36"/>
-      <c r="EE8" s="36"/>
-      <c r="EF8" s="36"/>
-      <c r="EG8" s="36"/>
-      <c r="EH8" s="36"/>
-      <c r="EI8" s="36"/>
-      <c r="EJ8" s="36"/>
-      <c r="EK8" s="36"/>
-      <c r="EL8" s="36"/>
-      <c r="EM8" s="36"/>
-      <c r="EN8" s="36"/>
-      <c r="EO8" s="36"/>
-      <c r="EP8" s="36"/>
-      <c r="EQ8" s="36"/>
-      <c r="ER8" s="36"/>
-      <c r="ES8" s="36"/>
-      <c r="ET8" s="36"/>
-      <c r="EU8" s="36"/>
-      <c r="EV8" s="36"/>
-      <c r="EW8" s="36"/>
-      <c r="EX8" s="36"/>
-      <c r="EY8" s="36"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="32"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="32"/>
+      <c r="W8" s="32"/>
+      <c r="X8" s="32"/>
+      <c r="Y8" s="32"/>
+      <c r="Z8" s="32"/>
+      <c r="AA8" s="32"/>
+      <c r="AB8" s="32"/>
+      <c r="AC8" s="32"/>
+      <c r="AD8" s="32"/>
+      <c r="AE8" s="32"/>
+      <c r="AF8" s="32"/>
+      <c r="AG8" s="32"/>
+      <c r="AH8" s="32"/>
+      <c r="AI8" s="32"/>
+      <c r="AJ8" s="32"/>
+      <c r="AK8" s="32"/>
+      <c r="AL8" s="32"/>
+      <c r="AM8" s="32"/>
+      <c r="AN8" s="32"/>
+      <c r="AO8" s="32"/>
+      <c r="AP8" s="32"/>
+      <c r="AQ8" s="32"/>
+      <c r="AR8" s="32"/>
+      <c r="AS8" s="32"/>
+      <c r="AT8" s="32"/>
+      <c r="AU8" s="32"/>
+      <c r="AV8" s="32"/>
+      <c r="AW8" s="32"/>
+      <c r="AX8" s="32"/>
+      <c r="AY8" s="32"/>
+      <c r="AZ8" s="32"/>
+      <c r="BA8" s="32"/>
+      <c r="BB8" s="32"/>
+      <c r="BC8" s="32"/>
+      <c r="BD8" s="32"/>
+      <c r="BE8" s="32"/>
+      <c r="BF8" s="32"/>
+      <c r="BG8" s="32"/>
+      <c r="BH8" s="32"/>
+      <c r="BI8" s="32"/>
+      <c r="BJ8" s="32"/>
+      <c r="BK8" s="32"/>
+      <c r="BL8" s="32"/>
+      <c r="BM8" s="32"/>
+      <c r="BN8" s="32"/>
+      <c r="BO8" s="32"/>
+      <c r="BP8" s="32"/>
+      <c r="BQ8" s="32"/>
+      <c r="BR8" s="32"/>
+      <c r="BS8" s="32"/>
+      <c r="BT8" s="32"/>
+      <c r="BU8" s="32"/>
+      <c r="BV8" s="32"/>
+      <c r="BW8" s="32"/>
+      <c r="BX8" s="32"/>
+      <c r="BY8" s="32"/>
+      <c r="BZ8" s="32"/>
+      <c r="CA8" s="32"/>
+      <c r="CB8" s="32"/>
+      <c r="CC8" s="32"/>
+      <c r="CD8" s="32"/>
+      <c r="CE8" s="32"/>
+      <c r="CF8" s="32"/>
+      <c r="CG8" s="32"/>
+      <c r="CH8" s="32"/>
+      <c r="CI8" s="32"/>
+      <c r="CJ8" s="32"/>
+      <c r="CK8" s="32"/>
+      <c r="CL8" s="32"/>
+      <c r="CM8" s="32"/>
+      <c r="CN8" s="32"/>
+      <c r="CO8" s="32"/>
+      <c r="CP8" s="32"/>
+      <c r="CQ8" s="32"/>
+      <c r="CR8" s="32"/>
+      <c r="CS8" s="32"/>
+      <c r="CT8" s="32"/>
+      <c r="CU8" s="32"/>
+      <c r="CV8" s="32"/>
+      <c r="CW8" s="32"/>
+      <c r="CX8" s="32"/>
+      <c r="CY8" s="32"/>
+      <c r="CZ8" s="32"/>
+      <c r="DA8" s="32"/>
+      <c r="DB8" s="32"/>
+      <c r="DC8" s="32"/>
+      <c r="DD8" s="32"/>
+      <c r="DE8" s="32"/>
+      <c r="DF8" s="32"/>
+      <c r="DG8" s="32"/>
+      <c r="DH8" s="32"/>
+      <c r="DI8" s="32"/>
+      <c r="DJ8" s="32"/>
+      <c r="DK8" s="32"/>
+      <c r="DL8" s="32"/>
+      <c r="DM8" s="32"/>
+      <c r="DN8" s="32"/>
+      <c r="DO8" s="32"/>
+      <c r="DP8" s="32"/>
+      <c r="DQ8" s="32"/>
+      <c r="DR8" s="32"/>
+      <c r="DS8" s="32"/>
+      <c r="DT8" s="32"/>
+      <c r="DU8" s="32"/>
+      <c r="DV8" s="32"/>
+      <c r="DW8" s="32"/>
+      <c r="DX8" s="32"/>
+      <c r="DY8" s="32"/>
+      <c r="DZ8" s="32"/>
+      <c r="EA8" s="32"/>
+      <c r="EB8" s="32"/>
+      <c r="EC8" s="32"/>
+      <c r="ED8" s="32"/>
+      <c r="EE8" s="32"/>
+      <c r="EF8" s="32"/>
+      <c r="EG8" s="32"/>
+      <c r="EH8" s="32"/>
+      <c r="EI8" s="32"/>
+      <c r="EJ8" s="32"/>
+      <c r="EK8" s="32"/>
+      <c r="EL8" s="32"/>
+      <c r="EM8" s="32"/>
+      <c r="EN8" s="32"/>
+      <c r="EO8" s="32"/>
+      <c r="EP8" s="32"/>
+      <c r="EQ8" s="32"/>
+      <c r="ER8" s="32"/>
+      <c r="ES8" s="32"/>
+      <c r="ET8" s="32"/>
+      <c r="EU8" s="32"/>
+      <c r="EV8" s="32"/>
+      <c r="EW8" s="32"/>
+      <c r="EX8" s="32"/>
+      <c r="EY8" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4969,7 +5345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -5054,11 +5430,11 @@
         <v>34</v>
       </c>
       <c r="C3" s="16" t="e">
-        <f t="array" ref="C3">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C3">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D3" s="16" t="e">
-        <f t="array" ref="D3">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D3">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E3" s="16" t="s">
@@ -5105,11 +5481,11 @@
         <v>34</v>
       </c>
       <c r="C4" s="16" t="e">
-        <f t="array" ref="C4">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C4">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D4" s="16" t="e">
-        <f t="array" ref="D4">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D4">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E4" s="16" t="s">
@@ -5155,11 +5531,11 @@
         <v>34</v>
       </c>
       <c r="C5" s="16" t="e">
-        <f t="array" ref="C5">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C5">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D5" s="16" t="e">
-        <f t="array" ref="D5">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D5">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E5" s="16" t="s">
@@ -5207,11 +5583,11 @@
         <v>34</v>
       </c>
       <c r="C6" s="16" t="e">
-        <f t="array" ref="C6">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C6">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D6" s="16" t="e">
-        <f t="array" ref="D6">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D6">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E6" s="16" t="s">
@@ -5259,11 +5635,11 @@
         <v>34</v>
       </c>
       <c r="C7" s="16" t="e">
-        <f t="array" ref="C7">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C7">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D7" s="16" t="e">
-        <f t="array" ref="D7">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D7">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E7" s="16" t="s">
@@ -5305,11 +5681,11 @@
         <v>38</v>
       </c>
       <c r="C8" s="16" t="e">
-        <f t="array" ref="C8">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C8">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D8" s="16" t="e">
-        <f t="array" ref="D8">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D8">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E8" s="16" t="s">
@@ -5357,11 +5733,11 @@
         <v>34</v>
       </c>
       <c r="C9" s="16" t="e">
-        <f t="array" ref="C9">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C9">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D9" s="16" t="e">
-        <f t="array" ref="D9">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D9">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E9" s="16" t="s">
@@ -5411,11 +5787,11 @@
         <v>34</v>
       </c>
       <c r="C10" s="16" t="e">
-        <f t="array" ref="C10">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C10">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D10" s="16" t="e">
-        <f t="array" ref="D10">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D10">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E10" s="16" t="s">
@@ -5465,11 +5841,11 @@
         <v>34</v>
       </c>
       <c r="C11" s="16" t="e">
-        <f t="array" ref="C11">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C11">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D11" s="16" t="e">
-        <f t="array" ref="D11">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D11">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E11" s="16" t="s">
@@ -5517,11 +5893,11 @@
         <v>38</v>
       </c>
       <c r="C12" s="16" t="e">
-        <f t="array" ref="C12">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C12">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D12" s="16" t="e">
-        <f t="array" ref="D12">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D12">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E12" s="16" t="s">
@@ -5563,11 +5939,11 @@
         <v>34</v>
       </c>
       <c r="C13" s="16" t="e">
-        <f t="array" ref="C13">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C13">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D13" s="16" t="e">
-        <f t="array" ref="D13">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D13">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E13" s="16" t="s">
@@ -5607,11 +5983,11 @@
         <v>38</v>
       </c>
       <c r="C14" s="16" t="e">
-        <f t="array" ref="C14">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C14">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D14" s="16" t="e">
-        <f t="array" ref="D14">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D14">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E14" s="16" t="s">
@@ -5651,11 +6027,11 @@
         <v>34</v>
       </c>
       <c r="C15" s="16" t="e">
-        <f t="array" ref="C15">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C15">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D15" s="16" t="e">
-        <f t="array" ref="D15">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D15">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E15" s="16" t="s">
@@ -5696,11 +6072,11 @@
         <v>34</v>
       </c>
       <c r="C16" s="16" t="e">
-        <f t="array" ref="C16">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C16">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D16" s="16" t="e">
-        <f t="array" ref="D16">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D16">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E16" s="16" t="s">
@@ -5740,11 +6116,11 @@
         <v>34</v>
       </c>
       <c r="C17" s="16" t="e">
-        <f t="array" ref="C17">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C17">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D17" s="16" t="e">
-        <f t="array" ref="D17">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D17">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E17" s="16" t="s">
@@ -5784,11 +6160,11 @@
         <v>34</v>
       </c>
       <c r="C18" s="16" t="e">
-        <f t="array" ref="C18">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C18">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D18" s="16" t="e">
-        <f t="array" ref="D18">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D18">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E18" s="16" t="s">
@@ -5828,11 +6204,11 @@
         <v>34</v>
       </c>
       <c r="C19" s="16" t="e">
-        <f t="array" ref="C19">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C19">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D19" s="16" t="e">
-        <f t="array" ref="D19">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D19">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E19" s="16" t="s">
@@ -5872,11 +6248,11 @@
         <v>38</v>
       </c>
       <c r="C20" s="16" t="e">
-        <f t="array" ref="C20">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C20">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D20" s="16" t="e">
-        <f t="array" ref="D20">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D20">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E20" s="16" t="s">
@@ -5917,11 +6293,11 @@
         <v>38</v>
       </c>
       <c r="C21" s="16" t="e">
-        <f t="array" ref="C21">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C21">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D21" s="16" t="e">
-        <f t="array" ref="D21">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D21">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E21" s="16" t="s">
@@ -5969,11 +6345,11 @@
         <v>38</v>
       </c>
       <c r="C22" s="16" t="e">
-        <f t="array" ref="C22">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C22">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D22" s="16" t="e">
-        <f t="array" ref="D22">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D22">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E22" s="16" t="s">
@@ -6023,11 +6399,11 @@
         <v>38</v>
       </c>
       <c r="C23" s="16" t="e">
-        <f t="array" ref="C23">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C23">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D23" s="16" t="e">
-        <f t="array" ref="D23">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D23">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E23" s="16" t="s">
@@ -6077,11 +6453,11 @@
         <v>38</v>
       </c>
       <c r="C24" s="16" t="e">
-        <f t="array" ref="C24">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C24">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D24" s="16" t="e">
-        <f t="array" ref="D24">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D24">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E24" s="16" t="s">
@@ -6130,11 +6506,11 @@
         <v>38</v>
       </c>
       <c r="C25" s="16" t="e">
-        <f t="array" ref="C25">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C25">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D25" s="16" t="e">
-        <f t="array" ref="D25">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D25">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E25" s="16" t="s">
@@ -6184,11 +6560,11 @@
         <v>38</v>
       </c>
       <c r="C26" s="16" t="e">
-        <f t="array" ref="C26">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C26">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D26" s="16" t="e">
-        <f t="array" ref="D26">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D26">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E26" s="16" t="s">
@@ -6238,11 +6614,11 @@
         <v>38</v>
       </c>
       <c r="C27" s="16" t="e">
-        <f t="array" ref="C27">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C27">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D27" s="16" t="e">
-        <f t="array" ref="D27">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D27">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E27" s="16" t="s">
@@ -6284,11 +6660,11 @@
         <v>38</v>
       </c>
       <c r="C28" s="16" t="e">
-        <f t="array" ref="C28">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C28">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D28" s="16" t="e">
-        <f t="array" ref="D28">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D28">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E28" s="16" t="s">
@@ -6336,11 +6712,11 @@
         <v>38</v>
       </c>
       <c r="C29" s="16" t="e">
-        <f t="array" ref="C29">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C29">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D29" s="16" t="e">
-        <f t="array" ref="D29">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D29">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E29" s="16" t="s">
@@ -6388,11 +6764,11 @@
         <v>38</v>
       </c>
       <c r="C30" s="16" t="e">
-        <f t="array" ref="C30">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C30">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D30" s="16" t="e">
-        <f t="array" ref="D30">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D30">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E30" s="16" t="s">
@@ -6434,11 +6810,11 @@
         <v>38</v>
       </c>
       <c r="C31" s="16" t="e">
-        <f t="array" ref="C31">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C31">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D31" s="16" t="e">
-        <f t="array" ref="D31">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D31">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E31" s="16" t="s">
@@ -6484,11 +6860,11 @@
         <v>38</v>
       </c>
       <c r="C32" s="16" t="e">
-        <f t="array" ref="C32">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C32">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D32" s="16" t="e">
-        <f t="array" ref="D32">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D32">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E32" s="16" t="s">
@@ -6534,11 +6910,11 @@
         <v>38</v>
       </c>
       <c r="C33" s="16" t="e">
-        <f t="array" ref="C33">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C33">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D33" s="16" t="e">
-        <f t="array" ref="D33">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D33">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E33" s="16" t="s">
@@ -6584,11 +6960,11 @@
         <v>38</v>
       </c>
       <c r="C34" s="16" t="e">
-        <f t="array" ref="C34">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C34">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D34" s="16" t="e">
-        <f t="array" ref="D34">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D34">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E34" s="16" t="s">
@@ -6630,11 +7006,11 @@
         <v>38</v>
       </c>
       <c r="C35" s="16" t="e">
-        <f t="array" ref="C35">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C35">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D35" s="16" t="e">
-        <f t="array" ref="D35">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D35">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E35" s="16" t="s">
@@ -6676,11 +7052,11 @@
         <v>41</v>
       </c>
       <c r="C36" s="16" t="e">
-        <f t="array" ref="C36">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C36">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D36" s="16" t="e">
-        <f t="array" ref="D36">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D36">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E36" s="16" t="s">
@@ -6720,11 +7096,11 @@
         <v>41</v>
       </c>
       <c r="C37" s="16" t="e">
-        <f t="array" ref="C37">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C37">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D37" s="16" t="e">
-        <f t="array" ref="D37">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D37">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E37" s="16" t="s">
@@ -6764,11 +7140,11 @@
         <v>41</v>
       </c>
       <c r="C38" s="16" t="e">
-        <f t="array" ref="C38">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C38">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D38" s="16" t="e">
-        <f t="array" ref="D38">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D38">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E38" s="16" t="s">
@@ -6808,11 +7184,11 @@
         <v>41</v>
       </c>
       <c r="C39" s="16" t="e">
-        <f t="array" ref="C39">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C39">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D39" s="16" t="e">
-        <f t="array" ref="D39">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D39">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E39" s="16" t="s">
@@ -6852,11 +7228,11 @@
         <v>41</v>
       </c>
       <c r="C40" s="16" t="e">
-        <f t="array" ref="C40">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C40">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D40" s="16" t="e">
-        <f t="array" ref="D40">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D40">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E40" s="16" t="s">
@@ -6896,11 +7272,11 @@
         <v>41</v>
       </c>
       <c r="C41" s="16" t="e">
-        <f t="array" ref="C41">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C41">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D41" s="16" t="e">
-        <f t="array" ref="D41">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D41">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E41" s="16" t="s">
@@ -6940,11 +7316,11 @@
         <v>41</v>
       </c>
       <c r="C42" s="16" t="e">
-        <f t="array" ref="C42">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C42">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D42" s="16" t="e">
-        <f t="array" ref="D42">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D42">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E42" s="16" t="s">
@@ -6984,11 +7360,11 @@
         <v>41</v>
       </c>
       <c r="C43" s="16" t="e">
-        <f t="array" ref="C43">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C43">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D43" s="16" t="e">
-        <f t="array" ref="D43">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D43">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E43" s="16" t="s">
@@ -7029,11 +7405,11 @@
         <v>41</v>
       </c>
       <c r="C44" s="16" t="e">
-        <f t="array" ref="C44">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C44">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D44" s="16" t="e">
-        <f t="array" ref="D44">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D44">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E44" s="16" t="s">
@@ -7073,11 +7449,11 @@
         <v>41</v>
       </c>
       <c r="C45" s="16" t="e">
-        <f t="array" ref="C45">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C45">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D45" s="16" t="e">
-        <f t="array" ref="D45">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D45">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E45" s="16" t="s">
@@ -7117,11 +7493,11 @@
         <v>41</v>
       </c>
       <c r="C46" s="16" t="e">
-        <f t="array" ref="C46">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C46">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D46" s="16" t="e">
-        <f t="array" ref="D46">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D46">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E46" s="16" t="s">
@@ -7162,11 +7538,11 @@
         <v>41</v>
       </c>
       <c r="C47" s="16" t="e">
-        <f t="array" ref="C47">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C47">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D47" s="16" t="e">
-        <f t="array" ref="D47">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D47">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E47" s="16" t="s">
@@ -7206,11 +7582,11 @@
         <v>41</v>
       </c>
       <c r="C48" s="16" t="e">
-        <f t="array" ref="C48">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C48">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D48" s="16" t="e">
-        <f t="array" ref="D48">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D48">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E48" s="16" t="s">
@@ -7250,11 +7626,11 @@
         <v>41</v>
       </c>
       <c r="C49" s="16" t="e">
-        <f t="array" ref="C49">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C49">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D49" s="16" t="e">
-        <f t="array" ref="D49">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D49">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E49" s="16" t="s">
@@ -7294,11 +7670,11 @@
         <v>41</v>
       </c>
       <c r="C50" s="16" t="e">
-        <f t="array" ref="C50">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C50">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D50" s="16" t="e">
-        <f t="array" ref="D50">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D50">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E50" s="16" t="s">
@@ -7338,11 +7714,11 @@
         <v>41</v>
       </c>
       <c r="C51" s="16" t="e">
-        <f t="array" ref="C51">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C51">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D51" s="16" t="e">
-        <f t="array" ref="D51">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D51">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E51" s="16" t="s">
@@ -7382,11 +7758,11 @@
         <v>41</v>
       </c>
       <c r="C52" s="16" t="e">
-        <f t="array" ref="C52">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C52">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D52" s="16" t="e">
-        <f t="array" ref="D52">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D52">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E52" s="16" t="s">
@@ -7426,11 +7802,11 @@
         <v>41</v>
       </c>
       <c r="C53" s="16" t="e">
-        <f t="array" ref="C53">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C53">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D53" s="16" t="e">
-        <f t="array" ref="D53">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D53">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E53" s="16" t="s">
@@ -7470,11 +7846,11 @@
         <v>41</v>
       </c>
       <c r="C54" s="16" t="e">
-        <f t="array" ref="C54">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C54">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D54" s="16" t="e">
-        <f t="array" ref="D54">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D54">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E54" s="16" t="s">
@@ -7514,11 +7890,11 @@
         <v>41</v>
       </c>
       <c r="C55" s="16" t="e">
-        <f t="array" ref="C55">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C55">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D55" s="16" t="e">
-        <f t="array" ref="D55">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D55">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E55" s="16" t="s">
@@ -7559,11 +7935,11 @@
         <v>41</v>
       </c>
       <c r="C56" s="16" t="e">
-        <f t="array" ref="C56">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C56">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D56" s="16" t="e">
-        <f t="array" ref="D56">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D56">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E56" s="16" t="s">
@@ -7603,11 +7979,11 @@
         <v>41</v>
       </c>
       <c r="C57" s="16" t="e">
-        <f t="array" ref="C57">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C57">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D57" s="16" t="e">
-        <f t="array" ref="D57">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D57">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E57" s="16" t="s">
@@ -7647,11 +8023,11 @@
         <v>41</v>
       </c>
       <c r="C58" s="16" t="e">
-        <f t="array" ref="C58">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C58">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D58" s="16" t="e">
-        <f t="array" ref="D58">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D58">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E58" s="16" t="s">
@@ -7691,11 +8067,11 @@
         <v>41</v>
       </c>
       <c r="C59" s="16" t="e">
-        <f t="array" ref="C59">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C59">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D59" s="16" t="e">
-        <f t="array" ref="D59">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D59">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E59" s="16" t="s">
@@ -7735,11 +8111,11 @@
         <v>41</v>
       </c>
       <c r="C60" s="16" t="e">
-        <f t="array" ref="C60">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C60">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D60" s="16" t="e">
-        <f t="array" ref="D60">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D60">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E60" s="16" t="s">
@@ -7779,11 +8155,11 @@
         <v>41</v>
       </c>
       <c r="C61" s="16" t="e">
-        <f t="array" ref="C61">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C61">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D61" s="16" t="e">
-        <f t="array" ref="D61">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D61">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E61" s="16" t="s">
@@ -7823,11 +8199,11 @@
         <v>41</v>
       </c>
       <c r="C62" s="16" t="e">
-        <f t="array" ref="C62">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C62">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D62" s="16" t="e">
-        <f t="array" ref="D62">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D62">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E62" s="16" t="s">
@@ -7868,11 +8244,11 @@
         <v>41</v>
       </c>
       <c r="C63" s="16" t="e">
-        <f t="array" ref="C63">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C63">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D63" s="16" t="e">
-        <f t="array" ref="D63">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D63">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E63" s="16" t="s">
@@ -7912,11 +8288,11 @@
         <v>41</v>
       </c>
       <c r="C64" s="16" t="e">
-        <f t="array" ref="C64">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C64">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D64" s="16" t="e">
-        <f t="array" ref="D64">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D64">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E64" s="16" t="s">
@@ -7957,11 +8333,11 @@
         <v>41</v>
       </c>
       <c r="C65" s="16" t="e">
-        <f t="array" ref="C65">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C65">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D65" s="16" t="e">
-        <f t="array" ref="D65">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D65">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E65" s="16" t="s">
@@ -8001,11 +8377,11 @@
         <v>41</v>
       </c>
       <c r="C66" s="16" t="e">
-        <f t="array" ref="C66">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C66">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D66" s="16" t="e">
-        <f t="array" ref="D66">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D66">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E66" s="16" t="s">
@@ -8045,11 +8421,11 @@
         <v>41</v>
       </c>
       <c r="C67" s="16" t="e">
-        <f t="array" ref="C67">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C67">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D67" s="16" t="e">
-        <f t="array" ref="D67">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D67">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E67" s="16" t="s">
@@ -8089,11 +8465,11 @@
         <v>41</v>
       </c>
       <c r="C68" s="16" t="e">
-        <f t="array" ref="C68">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C68">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D68" s="16" t="e">
-        <f t="array" ref="D68">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D68">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E68" s="16" t="s">
@@ -8133,11 +8509,11 @@
         <v>41</v>
       </c>
       <c r="C69" s="16" t="e">
-        <f t="array" ref="C69">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C69">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D69" s="16" t="e">
-        <f t="array" ref="D69">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D69">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E69" s="16" t="s">
@@ -8177,11 +8553,11 @@
         <v>41</v>
       </c>
       <c r="C70" s="16" t="e">
-        <f t="array" ref="C70">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C70">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D70" s="16" t="e">
-        <f t="array" ref="D70">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D70">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E70" s="16" t="s">
@@ -8221,11 +8597,11 @@
         <v>41</v>
       </c>
       <c r="C71" s="16" t="e">
-        <f t="array" ref="C71">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C71">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D71" s="16" t="e">
-        <f t="array" ref="D71">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D71">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E71" s="16" t="s">
@@ -8265,11 +8641,11 @@
         <v>41</v>
       </c>
       <c r="C72" s="16" t="e">
-        <f t="array" ref="C72">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C72">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D72" s="16" t="e">
-        <f t="array" ref="D72">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D72">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E72" s="16" t="s">
@@ -8309,11 +8685,11 @@
         <v>41</v>
       </c>
       <c r="C73" s="16" t="e">
-        <f t="array" ref="C73">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C73">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D73" s="16" t="e">
-        <f t="array" ref="D73">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D73">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E73" s="16" t="s">
@@ -8353,11 +8729,11 @@
         <v>41</v>
       </c>
       <c r="C74" s="16" t="e">
-        <f t="array" ref="C74">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Account Type2]])</f>
+        <f t="array" ref="C74">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="D74" s="16" t="e">
-        <f t="array" ref="D74">_xlfn.XLOOKUP(#REF!,Table2[[#All],[Account]],Table2[[#All],[Owner]])</f>
+        <f t="array" ref="D74">_xlfn.XLOOKUP(#REF!,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
       <c r="E74" s="16" t="s">
@@ -8398,7 +8774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -8413,979 +8789,979 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="24" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B4" s="25" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B4" s="29" t="s">
+      <c r="C4" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="29" t="s">
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B5" s="25" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B5" s="29" t="s">
+      <c r="C5" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="29" t="s">
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B6" s="25" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B6" s="29" t="s">
+      <c r="C6" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="16" t="s">
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B7" s="25" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B7" s="29" t="s">
+      <c r="C7" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="29" t="s">
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B8" s="25" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B8" s="29" t="s">
+      <c r="C8" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="29" t="s">
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B9" s="25" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B9" s="29" t="s">
+      <c r="C9" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="29" t="s">
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B10" s="25" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B10" s="29" t="s">
+      <c r="C10" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="30" t="s">
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B11" s="25" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B11" s="29" t="s">
+      <c r="C11" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="29" t="s">
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B12" s="25" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B12" s="29" t="s">
+      <c r="C12" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="29" t="s">
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B13" s="25" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B13" s="29" t="s">
+      <c r="C13" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="29" t="s">
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B14" s="25" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B14" s="29" t="s">
+      <c r="C14" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="29" t="s">
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B15" s="25" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B15" s="29" t="s">
+      <c r="C15" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="29" t="s">
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B16" s="25" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B16" s="29" t="s">
+      <c r="C16" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="29" t="s">
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B17" s="25" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B17" s="29" t="s">
+      <c r="C17" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="29" t="s">
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B18" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="25" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="29" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B19" s="25" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B19" s="29" t="s">
+      <c r="C19" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="29" t="s">
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B20" s="25" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B20" s="29" t="s">
+      <c r="C20" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="29" t="s">
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B21" s="25" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B21" s="29" t="s">
+      <c r="C21" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="29" t="s">
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B22" s="25" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B22" s="29" t="s">
+      <c r="C22" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="29" t="s">
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B23" s="25" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B23" s="29" t="s">
+      <c r="C23" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="29" t="s">
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B24" s="25" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B24" s="29" t="s">
+      <c r="C24" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="29" t="s">
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B25" s="25" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B25" s="29" t="s">
+      <c r="C25" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="C25" s="29" t="s">
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B26" s="25" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="29" t="s">
+      <c r="C26" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="29" t="s">
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B27" s="25" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B27" s="29" t="s">
+      <c r="C27" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="29" t="s">
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B28" s="25" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B28" s="29" t="s">
+      <c r="C28" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="29" t="s">
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B29" s="25" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B29" s="29" t="s">
+      <c r="C29" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C29" s="29" t="s">
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B30" s="25" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B30" s="29" t="s">
+      <c r="C30" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="29" t="s">
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B31" s="25" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B31" s="29" t="s">
+      <c r="C31" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="29" t="s">
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B32" s="25" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B32" s="29" t="s">
+      <c r="C32" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="C32" s="29" t="s">
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B33" s="25" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B33" s="29" t="s">
+      <c r="C33" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="C33" s="29" t="s">
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B34" s="25" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B34" s="29" t="s">
+      <c r="C34" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="C34" s="29" t="s">
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B35" s="25" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B35" s="29" t="s">
+      <c r="C35" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="C35" s="29" t="s">
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B36" s="25" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B36" s="29" t="s">
+      <c r="C36" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="29" t="s">
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B37" s="25" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B37" s="29" t="s">
+      <c r="C37" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C37" s="29" t="s">
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B38" s="25" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B38" s="29" t="s">
+      <c r="C38" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="C38" s="29" t="s">
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B39" s="25" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B39" s="29" t="s">
+      <c r="C39" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="C39" s="29" t="s">
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B40" s="25" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B40" s="29" t="s">
+      <c r="C40" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="29" t="s">
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B41" s="25" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B41" s="29" t="s">
+      <c r="C41" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="29" t="s">
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B42" s="25" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B42" s="29" t="s">
+      <c r="C42" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="C42" s="29" t="s">
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B43" s="25" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B43" s="29" t="s">
+      <c r="C43" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="C43" s="29" t="s">
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B44" s="25" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B44" s="29" t="s">
+      <c r="C44" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="C44" s="29" t="s">
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B45" s="25" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B45" s="29" t="s">
+      <c r="C45" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="29" t="s">
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B46" s="25" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B46" s="29" t="s">
+      <c r="C46" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="C46" s="29" t="s">
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B47" s="25" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B47" s="29" t="s">
+      <c r="C47" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="C47" s="29" t="s">
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B48" s="25" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B48" s="29" t="s">
+      <c r="C48" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="C48" s="29" t="s">
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="25" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="29" t="s">
+      <c r="C49" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="C49" s="29" t="s">
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="25" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B50" s="29" t="s">
+      <c r="C50" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="C50" s="29" t="s">
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B51" s="25" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="29" t="s">
+      <c r="C51" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="C51" s="29" t="s">
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C52" s="25" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="C52" s="29" t="s">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C53" s="27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="25" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="C53" s="31" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="29" t="s">
+      <c r="C54" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="C54" s="29" t="s">
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="25" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="29" t="s">
+      <c r="C55" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="C55" s="29" t="s">
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="25" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="29" t="s">
+      <c r="C56" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="C56" s="29" t="s">
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="25" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="29" t="s">
+      <c r="C57" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="C57" s="29" t="s">
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="25" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B58" s="29" t="s">
+      <c r="C58" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="C58" s="29" t="s">
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B59" s="25" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="29" t="s">
+      <c r="C59" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="C59" s="29" t="s">
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="25" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="29" t="s">
+      <c r="C60" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="C60" s="29" t="s">
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="25" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="29" t="s">
+      <c r="C61" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="C61" s="29" t="s">
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="25" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="29" t="s">
+      <c r="C62" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="C62" s="29" t="s">
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="25" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63" s="29" t="s">
+      <c r="C63" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="C63" s="29" t="s">
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B64" s="25" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B64" s="29" t="s">
+      <c r="C64" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C64" s="29" t="s">
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="25" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B65" s="29" t="s">
+      <c r="C65" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="C65" s="29" t="s">
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="25" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B66" s="29" t="s">
+      <c r="C66" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="C66" s="29" t="s">
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="25" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B67" s="29" t="s">
+      <c r="C67" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="C67" s="29" t="s">
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="25" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B68" s="29" t="s">
+      <c r="C68" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="C68" s="29" t="s">
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="25" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B69" s="29" t="s">
+      <c r="C69" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="C69" s="29" t="s">
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="25" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="29" t="s">
+      <c r="C70" s="25" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="C70" s="29" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B71" s="29" t="s">
+      <c r="C71" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="C71" s="29" t="s">
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B72" s="25" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B72" s="29" t="s">
+      <c r="C72" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="C72" s="29" t="s">
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="25" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="29" t="s">
+      <c r="C73" s="25" t="s">
         <v>183</v>
       </c>
-      <c r="C73" s="29" t="s">
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="25" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B74" s="29" t="s">
+      <c r="C74" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="C74" s="29" t="s">
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="25" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B75" s="29" t="s">
+      <c r="C75" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="C75" s="29" t="s">
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="25" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B76" s="29" t="s">
+      <c r="C76" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="C76" s="29" t="s">
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C77" s="25" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B77" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C77" s="29" t="s">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="25" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B78" s="29" t="s">
+      <c r="C78" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="C78" s="29" t="s">
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="C79" s="25" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B79" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="C79" s="29" t="s">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="25" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B80" s="29" t="s">
+      <c r="C80" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="C80" s="29" t="s">
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="25" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B81" s="29" t="s">
+      <c r="C81" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="C81" s="29" t="s">
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="25" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B82" s="29" t="s">
+      <c r="C82" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="C82" s="29" t="s">
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="25" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B83" s="29" t="s">
+      <c r="C83" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="C83" s="29" t="s">
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="25" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B84" s="29" t="s">
+      <c r="C84" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="C84" s="29" t="s">
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B85" s="25" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B85" s="29" t="s">
+      <c r="C85" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="C85" s="29" t="s">
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B86" s="25" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B86" s="29" t="s">
+      <c r="C86" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="C86" s="29" t="s">
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B87" s="25" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B87" s="29" t="s">
+      <c r="C87" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="C87" s="29" t="s">
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B88" s="25" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B88" s="29" t="s">
+      <c r="C88" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="C88" s="29" t="s">
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B89" s="25" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B89" s="29" t="s">
+      <c r="C89" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="C89" s="29" t="s">
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B90" s="25" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B90" s="29" t="s">
+      <c r="C90" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="C90" s="29" t="s">
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B91" s="25" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B91" s="29" t="s">
+      <c r="C91" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="C91" s="29" t="s">
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B92" s="25" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B92" s="29" t="s">
+      <c r="C92" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="C92" s="29" t="s">
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B93" s="25" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B93" s="29" t="s">
+      <c r="C93" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="C93" s="29" t="s">
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B94" s="25" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B94" s="29" t="s">
+      <c r="C94" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="C94" s="29" t="s">
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B95" s="25" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B95" s="29" t="s">
+      <c r="C95" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="C95" s="29" t="s">
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B96" s="25" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B96" s="29" t="s">
+      <c r="C96" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="C96" s="29" t="s">
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B97" s="25" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B97" s="29" t="s">
+      <c r="C97" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="C97" s="29" t="s">
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B98" s="25" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B98" s="29" t="s">
+      <c r="C98" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="C98" s="29" t="s">
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B99" s="25" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B99" s="29" t="s">
+      <c r="C99" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="C99" s="29" t="s">
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B100" s="25" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B100" s="29" t="s">
+      <c r="C100" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="C100" s="29" t="s">
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B101" s="25" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B101" s="29" t="s">
+      <c r="C101" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="C101" s="29" t="s">
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B102" s="25" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B102" s="29" t="s">
+      <c r="C102" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="C102" s="29" t="s">
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B103" s="25" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B103" s="29" t="s">
+      <c r="C103" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="C103" s="29" t="s">
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B104" s="25" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B104" s="29" t="s">
+      <c r="C104" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="C104" s="29" t="s">
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B105" s="25" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B105" s="29" t="s">
+      <c r="C105" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="C105" s="29" t="s">
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B106" s="25" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B106" s="29" t="s">
+      <c r="C106" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="C106" s="29" t="s">
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B107" s="25" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B107" s="29" t="s">
+      <c r="C107" s="25" t="s">
         <v>249</v>
       </c>
-      <c r="C107" s="29" t="s">
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B108" s="25" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B108" s="29" t="s">
+      <c r="C108" s="25" t="s">
         <v>251</v>
       </c>
-      <c r="C108" s="29" t="s">
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B109" s="25" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B109" s="29" t="s">
+      <c r="C109" s="25" t="s">
         <v>253</v>
       </c>
-      <c r="C109" s="29" t="s">
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B110" s="25" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B110" s="29" t="s">
+      <c r="C110" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="C110" s="29" t="s">
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B111" s="25" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B111" s="29" t="s">
+      <c r="C111" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="C111" s="29" t="s">
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B112" s="25" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B112" s="29" t="s">
+      <c r="C112" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="C112" s="29" t="s">
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B113" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C113" s="25" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B113" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="C113" s="29" t="s">
+    <row r="114" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B114" s="25" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B114" s="29" t="s">
+      <c r="C114" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="C114" s="29" t="s">
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B115" s="25" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B115" s="29" t="s">
+      <c r="C115" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="C115" s="29" t="s">
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B116" s="25" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B116" s="29" t="s">
+      <c r="C116" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="C116" s="29" t="s">
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B117" s="25" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B117" s="29" t="s">
+      <c r="C117" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="C117" s="29" t="s">
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B118" s="25" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B118" s="29" t="s">
+      <c r="C118" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="C118" s="29" t="s">
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B119" s="25" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B119" s="29" t="s">
+      <c r="C119" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="C119" s="29" t="s">
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B120" s="25" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B120" s="29" t="s">
+      <c r="C120" s="25" t="s">
         <v>274</v>
       </c>
-      <c r="C120" s="29" t="s">
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B121" s="25" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B121" s="29" t="s">
+      <c r="C121" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="C121" s="29" t="s">
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B122" s="25" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B122" s="29" t="s">
+      <c r="C122" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="C122" s="29" t="s">
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B123" s="28" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B123" s="32" t="s">
+      <c r="C123" s="28" t="s">
         <v>280</v>
-      </c>
-      <c r="C123" s="32" t="s">
-        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/core/sample-data/Financial Template.xlsx
+++ b/core/sample-data/Financial Template.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10419"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C139EB28-2D46-0E42-AC68-08019D845E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9D0CDC-6962-CA41-9F77-944906F846C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5040" yWindow="600" windowWidth="23760" windowHeight="14620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Lookup Tables" sheetId="8" r:id="rId1"/>
+    <sheet name="Lookup Tables" sheetId="8" state="hidden" r:id="rId1"/>
     <sheet name="Accounts" sheetId="4" r:id="rId2"/>
     <sheet name="Net Worth MoM" sheetId="2" r:id="rId3"/>
     <sheet name="Mortgage" sheetId="1" r:id="rId4"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="316">
   <si>
     <t>I captured data at month end balances</t>
   </si>
@@ -969,12 +969,6 @@
     <t>Etta</t>
   </si>
   <si>
-    <t>Subtype</t>
-  </si>
-  <si>
-    <t>Account Type Lookup</t>
-  </si>
-  <si>
     <t>Trust</t>
   </si>
   <si>
@@ -1015,6 +1009,9 @@
   </si>
   <si>
     <t>RSU</t>
+  </si>
+  <si>
+    <t>Account Type Group</t>
   </si>
 </sst>
 </file>
@@ -1483,8 +1480,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{23417DED-0198-6143-B962-A0F5AD48A263}" name="Table3" displayName="Table3" ref="B2:C18" totalsRowShown="0" dataDxfId="8">
   <autoFilter ref="B2:C18" xr:uid="{EE18B4AB-3C31-074B-A1AF-5770971F7EB4}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6C8268AC-5A43-7348-9E49-D23B2435E709}" name="Subtype" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{D8D4C27C-BFF3-F042-8978-1BA496608353}" name="Account Type Lookup" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{6C8268AC-5A43-7348-9E49-D23B2435E709}" name="Account Type" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{D8D4C27C-BFF3-F042-8978-1BA496608353}" name="Account Type Group" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1812,10 +1809,10 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>301</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="17" x14ac:dyDescent="0.2">
@@ -1828,7 +1825,7 @@
     </row>
     <row r="4" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B4" s="38" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>3</v>
@@ -1836,7 +1833,7 @@
     </row>
     <row r="5" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B5" s="38" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>3</v>
@@ -1844,7 +1841,7 @@
     </row>
     <row r="6" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B6" s="38" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>5</v>
@@ -1852,7 +1849,7 @@
     </row>
     <row r="7" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B7" s="38" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>5</v>
@@ -1860,7 +1857,7 @@
     </row>
     <row r="8" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B8" s="38" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>5</v>
@@ -1868,7 +1865,7 @@
     </row>
     <row r="9" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B9" s="38" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C9" s="38" t="s">
         <v>5</v>
@@ -1876,7 +1873,7 @@
     </row>
     <row r="10" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B10" s="38" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C10" s="38" t="s">
         <v>5</v>
@@ -1884,7 +1881,7 @@
     </row>
     <row r="11" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B11" s="38" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>5</v>
@@ -1892,7 +1889,7 @@
     </row>
     <row r="12" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B12" s="38" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C12" s="38" t="s">
         <v>5</v>
@@ -1900,7 +1897,7 @@
     </row>
     <row r="13" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B13" s="38" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C13" s="38" t="s">
         <v>5</v>
@@ -1908,7 +1905,7 @@
     </row>
     <row r="14" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B14" s="38" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C14" s="38" t="s">
         <v>5</v>
@@ -1927,20 +1924,20 @@
         <v>529</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B17" s="38" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" x14ac:dyDescent="0.2">
       <c r="B18" s="38" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>3</v>
@@ -1994,7 +1991,7 @@
         <v>38</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D4" s="41" t="s">
         <v>45</v>

--- a/core/sample-data/Financial Template.xlsx
+++ b/core/sample-data/Financial Template.xlsx
@@ -3,18 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10419"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9D0CDC-6962-CA41-9F77-944906F846C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0F40E3-EB00-1741-8493-F736B051B236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5040" yWindow="600" windowWidth="23760" windowHeight="14620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4300" yWindow="1540" windowWidth="23760" windowHeight="14620" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lookup Tables" sheetId="8" state="hidden" r:id="rId1"/>
     <sheet name="Accounts" sheetId="4" r:id="rId2"/>
     <sheet name="Net Worth MoM" sheetId="2" r:id="rId3"/>
-    <sheet name="Mortgage" sheetId="1" r:id="rId4"/>
-    <sheet name="Education Savings" sheetId="7" r:id="rId5"/>
-    <sheet name="Brokerage Ledger" sheetId="3" r:id="rId6"/>
-    <sheet name="TICKERS" sheetId="5" r:id="rId7"/>
+    <sheet name="Budget" sheetId="9" r:id="rId4"/>
+    <sheet name="Mortgage" sheetId="1" r:id="rId5"/>
+    <sheet name="Education Savings" sheetId="7" r:id="rId6"/>
+    <sheet name="Brokerage Ledger" sheetId="3" r:id="rId7"/>
+    <sheet name="TICKERS" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="APR">#REF!</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="342">
   <si>
     <t>I captured data at month end balances</t>
   </si>
@@ -1012,18 +1013,97 @@
   </si>
   <si>
     <t>Account Type Group</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Emergency '25</t>
+  </si>
+  <si>
+    <t>Emergency OB</t>
+  </si>
+  <si>
+    <t>Dividend Stocks</t>
+  </si>
+  <si>
+    <t>Growth Stocks '25</t>
+  </si>
+  <si>
+    <t>'25 RSUs</t>
+  </si>
+  <si>
+    <t>Investment Reserve</t>
+  </si>
+  <si>
+    <t>WWW OB</t>
+  </si>
+  <si>
+    <t>'25 Cash Bonus</t>
+  </si>
+  <si>
+    <t>Annual OB</t>
+  </si>
+  <si>
+    <t>Travel OB</t>
+  </si>
+  <si>
+    <t>Whatever We Want '25</t>
+  </si>
+  <si>
+    <t>Property Taxes</t>
+  </si>
+  <si>
+    <t>Income Taxes</t>
+  </si>
+  <si>
+    <t>Auto Registrations</t>
+  </si>
+  <si>
+    <t>HOA + Assessment</t>
+  </si>
+  <si>
+    <t>Lila Graduation</t>
+  </si>
+  <si>
+    <t>Ski Trip</t>
+  </si>
+  <si>
+    <t>Kaui</t>
+  </si>
+  <si>
+    <t>Summer Trip(s)</t>
+  </si>
+  <si>
+    <t>Volleyball '26</t>
+  </si>
+  <si>
+    <t>Spring Break '27 Deposit</t>
+  </si>
+  <si>
+    <t>10 Year Mortgage Plan</t>
+  </si>
+  <si>
+    <t>Unallocated</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="m/d/yy;@"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="\(\$#,##0.00\);\(\$#,##0.00\)"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -1222,7 +1302,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1292,6 +1372,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3377,6 +3458,301 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13E04C96-37C6-B843-8490-73D3F2BBF169}">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="B2:D26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="41"/>
+    <col min="2" max="2" width="24" style="41" customWidth="1"/>
+    <col min="3" max="3" width="26" style="41" customWidth="1"/>
+    <col min="4" max="4" width="14" style="41" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="41"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B2" s="41" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>317</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B3" s="41" t="s">
+        <v>319</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>320</v>
+      </c>
+      <c r="D3" s="45">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="45">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5" s="41" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="45">
+        <v>26500</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B6" s="41" t="s">
+        <v>322</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="45">
+        <v>537000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" s="41" t="s">
+        <v>323</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="45">
+        <v>9700</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B8" s="41" t="s">
+        <v>323</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>324</v>
+      </c>
+      <c r="D8" s="45">
+        <v>48500</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" s="41" t="s">
+        <v>323</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>325</v>
+      </c>
+      <c r="D9" s="45">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B10" s="41" t="s">
+        <v>324</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="45">
+        <v>48500</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B11" s="41" t="s">
+        <v>326</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="D11" s="45">
+        <v>30700</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B12" s="41" t="s">
+        <v>326</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="D12" s="45">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B13" s="41" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>325</v>
+      </c>
+      <c r="D13" s="45">
+        <v>38200</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B14" s="41" t="s">
+        <v>329</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>325</v>
+      </c>
+      <c r="D14" s="45">
+        <v>61200</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>330</v>
+      </c>
+      <c r="D15" s="45">
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="D16" s="45">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>332</v>
+      </c>
+      <c r="D17" s="45">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>333</v>
+      </c>
+      <c r="D18" s="45">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="41" t="s">
+        <v>327</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>334</v>
+      </c>
+      <c r="D19" s="45">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>335</v>
+      </c>
+      <c r="D20" s="45">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>336</v>
+      </c>
+      <c r="D21" s="45">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>337</v>
+      </c>
+      <c r="D22" s="45">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>338</v>
+      </c>
+      <c r="D23" s="45">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>339</v>
+      </c>
+      <c r="D24" s="45">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="41" t="s">
+        <v>325</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>340</v>
+      </c>
+      <c r="D25" s="45">
+        <v>38400</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="41" t="s">
+        <v>325</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>341</v>
+      </c>
+      <c r="D26" s="45">
+        <v>80100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
@@ -3443,7 +3819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB0E85D-0232-5647-9A75-FF64DBBA5AC5}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -5342,7 +5718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -8771,7 +9147,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>

--- a/core/sample-data/Financial Template.xlsx
+++ b/core/sample-data/Financial Template.xlsx
@@ -5404,7 +5404,7 @@
         <v>46753</v>
       </c>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
         <v>29</v>
       </c>
@@ -5470,8 +5470,9 @@
         <f t="shared" si="0"/>
         <v>-237500</v>
       </c>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S3" s="8"/>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
         <v>30</v>
       </c>
@@ -5538,8 +5539,9 @@
         <f t="shared" si="1"/>
         <v>58048.44776849994</v>
       </c>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S4" s="8"/>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
@@ -5606,8 +5608,9 @@
         <f t="shared" si="2"/>
         <v>155796.74166007648</v>
       </c>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S5" s="8"/>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
         <v>31</v>
       </c>
@@ -5674,8 +5677,9 @@
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S6" s="8"/>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
@@ -5742,8 +5746,9 @@
         <f t="shared" si="4"/>
         <v>290242.2388424996</v>
       </c>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S7" s="8"/>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
         <v>32</v>
       </c>
@@ -5795,8 +5800,9 @@
       <c r="R8" s="12">
         <v>500000</v>
       </c>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S8" s="8"/>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
         <v>33</v>
       </c>
@@ -5848,6 +5854,7 @@
       <c r="R9" s="11">
         <v>25000</v>
       </c>
+      <c r="S9" s="8"/>
     </row>
     <row r="10" hidden="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
@@ -6227,7 +6234,7 @@
       <c r="Q15" s="14"/>
       <c r="R15" s="14"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>40</v>
       </c>
@@ -6295,6 +6302,7 @@
         <f t="shared" si="9"/>
         <v>776587.4282710761</v>
       </c>
+      <c r="S16" s="8"/>
     </row>
     <row r="17" hidden="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
@@ -6431,7 +6439,7 @@
         <v>0.013502912141680742</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="19" ht="15" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>43</v>
       </c>
@@ -6499,6 +6507,7 @@
         <f t="shared" si="12"/>
         <v>0.22856594501886443</v>
       </c>
+      <c r="S19" s="8"/>
     </row>
     <row r="20" ht="15" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">

--- a/core/sample-data/Financial Template.xlsx
+++ b/core/sample-data/Financial Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5798CF62-5DC0-2E49-A1E7-89B4B94822CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A3E3CC-303C-0544-B546-1DB7D794352D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35500" yWindow="2560" windowWidth="29240" windowHeight="20480" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1054,9 +1054,6 @@
     <t>Open</t>
   </si>
   <si>
-    <t>Scenario 1</t>
-  </si>
-  <si>
     <t>Stop Working</t>
   </si>
   <si>
@@ -1130,6 +1127,9 @@
   </si>
   <si>
     <t>Contemporary Benefit Options</t>
+  </si>
+  <si>
+    <t>My Date of Birth</t>
   </si>
 </sst>
 </file>
@@ -1361,7 +1361,7 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1456,9 +1456,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="8" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4847,167 +4844,167 @@
       </c>
       <c r="H3" s="28">
         <f ca="1">G3+G3*(RAND()*(0.15--0.15)+-0.15)/12+$F3</f>
-        <v>20392.411880057309</v>
+        <v>20491.947602550688</v>
       </c>
       <c r="I3" s="28">
         <f t="shared" ref="I3:AV3" ca="1" si="0">H3+H3*(RAND()*(0.15--0.15)+-0.15)/12+$F3</f>
-        <v>20797.4649176692</v>
+        <v>20902.507959656436</v>
       </c>
       <c r="J3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>20953.925466696328</v>
+        <v>21425.539597105133</v>
       </c>
       <c r="K3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>21482.013178841702</v>
+        <v>21534.574526293818</v>
       </c>
       <c r="L3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22042.731449297411</v>
+        <v>21987.771675740132</v>
       </c>
       <c r="M3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22195.417016399806</v>
+        <v>22407.182656059886</v>
       </c>
       <c r="N3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22820.208727495141</v>
+        <v>22512.217045264071</v>
       </c>
       <c r="O3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>23436.603060924026</v>
+        <v>22645.020697695592</v>
       </c>
       <c r="P3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>23897.647955077708</v>
+        <v>22924.073629306564</v>
       </c>
       <c r="Q3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24158.639344833824</v>
+        <v>23080.511727433266</v>
       </c>
       <c r="R3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24323.829672371259</v>
+        <v>23288.34023969117</v>
       </c>
       <c r="S3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24957.906690250205</v>
+        <v>23710.350188747154</v>
       </c>
       <c r="T3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>25164.206887474484</v>
+        <v>23962.383060922693</v>
       </c>
       <c r="U3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>25285.093384200089</v>
+        <v>24173.699844108072</v>
       </c>
       <c r="V3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>25449.479848086423</v>
+        <v>24527.055394884777</v>
       </c>
       <c r="W3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>25576.488641655833</v>
+        <v>24955.528625360465</v>
       </c>
       <c r="X3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26044.036961238719</v>
+        <v>25515.647575758361</v>
       </c>
       <c r="Y3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26600.343189795869</v>
+        <v>25963.63087921363</v>
       </c>
       <c r="Z3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27277.353829348747</v>
+        <v>26501.914480607713</v>
       </c>
       <c r="AA3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27963.676044142649</v>
+        <v>26545.08587040189</v>
       </c>
       <c r="AB3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>28413.970013149246</v>
+        <v>26819.269734637728</v>
       </c>
       <c r="AC3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>28754.627117743257</v>
+        <v>26871.924857798378</v>
       </c>
       <c r="AD3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>29380.113919917079</v>
+        <v>27301.211311402367</v>
       </c>
       <c r="AE3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>29720.996737683057</v>
+        <v>27444.368657169231</v>
       </c>
       <c r="AF3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>30228.700068338381</v>
+        <v>28009.022156338178</v>
       </c>
       <c r="AG3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>30439.717352771971</v>
+        <v>28318.791501888139</v>
       </c>
       <c r="AH3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>30788.991221257362</v>
+        <v>28871.016607103909</v>
       </c>
       <c r="AI3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>31275.650276549677</v>
+        <v>29569.837202890485</v>
       </c>
       <c r="AJ3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>31738.054464860594</v>
+        <v>29966.260816794391</v>
       </c>
       <c r="AK3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>31804.162848059928</v>
+        <v>30652.517084434858</v>
       </c>
       <c r="AL3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>32121.850792901892</v>
+        <v>30968.223124698543</v>
       </c>
       <c r="AM3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>32250.630607000356</v>
+        <v>31493.777264280834</v>
       </c>
       <c r="AN3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>32685.530348760818</v>
+        <v>31593.782320319282</v>
       </c>
       <c r="AO3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>33314.028184080904</v>
+        <v>32004.780477113156</v>
       </c>
       <c r="AP3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>34028.753432483369</v>
+        <v>32645.340220509006</v>
       </c>
       <c r="AQ3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>34094.889245364262</v>
+        <v>32760.377500289353</v>
       </c>
       <c r="AR3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>34637.418563537358</v>
+        <v>33257.831270278213</v>
       </c>
       <c r="AS3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>35366.600981673109</v>
+        <v>33678.626144086775</v>
       </c>
       <c r="AT3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>35586.704490202377</v>
+        <v>33728.120120749125</v>
       </c>
       <c r="AU3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>36058.826354597753</v>
+        <v>33781.213539566656</v>
       </c>
       <c r="AV3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>36411.278175840154</v>
+        <v>34273.229168050442</v>
       </c>
       <c r="AW3" s="28"/>
       <c r="AX3" s="28"/>
@@ -5139,167 +5136,167 @@
       </c>
       <c r="H4" s="28">
         <f t="shared" ref="H4:AV4" ca="1" si="1">G4+G4*(RAND()*(0.15--0.15)+-0.15)/12+$F4</f>
-        <v>15011.787761683767</v>
+        <v>15024.243557942842</v>
       </c>
       <c r="I4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15080.273652502932</v>
+        <v>15047.680302915162</v>
       </c>
       <c r="J4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15353.083487146832</v>
+        <v>15066.016613665219</v>
       </c>
       <c r="K4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15630.241922627869</v>
+        <v>15238.145188909244</v>
       </c>
       <c r="L4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15972.086221231799</v>
+        <v>15564.208158530253</v>
       </c>
       <c r="M4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16256.805542371243</v>
+        <v>15890.832591790639</v>
       </c>
       <c r="N4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16433.994620703415</v>
+        <v>16124.127336034355</v>
       </c>
       <c r="O4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16448.081265803587</v>
+        <v>16265.430659134714</v>
       </c>
       <c r="P4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16563.426046864883</v>
+        <v>16409.578943523658</v>
       </c>
       <c r="Q4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16696.207419269464</v>
+        <v>16526.213344050982</v>
       </c>
       <c r="R4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16787.512816886625</v>
+        <v>16508.819437181111</v>
       </c>
       <c r="S4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16759.927283138299</v>
+        <v>16754.305258046759</v>
       </c>
       <c r="T4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16713.478198572568</v>
+        <v>16752.959284149281</v>
       </c>
       <c r="U4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16891.728642833441</v>
+        <v>16785.391777491401</v>
       </c>
       <c r="V4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17178.646155231905</v>
+        <v>17062.226331927151</v>
       </c>
       <c r="W4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17338.902959323881</v>
+        <v>17115.468396973731</v>
       </c>
       <c r="X4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17704.780705056084</v>
+        <v>17313.570488320962</v>
       </c>
       <c r="Y4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18065.959062605456</v>
+        <v>17377.122223751987</v>
       </c>
       <c r="Z4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18229.36403527252</v>
+        <v>17433.341314809692</v>
       </c>
       <c r="AA4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18598.623896069897</v>
+        <v>17630.780269951512</v>
       </c>
       <c r="AB4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18743.840474370572</v>
+        <v>17644.163175420748</v>
       </c>
       <c r="AC4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18960.524725726562</v>
+        <v>17925.655376371134</v>
       </c>
       <c r="AD4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19093.2844821135</v>
+        <v>17888.246261190172</v>
       </c>
       <c r="AE4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19110.266150466028</v>
+        <v>18002.612257836099</v>
       </c>
       <c r="AF4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19040.194602843447</v>
+        <v>17970.644701523986</v>
       </c>
       <c r="AG4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19095.357312593082</v>
+        <v>18333.761068899988</v>
       </c>
       <c r="AH4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19435.365275882592</v>
+        <v>18500.796504157199</v>
       </c>
       <c r="AI4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19448.977901115868</v>
+        <v>18834.764507814689</v>
       </c>
       <c r="AJ4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19814.566469156907</v>
+        <v>19051.293145658696</v>
       </c>
       <c r="AK4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19725.256116583801</v>
+        <v>19199.943657080927</v>
       </c>
       <c r="AL4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19934.492220575827</v>
+        <v>19185.096702506547</v>
       </c>
       <c r="AM4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19953.366733532839</v>
+        <v>19234.036417876854</v>
       </c>
       <c r="AN4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20208.511066593153</v>
+        <v>19144.259551770676</v>
       </c>
       <c r="AO4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20308.941285046149</v>
+        <v>19090.836481148293</v>
       </c>
       <c r="AP4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20345.419838869471</v>
+        <v>19283.98586738409</v>
       </c>
       <c r="AQ4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20480.910067091634</v>
+        <v>19576.663731057466</v>
       </c>
       <c r="AR4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20618.207917062333</v>
+        <v>19722.847111868574</v>
       </c>
       <c r="AS4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20966.86808163915</v>
+        <v>19918.168389599061</v>
       </c>
       <c r="AT4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>21311.016037310852</v>
+        <v>19914.405506634412</v>
       </c>
       <c r="AU4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>21668.000743342513</v>
+        <v>19878.347024753224</v>
       </c>
       <c r="AV4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>22005.211578971041</v>
+        <v>19808.465434189078</v>
       </c>
       <c r="AW4" s="28"/>
       <c r="AX4" s="28"/>
@@ -5431,167 +5428,167 @@
       </c>
       <c r="H5" s="28">
         <f t="shared" ref="H5:AV5" ca="1" si="2">G5+G5*(RAND()*(0.15--0.15)+-0.15)/12+$F5</f>
-        <v>10139.522302641428</v>
+        <v>10268.480075636538</v>
       </c>
       <c r="I5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10355.612267222825</v>
+        <v>10486.449902774073</v>
       </c>
       <c r="J5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10618.24061693699</v>
+        <v>10576.856461762511</v>
       </c>
       <c r="K5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10652.907378022495</v>
+        <v>10694.866101752903</v>
       </c>
       <c r="L5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10870.077388078</v>
+        <v>10974.29164096864</v>
       </c>
       <c r="M5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10948.202424249152</v>
+        <v>11061.021638090902</v>
       </c>
       <c r="N5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11102.267646265103</v>
+        <v>11100.116031244112</v>
       </c>
       <c r="O5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11236.813176039506</v>
+        <v>11193.701136352302</v>
       </c>
       <c r="P5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11423.967053390003</v>
+        <v>11378.156029239766</v>
       </c>
       <c r="Q5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11566.638301292296</v>
+        <v>11586.221924416606</v>
       </c>
       <c r="R5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11829.003695601225</v>
+        <v>11600.882043480191</v>
       </c>
       <c r="S5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12001.850691411291</v>
+        <v>11850.746258468276</v>
       </c>
       <c r="T5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12101.786815636948</v>
+        <v>11911.829429574263</v>
       </c>
       <c r="U5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12331.695694650361</v>
+        <v>12185.682127821003</v>
       </c>
       <c r="V5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12509.745066585401</v>
+        <v>12256.391293264538</v>
       </c>
       <c r="W5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12701.929194685961</v>
+        <v>12428.103006589266</v>
       </c>
       <c r="X5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12847.68477618446</v>
+        <v>12623.469758433232</v>
       </c>
       <c r="Y5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12931.986177161623</v>
+        <v>12905.184865066169</v>
       </c>
       <c r="Z5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12966.32442649236</v>
+        <v>12961.200861730738</v>
       </c>
       <c r="AA5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13046.460821570632</v>
+        <v>13267.124185345887</v>
       </c>
       <c r="AB5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13082.331981393801</v>
+        <v>13277.886968920729</v>
       </c>
       <c r="AC5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13260.816887415303</v>
+        <v>13390.515604140915</v>
       </c>
       <c r="AD5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13346.433402708966</v>
+        <v>13608.360795449686</v>
       </c>
       <c r="AE5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13440.231585736366</v>
+        <v>13735.587048207813</v>
       </c>
       <c r="AF5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13590.695000736583</v>
+        <v>14056.306147623876</v>
       </c>
       <c r="AG5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13640.11927941415</v>
+        <v>14093.038883907044</v>
       </c>
       <c r="AH5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13953.518736149997</v>
+        <v>14266.614402305846</v>
       </c>
       <c r="AI5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14213.58177522265</v>
+        <v>14585.679930115022</v>
       </c>
       <c r="AJ5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14367.737443106991</v>
+        <v>14720.933467296696</v>
       </c>
       <c r="AK5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14473.831347446361</v>
+        <v>14842.004038883451</v>
       </c>
       <c r="AL5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14784.190762741629</v>
+        <v>14994.810159229042</v>
       </c>
       <c r="AM5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14866.498903301419</v>
+        <v>15155.879153267351</v>
       </c>
       <c r="AN5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15035.005217012407</v>
+        <v>15286.713964322718</v>
       </c>
       <c r="AO5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15310.44002281513</v>
+        <v>15514.140236862597</v>
       </c>
       <c r="AP5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15364.422897799681</v>
+        <v>15591.062525610883</v>
       </c>
       <c r="AQ5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15496.475512338562</v>
+        <v>15824.660501848697</v>
       </c>
       <c r="AR5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15564.071923705982</v>
+        <v>15807.553793638737</v>
       </c>
       <c r="AS5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15695.475374811291</v>
+        <v>15924.989683121312</v>
       </c>
       <c r="AT5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15864.330043039177</v>
+        <v>16133.395281748501</v>
       </c>
       <c r="AU5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>16132.930782995754</v>
+        <v>16365.264822902811</v>
       </c>
       <c r="AV5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>16190.289184719963</v>
+        <v>16380.08257560359</v>
       </c>
       <c r="AW5" s="28"/>
       <c r="AX5" s="28"/>
@@ -7827,75 +7824,78 @@
   <dimension ref="A2:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21.1640625" style="64" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" style="63" customWidth="1"/>
     <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.83203125" style="64"/>
+    <col min="6" max="7" width="10.83203125" style="63"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B2"/>
-      <c r="C2" s="62" t="s">
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="B2" s="59" t="s">
         <v>331</v>
       </c>
-      <c r="D2" s="62"/>
+      <c r="C2" s="21">
+        <v>47908</v>
+      </c>
+      <c r="D2" s="57"/>
+      <c r="F2" s="69"/>
     </row>
     <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.2">
       <c r="B3" s="59" t="s">
         <v>332</v>
       </c>
       <c r="C3" s="21">
-        <v>47908</v>
-      </c>
-      <c r="D3" s="57"/>
-      <c r="F3" s="70"/>
+        <v>47939</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>333</v>
+      </c>
+      <c r="F3" s="69"/>
     </row>
     <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.2">
       <c r="B4" s="59" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="C4" s="21">
-        <v>47939</v>
-      </c>
-      <c r="D4" s="59" t="s">
-        <v>334</v>
-      </c>
-      <c r="F4" s="70"/>
+        <v>27722</v>
+      </c>
+      <c r="D4" s="59"/>
+      <c r="F4" s="69"/>
     </row>
     <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.2">
       <c r="B5" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="C5" t="s">
         <v>336</v>
       </c>
-      <c r="C5" t="s">
-        <v>337</v>
-      </c>
       <c r="D5" s="57"/>
-      <c r="F5" s="70"/>
+      <c r="F5" s="69"/>
     </row>
     <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.2">
       <c r="B6" s="59" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C6" s="21">
         <v>28515</v>
       </c>
       <c r="D6" s="57"/>
-      <c r="F6" s="70"/>
+      <c r="F6" s="69"/>
     </row>
     <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.2">
       <c r="B7" s="59" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C7" s="58">
         <v>0</v>
       </c>
       <c r="D7" s="57"/>
-      <c r="F7" s="70"/>
+      <c r="F7" s="69"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" s="59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C8" s="58">
         <v>0</v>
@@ -7904,98 +7904,98 @@
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="60"/>
       <c r="B10" s="59" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D10" s="59" t="s">
+        <v>340</v>
+      </c>
+      <c r="E10" s="59" t="s">
         <v>341</v>
       </c>
-      <c r="E10" s="59" t="s">
-        <v>342</v>
-      </c>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="60"/>
       <c r="B11" s="59" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D11" s="61">
         <v>660637.24</v>
       </c>
-      <c r="E11" s="63">
+      <c r="E11" s="62">
         <v>0</v>
       </c>
-      <c r="F11" s="68" t="s">
+      <c r="F11" s="67" t="s">
+        <v>352</v>
+      </c>
+      <c r="G11" s="67" t="s">
         <v>353</v>
       </c>
-      <c r="G11" s="68" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="B12" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="C12" s="60" t="s">
         <v>354</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="B12" s="65" t="s">
-        <v>344</v>
-      </c>
-      <c r="C12" s="60" t="s">
-        <v>355</v>
       </c>
       <c r="D12" s="61">
         <v>3815.64</v>
       </c>
-      <c r="E12" s="63">
+      <c r="E12" s="62">
         <v>0</v>
       </c>
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="67" t="s">
+        <v>344</v>
+      </c>
+      <c r="G12" s="67"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="65" t="s">
         <v>345</v>
       </c>
-      <c r="G12" s="68"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="66" t="s">
+      <c r="C13" s="60" t="s">
         <v>346</v>
-      </c>
-      <c r="C13" s="60" t="s">
-        <v>347</v>
       </c>
       <c r="D13" s="61">
         <v>5711.25</v>
       </c>
-      <c r="E13" s="63">
+      <c r="E13" s="62">
         <v>0</v>
       </c>
-      <c r="F13" s="68" t="s">
-        <v>345</v>
+      <c r="F13" s="67" t="s">
+        <v>344</v>
       </c>
       <c r="G13" s="21">
         <v>47939</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="66"/>
+      <c r="B14" s="65"/>
       <c r="C14" s="60" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D14" s="61">
         <v>2727.65</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="62">
         <v>0</v>
       </c>
-      <c r="F14" s="68" t="s">
-        <v>345</v>
-      </c>
-      <c r="G14" s="71">
+      <c r="F14" s="67" t="s">
+        <v>344</v>
+      </c>
+      <c r="G14" s="70">
         <v>50406</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="60"/>
-      <c r="B15" s="65" t="s">
-        <v>349</v>
+      <c r="B15" s="64" t="s">
+        <v>348</v>
       </c>
       <c r="C15" s="60" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D15" s="61">
         <v>3576.77</v>
@@ -8003,19 +8003,19 @@
       <c r="E15" s="61">
         <v>1948.65</v>
       </c>
-      <c r="F15" s="68" t="s">
-        <v>345</v>
+      <c r="F15" s="67" t="s">
+        <v>344</v>
       </c>
       <c r="G15" s="21">
         <v>47939</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="67" t="s">
-        <v>350</v>
+      <c r="B16" s="66" t="s">
+        <v>349</v>
       </c>
       <c r="C16" s="60" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D16" s="61">
         <v>5472.46</v>
@@ -8023,17 +8023,17 @@
       <c r="E16" s="61">
         <v>4333.99</v>
       </c>
-      <c r="F16" s="68" t="s">
-        <v>345</v>
+      <c r="F16" s="67" t="s">
+        <v>344</v>
       </c>
       <c r="G16" s="21">
         <v>47939</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="67"/>
+      <c r="B17" s="66"/>
       <c r="C17" s="60" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D17" s="61">
         <v>2488.86</v>
@@ -8041,19 +8041,19 @@
       <c r="E17" s="61">
         <v>1350.39</v>
       </c>
-      <c r="F17" s="68" t="s">
-        <v>345</v>
-      </c>
-      <c r="G17" s="71">
+      <c r="F17" s="67" t="s">
+        <v>344</v>
+      </c>
+      <c r="G17" s="70">
         <v>50406</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="B18" s="65" t="s">
-        <v>351</v>
+      <c r="B18" s="64" t="s">
+        <v>350</v>
       </c>
       <c r="C18" s="60" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D18" s="61">
         <v>3497.16</v>
@@ -8061,37 +8061,37 @@
       <c r="E18" s="61">
         <v>2622.87</v>
       </c>
-      <c r="F18" s="68" t="s">
-        <v>345</v>
+      <c r="F18" s="67" t="s">
+        <v>344</v>
       </c>
       <c r="G18" s="21">
         <v>47939</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="66" t="s">
-        <v>352</v>
+      <c r="B19" s="65" t="s">
+        <v>351</v>
       </c>
       <c r="C19" s="60" t="s">
-        <v>347</v>
-      </c>
-      <c r="D19" s="69">
+        <v>346</v>
+      </c>
+      <c r="D19" s="68">
         <v>5392.97</v>
       </c>
-      <c r="E19" s="69">
+      <c r="E19" s="68">
         <v>4790.63</v>
       </c>
-      <c r="F19" s="68" t="s">
-        <v>345</v>
+      <c r="F19" s="67" t="s">
+        <v>344</v>
       </c>
       <c r="G19" s="21">
         <v>47939</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="66"/>
+      <c r="B20" s="65"/>
       <c r="C20" s="60" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D20" s="61">
         <v>2409.37</v>
@@ -8099,27 +8099,27 @@
       <c r="E20" s="61">
         <v>1807.03</v>
       </c>
-      <c r="F20" s="68" t="s">
-        <v>345</v>
-      </c>
-      <c r="G20" s="71">
+      <c r="F20" s="67" t="s">
+        <v>344</v>
+      </c>
+      <c r="G20" s="70">
         <v>50406</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="65"/>
+      <c r="B21" s="64"/>
       <c r="C21" s="60"/>
       <c r="D21" s="61"/>
       <c r="E21" s="61"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B22" s="59" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C22" s="60" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D22" s="61">
         <v>28471.48</v>
@@ -8127,10 +8127,10 @@
       <c r="E22" s="61">
         <v>0</v>
       </c>
-      <c r="F22" s="68" t="s">
-        <v>353</v>
-      </c>
-      <c r="G22" s="71">
+      <c r="F22" s="67" t="s">
+        <v>352</v>
+      </c>
+      <c r="G22" s="70">
         <v>48106</v>
       </c>
     </row>
@@ -8138,8 +8138,8 @@
       <c r="C23" s="60"/>
       <c r="D23" s="60"/>
       <c r="E23" s="60"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/core/sample-data/Financial Template.xlsx
+++ b/core/sample-data/Financial Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A3E3CC-303C-0544-B546-1DB7D794352D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6E6403-DECD-934F-88C9-AD384AB2D95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35500" yWindow="2560" windowWidth="29240" windowHeight="20480" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4500" yWindow="2520" windowWidth="29240" windowHeight="20480" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lookup Tables" sheetId="8" state="hidden" r:id="rId1"/>
@@ -1361,7 +1361,7 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1472,7 +1472,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4844,167 +4843,167 @@
       </c>
       <c r="H3" s="28">
         <f ca="1">G3+G3*(RAND()*(0.15--0.15)+-0.15)/12+$F3</f>
-        <v>20491.947602550688</v>
+        <v>20233.509676520946</v>
       </c>
       <c r="I3" s="28">
         <f t="shared" ref="I3:AV3" ca="1" si="0">H3+H3*(RAND()*(0.15--0.15)+-0.15)/12+$F3</f>
-        <v>20902.507959656436</v>
+        <v>20813.907754952852</v>
       </c>
       <c r="J3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>21425.539597105133</v>
+        <v>21418.27715556257</v>
       </c>
       <c r="K3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>21534.574526293818</v>
+        <v>21936.23351090814</v>
       </c>
       <c r="L3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>21987.771675740132</v>
+        <v>22336.269127274471</v>
       </c>
       <c r="M3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22407.182656059886</v>
+        <v>22954.162232831026</v>
       </c>
       <c r="N3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22512.217045264071</v>
+        <v>23237.704532470194</v>
       </c>
       <c r="O3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22645.020697695592</v>
+        <v>23805.459502169746</v>
       </c>
       <c r="P3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22924.073629306564</v>
+        <v>23967.019923961958</v>
       </c>
       <c r="Q3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>23080.511727433266</v>
+        <v>24412.281034901782</v>
       </c>
       <c r="R3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>23288.34023969117</v>
+        <v>24555.462458468483</v>
       </c>
       <c r="S3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>23710.350188747154</v>
+        <v>24802.679078580371</v>
       </c>
       <c r="T3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>23962.383060922693</v>
+        <v>25060.184712523904</v>
       </c>
       <c r="U3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24173.699844108072</v>
+        <v>25189.042414649237</v>
       </c>
       <c r="V3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24527.055394884777</v>
+        <v>25852.6500107795</v>
       </c>
       <c r="W3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24955.528625360465</v>
+        <v>26073.881054185636</v>
       </c>
       <c r="X3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>25515.647575758361</v>
+        <v>26679.642743252487</v>
       </c>
       <c r="Y3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>25963.63087921363</v>
+        <v>27262.995387587984</v>
       </c>
       <c r="Z3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26501.914480607713</v>
+        <v>27372.969397689194</v>
       </c>
       <c r="AA3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26545.08587040189</v>
+        <v>27687.786392421218</v>
       </c>
       <c r="AB3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26819.269734637728</v>
+        <v>28005.032880487168</v>
       </c>
       <c r="AC3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26871.924857798378</v>
+        <v>28094.836605580582</v>
       </c>
       <c r="AD3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27301.211311402367</v>
+        <v>28369.295768096465</v>
       </c>
       <c r="AE3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27444.368657169231</v>
+        <v>28730.134070180357</v>
       </c>
       <c r="AF3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>28009.022156338178</v>
+        <v>29149.435294307437</v>
       </c>
       <c r="AG3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>28318.791501888139</v>
+        <v>29157.99554724558</v>
       </c>
       <c r="AH3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>28871.016607103909</v>
+        <v>29820.633232282209</v>
       </c>
       <c r="AI3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>29569.837202890485</v>
+        <v>29944.411067657344</v>
       </c>
       <c r="AJ3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>29966.260816794391</v>
+        <v>29975.355309175113</v>
       </c>
       <c r="AK3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>30652.517084434858</v>
+        <v>30302.059723691502</v>
       </c>
       <c r="AL3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>30968.223124698543</v>
+        <v>30526.80591966772</v>
       </c>
       <c r="AM3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>31493.777264280834</v>
+        <v>30756.574109276709</v>
       </c>
       <c r="AN3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>31593.782320319282</v>
+        <v>31178.533058024896</v>
       </c>
       <c r="AO3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>32004.780477113156</v>
+        <v>31229.110458821815</v>
       </c>
       <c r="AP3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>32645.340220509006</v>
+        <v>31403.988713789968</v>
       </c>
       <c r="AQ3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>32760.377500289353</v>
+        <v>31509.838737336253</v>
       </c>
       <c r="AR3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>33257.831270278213</v>
+        <v>31774.897287571795</v>
       </c>
       <c r="AS3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>33678.626144086775</v>
+        <v>32170.387137756297</v>
       </c>
       <c r="AT3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>33728.120120749125</v>
+        <v>32353.816477266195</v>
       </c>
       <c r="AU3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>33781.213539566656</v>
+        <v>32499.038892219451</v>
       </c>
       <c r="AV3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>34273.229168050442</v>
+        <v>32873.433373195716</v>
       </c>
       <c r="AW3" s="28"/>
       <c r="AX3" s="28"/>
@@ -5136,167 +5135,167 @@
       </c>
       <c r="H4" s="28">
         <f t="shared" ref="H4:AV4" ca="1" si="1">G4+G4*(RAND()*(0.15--0.15)+-0.15)/12+$F4</f>
-        <v>15024.243557942842</v>
+        <v>15085.604463657086</v>
       </c>
       <c r="I4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15047.680302915162</v>
+        <v>15340.027391093918</v>
       </c>
       <c r="J4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15066.016613665219</v>
+        <v>15596.354232185395</v>
       </c>
       <c r="K4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15238.145188909244</v>
+        <v>15868.234712572275</v>
       </c>
       <c r="L4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15564.208158530253</v>
+        <v>16206.564431110255</v>
       </c>
       <c r="M4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15890.832591790639</v>
+        <v>16539.578183106554</v>
       </c>
       <c r="N4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16124.127336034355</v>
+        <v>16663.438176064301</v>
       </c>
       <c r="O4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16265.430659134714</v>
+        <v>16686.106404598624</v>
       </c>
       <c r="P4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16409.578943523658</v>
+        <v>16656.649337753039</v>
       </c>
       <c r="Q4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16526.213344050982</v>
+        <v>16702.265119712523</v>
       </c>
       <c r="R4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16508.819437181111</v>
+        <v>17000.199785223616</v>
       </c>
       <c r="S4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16754.305258046759</v>
+        <v>17226.85887942541</v>
       </c>
       <c r="T4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16752.959284149281</v>
+        <v>17408.787877079623</v>
       </c>
       <c r="U4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16785.391777491401</v>
+        <v>17373.641077535704</v>
       </c>
       <c r="V4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17062.226331927151</v>
+        <v>17592.48616350671</v>
       </c>
       <c r="W4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17115.468396973731</v>
+        <v>17553.163205244742</v>
       </c>
       <c r="X4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17313.570488320962</v>
+        <v>17497.34942656444</v>
       </c>
       <c r="Y4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17377.122223751987</v>
+        <v>17802.813028573597</v>
       </c>
       <c r="Z4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17433.341314809692</v>
+        <v>17747.586221577581</v>
       </c>
       <c r="AA4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17630.780269951512</v>
+        <v>17895.143243445535</v>
       </c>
       <c r="AB4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17644.163175420748</v>
+        <v>17906.972559107937</v>
       </c>
       <c r="AC4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17925.655376371134</v>
+        <v>18025.251233216553</v>
       </c>
       <c r="AD4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17888.246261190172</v>
+        <v>18213.397290642093</v>
       </c>
       <c r="AE4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18002.612257836099</v>
+        <v>18541.187683563363</v>
       </c>
       <c r="AF4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17970.644701523986</v>
+        <v>18777.237998140834</v>
       </c>
       <c r="AG4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18333.761068899988</v>
+        <v>18996.217618558614</v>
       </c>
       <c r="AH4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18500.796504157199</v>
+        <v>19200.283589068404</v>
       </c>
       <c r="AI4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18834.764507814689</v>
+        <v>19561.24198871139</v>
       </c>
       <c r="AJ4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19051.293145658696</v>
+        <v>19786.138628991299</v>
       </c>
       <c r="AK4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19199.943657080927</v>
+        <v>19782.601263654746</v>
       </c>
       <c r="AL4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19185.096702506547</v>
+        <v>19832.154578996746</v>
       </c>
       <c r="AM4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19234.036417876854</v>
+        <v>19903.709883835458</v>
       </c>
       <c r="AN4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19144.259551770676</v>
+        <v>19929.60246421953</v>
       </c>
       <c r="AO4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19090.836481148293</v>
+        <v>19867.589835820312</v>
       </c>
       <c r="AP4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19283.98586738409</v>
+        <v>20003.213328563899</v>
       </c>
       <c r="AQ4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19576.663731057466</v>
+        <v>20216.256681978641</v>
       </c>
       <c r="AR4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19722.847111868574</v>
+        <v>20481.619207314921</v>
       </c>
       <c r="AS4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19918.168389599061</v>
+        <v>20546.359337495356</v>
       </c>
       <c r="AT4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19914.405506634412</v>
+        <v>20725.266099100918</v>
       </c>
       <c r="AU4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19878.347024753224</v>
+        <v>20632.966278801319</v>
       </c>
       <c r="AV4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19808.465434189078</v>
+        <v>20614.522438557316</v>
       </c>
       <c r="AW4" s="28"/>
       <c r="AX4" s="28"/>
@@ -5428,167 +5427,167 @@
       </c>
       <c r="H5" s="28">
         <f t="shared" ref="H5:AV5" ca="1" si="2">G5+G5*(RAND()*(0.15--0.15)+-0.15)/12+$F5</f>
-        <v>10268.480075636538</v>
+        <v>10245.22528916732</v>
       </c>
       <c r="I5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10486.449902774073</v>
+        <v>10484.108869554646</v>
       </c>
       <c r="J5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10576.856461762511</v>
+        <v>10616.605572014529</v>
       </c>
       <c r="K5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10694.866101752903</v>
+        <v>10645.626600890568</v>
       </c>
       <c r="L5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10974.29164096864</v>
+        <v>10905.898887982057</v>
       </c>
       <c r="M5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11061.021638090902</v>
+        <v>11023.79889179336</v>
       </c>
       <c r="N5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11100.116031244112</v>
+        <v>11230.159186639255</v>
       </c>
       <c r="O5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11193.701136352302</v>
+        <v>11333.09947814618</v>
       </c>
       <c r="P5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11378.156029239766</v>
+        <v>11436.190264459025</v>
       </c>
       <c r="Q5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11586.221924416606</v>
+        <v>11490.150067158938</v>
       </c>
       <c r="R5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11600.882043480191</v>
+        <v>11774.767213083784</v>
       </c>
       <c r="S5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11850.746258468276</v>
+        <v>12065.713516812988</v>
       </c>
       <c r="T5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11911.829429574263</v>
+        <v>12183.435915542525</v>
       </c>
       <c r="U5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12185.682127821003</v>
+        <v>12457.143262953785</v>
       </c>
       <c r="V5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12256.391293264538</v>
+        <v>12552.927623671507</v>
       </c>
       <c r="W5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12428.103006589266</v>
+        <v>12698.195748380083</v>
       </c>
       <c r="X5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12623.469758433232</v>
+        <v>12928.914812436606</v>
       </c>
       <c r="Y5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12905.184865066169</v>
+        <v>12953.592947523937</v>
       </c>
       <c r="Z5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12961.200861730738</v>
+        <v>12965.66209007838</v>
       </c>
       <c r="AA5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13267.124185345887</v>
+        <v>13258.561972932494</v>
       </c>
       <c r="AB5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13277.886968920729</v>
+        <v>13260.923931013273</v>
       </c>
       <c r="AC5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13390.515604140915</v>
+        <v>13529.762678980904</v>
       </c>
       <c r="AD5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13608.360795449686</v>
+        <v>13762.808959950247</v>
       </c>
       <c r="AE5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13735.587048207813</v>
+        <v>13874.533240896448</v>
       </c>
       <c r="AF5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14056.306147623876</v>
+        <v>13976.821768619784</v>
       </c>
       <c r="AG5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14093.038883907044</v>
+        <v>14228.396648873248</v>
       </c>
       <c r="AH5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14266.614402305846</v>
+        <v>14461.560838146253</v>
       </c>
       <c r="AI5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14585.679930115022</v>
+        <v>14753.64981962962</v>
       </c>
       <c r="AJ5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14720.933467296696</v>
+        <v>14944.961713197705</v>
       </c>
       <c r="AK5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14842.004038883451</v>
+        <v>15159.35576683816</v>
       </c>
       <c r="AL5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14994.810159229042</v>
+        <v>15392.981313346236</v>
       </c>
       <c r="AM5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15155.879153267351</v>
+        <v>15543.512388002453</v>
       </c>
       <c r="AN5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15286.713964322718</v>
+        <v>15789.943466819641</v>
       </c>
       <c r="AO5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15514.140236862597</v>
+        <v>15803.365464183214</v>
       </c>
       <c r="AP5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15591.062525610883</v>
+        <v>15811.601623467805</v>
       </c>
       <c r="AQ5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15824.660501848697</v>
+        <v>15903.013613883684</v>
       </c>
       <c r="AR5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15807.553793638737</v>
+        <v>15967.875662375305</v>
       </c>
       <c r="AS5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15924.989683121312</v>
+        <v>16162.458177815299</v>
       </c>
       <c r="AT5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>16133.395281748501</v>
+        <v>16430.983858656778</v>
       </c>
       <c r="AU5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>16365.264822902811</v>
+        <v>16588.974109293005</v>
       </c>
       <c r="AV5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>16380.08257560359</v>
+        <v>16589.917467997413</v>
       </c>
       <c r="AW5" s="28"/>
       <c r="AX5" s="28"/>
@@ -7821,7 +7820,7 @@
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="A2:G23"/>
+  <dimension ref="A2:I23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="21.1640625" style="63" customWidth="1"/>
@@ -7829,41 +7828,42 @@
     <col min="4" max="4" width="24.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="10.83203125" style="63"/>
+    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="B2" s="59" t="s">
         <v>331</v>
       </c>
       <c r="C2" s="21">
-        <v>47908</v>
+        <v>51561</v>
       </c>
       <c r="D2" s="57"/>
-      <c r="F2" s="69"/>
-    </row>
-    <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="F2" s="68"/>
+    </row>
+    <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="B3" s="59" t="s">
         <v>332</v>
       </c>
       <c r="C3" s="21">
-        <v>47939</v>
+        <v>51592</v>
       </c>
       <c r="D3" s="59" t="s">
         <v>333</v>
       </c>
-      <c r="F3" s="69"/>
-    </row>
-    <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="F3" s="68"/>
+    </row>
+    <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="B4" s="59" t="s">
         <v>356</v>
       </c>
       <c r="C4" s="21">
-        <v>27722</v>
+        <v>31375</v>
       </c>
       <c r="D4" s="59"/>
-      <c r="F4" s="69"/>
-    </row>
-    <row r="5" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="F4" s="68"/>
+    </row>
+    <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="B5" s="59" t="s">
         <v>335</v>
       </c>
@@ -7871,19 +7871,19 @@
         <v>336</v>
       </c>
       <c r="D5" s="57"/>
-      <c r="F5" s="69"/>
-    </row>
-    <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="F5" s="68"/>
+    </row>
+    <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="B6" s="59" t="s">
         <v>337</v>
       </c>
       <c r="C6" s="21">
-        <v>28515</v>
+        <v>32167</v>
       </c>
       <c r="D6" s="57"/>
-      <c r="F6" s="69"/>
-    </row>
-    <row r="7" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="F6" s="68"/>
+    </row>
+    <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.2">
       <c r="B7" s="59" t="s">
         <v>338</v>
       </c>
@@ -7891,9 +7891,9 @@
         <v>0</v>
       </c>
       <c r="D7" s="57"/>
-      <c r="F7" s="69"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F7" s="68"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8" s="59" t="s">
         <v>339</v>
       </c>
@@ -7901,7 +7901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="60"/>
       <c r="B10" s="59" t="s">
         <v>355</v>
@@ -7915,13 +7915,13 @@
       <c r="F10" s="67"/>
       <c r="G10" s="67"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="60"/>
       <c r="B11" s="59" t="s">
         <v>342</v>
       </c>
       <c r="D11" s="61">
-        <v>660637.24</v>
+        <v>220212.41333333333</v>
       </c>
       <c r="E11" s="62">
         <v>0</v>
@@ -7932,8 +7932,10 @@
       <c r="G11" s="67" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+    </row>
+    <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="64" t="s">
         <v>343</v>
       </c>
@@ -7941,7 +7943,7 @@
         <v>354</v>
       </c>
       <c r="D12" s="61">
-        <v>3815.64</v>
+        <v>1271.8799999999999</v>
       </c>
       <c r="E12" s="62">
         <v>0</v>
@@ -7950,8 +7952,10 @@
         <v>344</v>
       </c>
       <c r="G12" s="67"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="65" t="s">
         <v>345</v>
       </c>
@@ -7959,7 +7963,7 @@
         <v>346</v>
       </c>
       <c r="D13" s="61">
-        <v>5711.25</v>
+        <v>1903.75</v>
       </c>
       <c r="E13" s="62">
         <v>0</v>
@@ -7968,16 +7972,18 @@
         <v>344</v>
       </c>
       <c r="G13" s="21">
-        <v>47939</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>51592</v>
+      </c>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="65"/>
       <c r="C14" s="60" t="s">
         <v>347</v>
       </c>
       <c r="D14" s="61">
-        <v>2727.65</v>
+        <v>909.2166666666667</v>
       </c>
       <c r="E14" s="62">
         <v>0</v>
@@ -7985,11 +7991,13 @@
       <c r="F14" s="67" t="s">
         <v>344</v>
       </c>
-      <c r="G14" s="70">
-        <v>50406</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="G14" s="69">
+        <v>54058</v>
+      </c>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+    </row>
+    <row r="15" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="60"/>
       <c r="B15" s="64" t="s">
         <v>348</v>
@@ -7998,19 +8006,21 @@
         <v>354</v>
       </c>
       <c r="D15" s="61">
-        <v>3576.77</v>
+        <v>1192.2566666666667</v>
       </c>
       <c r="E15" s="61">
-        <v>1948.65</v>
+        <v>649.55000000000007</v>
       </c>
       <c r="F15" s="67" t="s">
         <v>344</v>
       </c>
       <c r="G15" s="21">
-        <v>47939</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51592</v>
+      </c>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+    </row>
+    <row r="16" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="66" t="s">
         <v>349</v>
       </c>
@@ -8018,37 +8028,41 @@
         <v>346</v>
       </c>
       <c r="D16" s="61">
-        <v>5472.46</v>
+        <v>1824.1533333333334</v>
       </c>
       <c r="E16" s="61">
-        <v>4333.99</v>
+        <v>1444.6633333333332</v>
       </c>
       <c r="F16" s="67" t="s">
         <v>344</v>
       </c>
       <c r="G16" s="21">
-        <v>47939</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+        <v>51592</v>
+      </c>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B17" s="66"/>
       <c r="C17" s="60" t="s">
         <v>347</v>
       </c>
       <c r="D17" s="61">
-        <v>2488.86</v>
+        <v>829.62</v>
       </c>
       <c r="E17" s="61">
-        <v>1350.39</v>
+        <v>450.13000000000005</v>
       </c>
       <c r="F17" s="67" t="s">
         <v>344</v>
       </c>
-      <c r="G17" s="70">
-        <v>50406</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="G17" s="69">
+        <v>54058</v>
+      </c>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+    </row>
+    <row r="18" spans="2:9" ht="32" x14ac:dyDescent="0.2">
       <c r="B18" s="64" t="s">
         <v>350</v>
       </c>
@@ -8056,65 +8070,73 @@
         <v>354</v>
       </c>
       <c r="D18" s="61">
-        <v>3497.16</v>
+        <v>1165.72</v>
       </c>
       <c r="E18" s="61">
-        <v>2622.87</v>
+        <v>874.29</v>
       </c>
       <c r="F18" s="67" t="s">
         <v>344</v>
       </c>
       <c r="G18" s="21">
-        <v>47939</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+        <v>51592</v>
+      </c>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="65" t="s">
         <v>351</v>
       </c>
       <c r="C19" s="60" t="s">
         <v>346</v>
       </c>
-      <c r="D19" s="68">
-        <v>5392.97</v>
-      </c>
-      <c r="E19" s="68">
-        <v>4790.63</v>
+      <c r="D19" s="61">
+        <v>1797.6566666666668</v>
+      </c>
+      <c r="E19" s="61">
+        <v>1596.8766666666668</v>
       </c>
       <c r="F19" s="67" t="s">
         <v>344</v>
       </c>
       <c r="G19" s="21">
-        <v>47939</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+        <v>51592</v>
+      </c>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="65"/>
       <c r="C20" s="60" t="s">
         <v>347</v>
       </c>
       <c r="D20" s="61">
-        <v>2409.37</v>
+        <v>803.12333333333333</v>
       </c>
       <c r="E20" s="61">
-        <v>1807.03</v>
+        <v>602.34333333333336</v>
       </c>
       <c r="F20" s="67" t="s">
         <v>344</v>
       </c>
-      <c r="G20" s="70">
-        <v>50406</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G20" s="69">
+        <v>54058</v>
+      </c>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B21" s="64"/>
       <c r="C21" s="60"/>
       <c r="D21" s="61"/>
       <c r="E21" s="61"/>
       <c r="F21" s="67"/>
       <c r="G21" s="67"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="59" t="s">
         <v>334</v>
       </c>
@@ -8122,7 +8144,7 @@
         <v>342</v>
       </c>
       <c r="D22" s="61">
-        <v>28471.48</v>
+        <v>0</v>
       </c>
       <c r="E22" s="61">
         <v>0</v>
@@ -8130,11 +8152,13 @@
       <c r="F22" s="67" t="s">
         <v>352</v>
       </c>
-      <c r="G22" s="70">
-        <v>48106</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="G22" s="69">
+        <v>51759</v>
+      </c>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C23" s="60"/>
       <c r="D23" s="60"/>
       <c r="E23" s="60"/>

--- a/core/sample-data/Financial Template.xlsx
+++ b/core/sample-data/Financial Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{06B00F92-76DC-D04B-8B88-2ABE60B49C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A9CA9B-94F0-564E-B405-6A37E7D98C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5820" yWindow="2240" windowWidth="29240" windowHeight="20480" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23120" yWindow="2260" windowWidth="29240" windowHeight="20480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lookup Tables" sheetId="8" state="hidden" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="Sankey" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -60,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="361">
   <si>
     <t>Account Type</t>
   </si>
@@ -122,9 +121,6 @@
     <t>Account</t>
   </si>
   <si>
-    <t>Account Type2</t>
-  </si>
-  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -1134,6 +1130,18 @@
   </si>
   <si>
     <t>ZSCALER INC COM</t>
+  </si>
+  <si>
+    <t>Account Name</t>
+  </si>
+  <si>
+    <t>Drew's Market</t>
+  </si>
+  <si>
+    <t>Shaua's Retirement</t>
+  </si>
+  <si>
+    <t>Jackson Health</t>
   </si>
 </sst>
 </file>
@@ -1149,9 +1157,16 @@
     <numFmt numFmtId="167" formatCode="\(\$#,##0.00\);\(\$#,##0.00\)"/>
     <numFmt numFmtId="168" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1350,117 +1365,121 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
     <dxf>
       <font>
         <b val="0"/>
@@ -1472,88 +1491,11 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Helvetica Neue"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
         <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Helvetica Neue"/>
-        <family val="2"/>
-        <scheme val="none"/>
+        <scheme val="minor"/>
       </font>
     </dxf>
     <dxf>
@@ -1717,6 +1659,26 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1754,6 +1716,44 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -1766,6 +1766,43 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Helvetica Neue"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1791,39 +1828,40 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table25" displayName="Table25" ref="B2:D5" headerRowCount="0">
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table25" displayName="Table25" ref="B2:E5" headerRowCount="0">
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Account"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Account Type2"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Owner"/>
+    <tableColumn id="4" xr3:uid="{C950A649-3BE5-1D49-9C22-1FC53E142931}" name="Column1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5F681B6E-186E-AB4D-BAC2-437CAFDB7002}" name="Table4" displayName="Table4" ref="B2:N41" totalsRowShown="0" headerRowDxfId="3" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5F681B6E-186E-AB4D-BAC2-437CAFDB7002}" name="Table4" displayName="Table4" ref="B2:N41" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="B2:N41" xr:uid="{5F681B6E-186E-AB4D-BAC2-437CAFDB7002}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{44ABB882-7907-0449-86C6-7D1EB2C6D90B}" name="Account" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{EF66979F-FA5D-AA49-B22C-9781D72A6514}" name="Account Type" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{44ABB882-7907-0449-86C6-7D1EB2C6D90B}" name="Account" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{EF66979F-FA5D-AA49-B22C-9781D72A6514}" name="Account Type" dataDxfId="12">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E3EAC05B-E30E-E24D-8C0B-E876FF67B7FC}" name="Owner" dataDxfId="1">
+    <tableColumn id="3" xr3:uid="{E3EAC05B-E30E-E24D-8C0B-E876FF67B7FC}" name="Owner" dataDxfId="11">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{348190E8-36F8-3D4E-AEDF-D62ABC8778D3}" name="Transaction" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{08380172-5D03-D34B-879F-2A6B96A894FA}" name="Symbol" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{2069EC4A-30DE-3241-93CB-213CCCB8C6B4}" name="Security Description" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{348190E8-36F8-3D4E-AEDF-D62ABC8778D3}" name="Transaction" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{08380172-5D03-D34B-879F-2A6B96A894FA}" name="Symbol" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{2069EC4A-30DE-3241-93CB-213CCCB8C6B4}" name="Security Description" dataDxfId="8">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8A722796-0EBD-404D-A4B5-8BBD14003108}" name="Date Acquired" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{DE2BC68E-9090-4E42-91E9-B347D59F0AEA}" name="Shares Bought" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{39330DF2-9948-5E49-B158-7E8529E815AF}" name="Cost Basis Per Share" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{FAD33138-0C6D-2246-AA81-68BA16CCB53A}" name="Date Sold" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{3E748A03-6922-7042-8C8A-59DD20A9C3D3}" name="Charitable Donation" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{51498472-466A-A946-AD11-9B62C566F1E9}" name="Shares Sold" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{919FF199-7CD0-7847-80E2-30B6FDE4BB78}" name="Sell Basis Per Share" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{8A722796-0EBD-404D-A4B5-8BBD14003108}" name="Date Acquired" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{DE2BC68E-9090-4E42-91E9-B347D59F0AEA}" name="Shares Bought" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{39330DF2-9948-5E49-B158-7E8529E815AF}" name="Cost Basis Per Share" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{FAD33138-0C6D-2246-AA81-68BA16CCB53A}" name="Date Sold" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{3E748A03-6922-7042-8C8A-59DD20A9C3D3}" name="Charitable Donation" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{51498472-466A-A946-AD11-9B62C566F1E9}" name="Shares Sold" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{919FF199-7CD0-7847-80E2-30B6FDE4BB78}" name="Sell Basis Per Share" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2298,16 +2336,16 @@
   <sheetData>
     <row r="2" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="G2" s="18">
         <v>200000</v>
@@ -2315,16 +2353,16 @@
     </row>
     <row r="3" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D3" s="19">
         <v>20000</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" s="18">
         <v>25000</v>
@@ -2332,16 +2370,16 @@
     </row>
     <row r="4" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="D4" s="19">
         <v>10000</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" s="18">
         <v>2500</v>
@@ -2349,17 +2387,17 @@
     </row>
     <row r="5" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" s="19">
         <f>(G4+2000)*12</f>
         <v>54000</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5" s="2">
         <v>2</v>
@@ -2367,10 +2405,10 @@
     </row>
     <row r="6" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" s="19">
         <v>5000</v>
@@ -2378,10 +2416,10 @@
     </row>
     <row r="7" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" s="19">
         <f>G2-SUM(D5:D6)</f>
@@ -2390,10 +2428,10 @@
     </row>
     <row r="8" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="D8" s="19">
         <f>(250*G5)*12</f>
@@ -2402,10 +2440,10 @@
     </row>
     <row r="9" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" s="19">
         <v>10000</v>
@@ -2413,10 +2451,10 @@
     </row>
     <row r="10" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10" s="19">
         <v>12000</v>
@@ -2424,10 +2462,10 @@
     </row>
     <row r="11" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="19">
         <f>D7-SUM(D8:D10,D12)</f>
@@ -2436,10 +2474,10 @@
     </row>
     <row r="12" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2">
         <v>5000</v>
@@ -2468,100 +2506,113 @@
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="B2:D18"/>
+  <dimension ref="B2:E18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
     <col min="2" max="3" width="14.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="2"/>
+    <col min="5" max="5" width="13.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="61" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="5" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="62" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="5" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="62" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="5" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="E5" s="62" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="5"/>
       <c r="C6" s="6"/>
     </row>
-    <row r="7" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="5"/>
       <c r="C7" s="6"/>
     </row>
-    <row r="8" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
     </row>
-    <row r="9" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
     </row>
-    <row r="10" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
     </row>
-    <row r="12" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
     </row>
-    <row r="13" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
     </row>
-    <row r="14" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
     </row>
-    <row r="15" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="7"/>
       <c r="C15" s="6"/>
     </row>
-    <row r="16" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="7"/>
       <c r="C16" s="6"/>
     </row>
@@ -2598,7 +2649,7 @@
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.2">
@@ -2716,7 +2767,7 @@
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="11">
         <v>-300000</v>
@@ -2783,7 +2834,7 @@
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B4" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" s="11">
         <v>50000</v>
@@ -2919,7 +2970,7 @@
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="11">
         <v>10000</v>
@@ -3055,7 +3106,7 @@
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B8" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="12">
         <v>500000</v>
@@ -3108,7 +3159,7 @@
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B9" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="11">
         <v>25000</v>
@@ -3161,7 +3212,7 @@
     </row>
     <row r="10" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
       <c r="B10" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="14" t="e">
         <f>#REF!-C3</f>
@@ -3224,7 +3275,7 @@
     </row>
     <row r="11" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
       <c r="B11" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="14" t="e">
         <f>C4-#REF!</f>
@@ -3287,7 +3338,7 @@
     </row>
     <row r="12" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
       <c r="B12" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="14" t="e">
         <f>C5-#REF!</f>
@@ -3350,7 +3401,7 @@
     </row>
     <row r="13" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
       <c r="B13" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" s="14" t="e">
         <f>C6-#REF!</f>
@@ -3413,7 +3464,7 @@
     </row>
     <row r="14" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
       <c r="B14" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="14" t="e">
         <f>C7-#REF!</f>
@@ -3476,7 +3527,7 @@
     </row>
     <row r="15" spans="1:39" hidden="1" x14ac:dyDescent="0.2">
       <c r="B15" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="14" t="e">
         <f>C9-#REF!</f>
@@ -3539,7 +3590,7 @@
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B16" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="16">
         <f t="shared" ref="C16:F16" si="8">SUM(C3:C8)</f>
@@ -3608,7 +3659,7 @@
     </row>
     <row r="17" spans="2:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="B17" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" s="16" t="e">
         <f>C16-#REF!</f>
@@ -3677,7 +3728,7 @@
     </row>
     <row r="18" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17">
@@ -3743,7 +3794,7 @@
     </row>
     <row r="19" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" s="17">
         <f t="shared" ref="C19:R19" si="12">-C3/SUM(C4:C9)</f>
@@ -3812,7 +3863,7 @@
     </row>
     <row r="20" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" s="17">
         <f t="shared" ref="C20:R20" si="13">C4/C5</f>
@@ -3908,16 +3959,16 @@
   <sheetData>
     <row r="2" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="G2" s="18">
         <v>100000</v>
@@ -3925,16 +3976,16 @@
     </row>
     <row r="3" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D3" s="19">
         <v>20000</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" s="18">
         <v>25000</v>
@@ -3942,16 +3993,16 @@
     </row>
     <row r="4" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="D4" s="19">
         <v>10000</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" s="18">
         <v>2500</v>
@@ -3959,17 +4010,17 @@
     </row>
     <row r="5" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" s="19">
         <f>(G4+2000)*12</f>
         <v>54000</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5" s="2">
         <v>2</v>
@@ -3977,10 +4028,10 @@
     </row>
     <row r="6" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" s="19">
         <v>5000</v>
@@ -3988,10 +4039,10 @@
     </row>
     <row r="7" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" s="19">
         <f>G2-SUM(D5:D6)</f>
@@ -4000,10 +4051,10 @@
     </row>
     <row r="8" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="D8" s="19">
         <f>(250*G5)*12</f>
@@ -4012,10 +4063,10 @@
     </row>
     <row r="9" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" s="19">
         <v>10000</v>
@@ -4023,10 +4074,10 @@
     </row>
     <row r="10" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10" s="19">
         <v>12000</v>
@@ -4034,10 +4085,10 @@
     </row>
     <row r="11" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="19">
         <f>D7-SUM(D8:D10,D12)</f>
@@ -4046,10 +4097,10 @@
     </row>
     <row r="12" spans="2:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2">
         <v>5000</v>
@@ -4088,15 +4139,15 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
         <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" s="20">
         <v>400000</v>
@@ -4104,7 +4155,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" s="21">
         <v>45139</v>
@@ -4112,7 +4163,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -4120,7 +4171,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" s="17">
         <v>0.06</v>
@@ -4128,7 +4179,7 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" s="22">
         <f>PMT(C6/12,C5*12,C3)</f>
@@ -4234,7 +4285,7 @@
       <c r="AY1" s="23"/>
       <c r="AZ1" s="23"/>
       <c r="BA1" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BB1" s="23"/>
       <c r="BC1" s="23"/>
@@ -4252,7 +4303,7 @@
       <c r="BO1" s="23"/>
       <c r="BP1" s="23"/>
       <c r="BQ1" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="BR1" s="23"/>
       <c r="BS1" s="23"/>
@@ -4278,7 +4329,7 @@
       <c r="CM1" s="23"/>
       <c r="CN1" s="23"/>
       <c r="CO1" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="CP1" s="23"/>
       <c r="CQ1" s="23"/>
@@ -4300,7 +4351,7 @@
       <c r="DG1" s="23"/>
       <c r="DH1" s="23"/>
       <c r="DI1" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="DJ1" s="23"/>
       <c r="DK1" s="23"/>
@@ -4343,25 +4394,25 @@
       <c r="EV1" s="23"/>
       <c r="EW1" s="23"/>
       <c r="EX1" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="EY1" s="23"/>
     </row>
     <row r="2" spans="2:155" x14ac:dyDescent="0.2">
       <c r="B2" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="D2" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="E2" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="F2" s="24" t="s">
         <v>76</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>77</v>
       </c>
       <c r="G2" s="25">
         <v>43831</v>
@@ -4813,7 +4864,7 @@
     </row>
     <row r="3" spans="2:155" x14ac:dyDescent="0.2">
       <c r="B3" s="23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" s="26">
         <v>25000</v>
@@ -4833,167 +4884,167 @@
       </c>
       <c r="H3" s="28">
         <f ca="1">G3+G3*(RAND()*(0.15--0.15)+-0.15)/12+$F3</f>
-        <v>20571.991925303639</v>
+        <v>20117.356134930607</v>
       </c>
       <c r="I3" s="28">
         <f t="shared" ref="I3:AV3" ca="1" si="0">H3+H3*(RAND()*(0.15--0.15)+-0.15)/12+$F3</f>
-        <v>21023.53594059703</v>
+        <v>20367.677199178364</v>
       </c>
       <c r="J3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>21610.924370207194</v>
+        <v>20552.956686156711</v>
       </c>
       <c r="K3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22008.464700280623</v>
+        <v>20743.851977740989</v>
       </c>
       <c r="L3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22589.55290804067</v>
+        <v>21010.778095958201</v>
       </c>
       <c r="M3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22851.902398356473</v>
+        <v>21396.323452180917</v>
       </c>
       <c r="N3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>23334.958673774647</v>
+        <v>21573.480740489027</v>
       </c>
       <c r="O3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>23732.79696020449</v>
+        <v>21771.74930572266</v>
       </c>
       <c r="P3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24279.806700881552</v>
+        <v>22161.813533197466</v>
       </c>
       <c r="Q3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24815.106676031031</v>
+        <v>22673.680705195551</v>
       </c>
       <c r="R3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24893.896575023031</v>
+        <v>22786.618948226187</v>
       </c>
       <c r="S3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>25324.973139046248</v>
+        <v>23305.370026858869</v>
       </c>
       <c r="T3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>25531.5290602319</v>
+        <v>23554.159424800568</v>
       </c>
       <c r="U3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>25620.43184558137</v>
+        <v>24172.584314163272</v>
       </c>
       <c r="V3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26083.260339481134</v>
+        <v>24604.842796100533</v>
       </c>
       <c r="W3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26528.218056848025</v>
+        <v>24840.302286863989</v>
       </c>
       <c r="X3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26985.554745760153</v>
+        <v>24946.299779818499</v>
       </c>
       <c r="Y3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27262.408805676223</v>
+        <v>25334.934979525624</v>
       </c>
       <c r="Z3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27325.234661937822</v>
+        <v>25549.636342336842</v>
       </c>
       <c r="AA3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27741.688763735692</v>
+        <v>25807.977035501062</v>
       </c>
       <c r="AB3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>28207.084302327916</v>
+        <v>26082.6347972861</v>
       </c>
       <c r="AC3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>28630.147013705824</v>
+        <v>26284.352104311671</v>
       </c>
       <c r="AD3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>29250.440623047616</v>
+        <v>26489.02897921699</v>
       </c>
       <c r="AE3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>29305.987101014678</v>
+        <v>26586.8422098745</v>
       </c>
       <c r="AF3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>29743.631482812147</v>
+        <v>26824.967799754439</v>
       </c>
       <c r="AG3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>30301.817977899078</v>
+        <v>26888.294196573122</v>
       </c>
       <c r="AH3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>30559.42516552427</v>
+        <v>27048.759315658564</v>
       </c>
       <c r="AI3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>31230.332412491389</v>
+        <v>27170.750588568135</v>
       </c>
       <c r="AJ3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>31362.543093537966</v>
+        <v>27484.432221067305</v>
       </c>
       <c r="AK3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>31944.036048750051</v>
+        <v>27629.582060297627</v>
       </c>
       <c r="AL3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>32351.03953645239</v>
+        <v>27668.117005595872</v>
       </c>
       <c r="AM3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>32416.414535472966</v>
+        <v>27928.465760652234</v>
       </c>
       <c r="AN3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>33121.360565392162</v>
+        <v>28525.46798290349</v>
       </c>
       <c r="AO3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>33693.296965906498</v>
+        <v>28608.021609271425</v>
       </c>
       <c r="AP3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>33629.785070916601</v>
+        <v>29204.93870489666</v>
       </c>
       <c r="AQ3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>33768.806844351326</v>
+        <v>29666.959557411272</v>
       </c>
       <c r="AR3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>34461.999972051541</v>
+        <v>29788.864235237033</v>
       </c>
       <c r="AS3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>34742.267675150069</v>
+        <v>30510.272062600809</v>
       </c>
       <c r="AT3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>35388.235031992495</v>
+        <v>30530.596049502037</v>
       </c>
       <c r="AU3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>35422.964531117177</v>
+        <v>30646.172057292708</v>
       </c>
       <c r="AV3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>35502.262689724725</v>
+        <v>30743.151896813062</v>
       </c>
       <c r="AW3" s="28"/>
       <c r="AX3" s="28"/>
@@ -5105,7 +5156,7 @@
     </row>
     <row r="4" spans="2:155" x14ac:dyDescent="0.2">
       <c r="B4" s="23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="26">
         <v>30000</v>
@@ -5125,167 +5176,167 @@
       </c>
       <c r="H4" s="28">
         <f t="shared" ref="H4:AV4" ca="1" si="1">G4+G4*(RAND()*(0.15--0.15)+-0.15)/12+$F4</f>
-        <v>15279.002738081201</v>
+        <v>14990.514361822292</v>
       </c>
       <c r="I4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15473.706152598825</v>
+        <v>15303.515598539934</v>
       </c>
       <c r="J4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15486.724030195106</v>
+        <v>15570.002437520176</v>
       </c>
       <c r="K4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15450.170856043966</v>
+        <v>15895.693363442066</v>
       </c>
       <c r="L4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15642.245923989858</v>
+        <v>15949.596743459635</v>
       </c>
       <c r="M4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15800.366855004126</v>
+        <v>15911.278602719756</v>
       </c>
       <c r="N4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15777.388024578866</v>
+        <v>15967.608564743297</v>
       </c>
       <c r="O4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15868.6482447626</v>
+        <v>16163.242040816329</v>
       </c>
       <c r="P4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15954.547196454265</v>
+        <v>16509.221610756773</v>
       </c>
       <c r="Q4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15994.802237114753</v>
+        <v>16690.513317076115</v>
       </c>
       <c r="R4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16083.632877075728</v>
+        <v>16947.759378320603</v>
       </c>
       <c r="S4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16095.975838381744</v>
+        <v>17173.580611338963</v>
       </c>
       <c r="T4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16403.842654128806</v>
+        <v>17218.850423594682</v>
       </c>
       <c r="U4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16505.984992088117</v>
+        <v>17324.20574614155</v>
       </c>
       <c r="V4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16745.554259447163</v>
+        <v>17263.511235520458</v>
       </c>
       <c r="W4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17029.311590962145</v>
+        <v>17431.901403158277</v>
       </c>
       <c r="X4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17202.699964748917</v>
+        <v>17715.953005465461</v>
       </c>
       <c r="Y4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17550.131978856221</v>
+        <v>17751.994231134446</v>
       </c>
       <c r="Z4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17899.330670939238</v>
+        <v>17804.510146460347</v>
       </c>
       <c r="AA4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17889.750212953753</v>
+        <v>18038.84211192797</v>
       </c>
       <c r="AB4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17911.841522200419</v>
+        <v>18072.946323573153</v>
       </c>
       <c r="AC4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17957.685078672497</v>
+        <v>18221.831831847008</v>
       </c>
       <c r="AD4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17929.644277360578</v>
+        <v>18222.866717377001</v>
       </c>
       <c r="AE4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18140.474527153638</v>
+        <v>18163.602482154438</v>
       </c>
       <c r="AF4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18295.83881328502</v>
+        <v>18303.060654507426</v>
       </c>
       <c r="AG4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18606.461689328178</v>
+        <v>18632.270464540157</v>
       </c>
       <c r="AH4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18856.331093916091</v>
+        <v>18840.555481564315</v>
       </c>
       <c r="AI4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19186.798496521533</v>
+        <v>18798.690311112234</v>
       </c>
       <c r="AJ4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19228.192304047738</v>
+        <v>19108.565167911365</v>
       </c>
       <c r="AK4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19414.418165899187</v>
+        <v>19342.831431992003</v>
       </c>
       <c r="AL4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19633.532834568636</v>
+        <v>19448.419115521945</v>
       </c>
       <c r="AM4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19612.632169880668</v>
+        <v>19822.31131725082</v>
       </c>
       <c r="AN4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19539.567905760661</v>
+        <v>20190.750901330965</v>
       </c>
       <c r="AO4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19574.634965905509</v>
+        <v>20528.74723105356</v>
       </c>
       <c r="AP4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19576.872335191318</v>
+        <v>20881.200349228533</v>
       </c>
       <c r="AQ4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19922.119472655275</v>
+        <v>21143.602323681265</v>
       </c>
       <c r="AR4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19859.88283294905</v>
+        <v>21069.136748310779</v>
       </c>
       <c r="AS4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20179.000449517647</v>
+        <v>21147.909605369896</v>
       </c>
       <c r="AT4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20390.321115115934</v>
+        <v>21081.708154760425</v>
       </c>
       <c r="AU4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20428.834007247919</v>
+        <v>21453.992765282692</v>
       </c>
       <c r="AV4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20401.036250133984</v>
+        <v>21370.555438131665</v>
       </c>
       <c r="AW4" s="28"/>
       <c r="AX4" s="28"/>
@@ -5397,7 +5448,7 @@
     </row>
     <row r="5" spans="2:155" x14ac:dyDescent="0.2">
       <c r="B5" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" s="26">
         <v>35000</v>
@@ -5417,167 +5468,167 @@
       </c>
       <c r="H5" s="28">
         <f t="shared" ref="H5:AV5" ca="1" si="2">G5+G5*(RAND()*(0.15--0.15)+-0.15)/12+$F5</f>
-        <v>10178.605309725779</v>
+        <v>10087.627167778086</v>
       </c>
       <c r="I5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10361.783185707869</v>
+        <v>10273.493950143817</v>
       </c>
       <c r="J5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10461.093655203469</v>
+        <v>10551.558684506475</v>
       </c>
       <c r="K5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10565.476363321786</v>
+        <v>10639.1988017531</v>
       </c>
       <c r="L5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10741.082958499339</v>
+        <v>10880.822376642365</v>
       </c>
       <c r="M5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11014.610011919043</v>
+        <v>11021.889949500601</v>
       </c>
       <c r="N5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11248.746463948948</v>
+        <v>11294.336887280104</v>
       </c>
       <c r="O5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11402.943710881345</v>
+        <v>11584.55520151016</v>
       </c>
       <c r="P5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11441.303487146482</v>
+        <v>11611.691710635147</v>
       </c>
       <c r="Q5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11625.778690953795</v>
+        <v>11772.758509926249</v>
       </c>
       <c r="R5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11909.991352512145</v>
+        <v>12024.48584604156</v>
       </c>
       <c r="S5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11940.277947916387</v>
+        <v>12232.078354020272</v>
       </c>
       <c r="T5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12046.900274936352</v>
+        <v>12366.002587887253</v>
       </c>
       <c r="U5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12250.504892680003</v>
+        <v>12473.622497122396</v>
       </c>
       <c r="V5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12318.637818095178</v>
+        <v>12707.867581664514</v>
       </c>
       <c r="W5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12315.907170431057</v>
+        <v>12808.976897866454</v>
       </c>
       <c r="X5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12433.074264548308</v>
+        <v>12883.889782245358</v>
       </c>
       <c r="Y5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12720.871235201292</v>
+        <v>12939.002617407057</v>
       </c>
       <c r="Z5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12997.582104616577</v>
+        <v>13149.976709210056</v>
       </c>
       <c r="AA5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13014.941996991651</v>
+        <v>13252.337682198513</v>
       </c>
       <c r="AB5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13019.512176103126</v>
+        <v>13415.574699112536</v>
       </c>
       <c r="AC5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13109.084149458264</v>
+        <v>13531.426684421504</v>
       </c>
       <c r="AD5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13303.999715940083</v>
+        <v>13837.653936907582</v>
       </c>
       <c r="AE5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13461.179946232789</v>
+        <v>14007.909083458004</v>
       </c>
       <c r="AF5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13720.849933867119</v>
+        <v>14109.207058344051</v>
       </c>
       <c r="AG5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13906.989873249568</v>
+        <v>14232.688000153963</v>
       </c>
       <c r="AH5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13904.865795147676</v>
+        <v>14252.696026832014</v>
       </c>
       <c r="AI5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13959.609370468044</v>
+        <v>14285.660464024359</v>
       </c>
       <c r="AJ5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13996.201765675969</v>
+        <v>14356.040567229265</v>
       </c>
       <c r="AK5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14114.718681216496</v>
+        <v>14673.079334271139</v>
       </c>
       <c r="AL5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14138.135589979562</v>
+        <v>14812.383575570388</v>
       </c>
       <c r="AM5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14382.3157028478</v>
+        <v>15055.518563347958</v>
       </c>
       <c r="AN5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14546.826265389403</v>
+        <v>15375.063954482406</v>
       </c>
       <c r="AO5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14632.506242690701</v>
+        <v>15547.836967662693</v>
       </c>
       <c r="AP5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14699.332877719016</v>
+        <v>15736.369010298533</v>
       </c>
       <c r="AQ5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14925.707741518001</v>
+        <v>15704.33272715183</v>
       </c>
       <c r="AR5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15019.848543547485</v>
+        <v>15917.876070124128</v>
       </c>
       <c r="AS5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15314.104250122913</v>
+        <v>16250.495148615362</v>
       </c>
       <c r="AT5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15523.494228831396</v>
+        <v>16540.36362805005</v>
       </c>
       <c r="AU5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15746.673582562533</v>
+        <v>16638.169523019613</v>
       </c>
       <c r="AV5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>16023.849730812421</v>
+        <v>16842.721735810104</v>
       </c>
       <c r="AW5" s="28"/>
       <c r="AX5" s="28"/>
@@ -6201,42 +6252,42 @@
         <v>0</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="G2" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="H2" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="I2" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="J2" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="J2" s="31" t="s">
+      <c r="K2" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="L2" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="L2" s="31" t="s">
+      <c r="M2" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="M2" s="31" t="s">
+      <c r="N2" s="31" t="s">
         <v>89</v>
-      </c>
-      <c r="N2" s="31" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="6" t="str" cm="1">
         <f t="array" ref="C3">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6247,10 +6298,10 @@
         <v>Drew</v>
       </c>
       <c r="E3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="G3" s="33" t="str" cm="1">
         <f t="array" ref="G3">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6277,7 +6328,7 @@
     </row>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="6" t="str" cm="1">
         <f t="array" ref="C4">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6288,10 +6339,10 @@
         <v>Drew</v>
       </c>
       <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="G4" s="33" t="str" cm="1">
         <f t="array" ref="G4">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6318,7 +6369,7 @@
     </row>
     <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="6" t="str" cm="1">
         <f t="array" ref="C5">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6329,10 +6380,10 @@
         <v>Drew</v>
       </c>
       <c r="E5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="G5" s="33" t="str" cm="1">
         <f t="array" ref="G5">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6359,7 +6410,7 @@
     </row>
     <row r="6" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="6" t="str" cm="1">
         <f t="array" ref="C6">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6370,10 +6421,10 @@
         <v>Drew</v>
       </c>
       <c r="E6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="G6" s="33" t="str" cm="1">
         <f t="array" ref="G6">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6400,7 +6451,7 @@
     </row>
     <row r="7" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="6" t="str" cm="1">
         <f t="array" ref="C7">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6411,10 +6462,10 @@
         <v>Drew</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G7" s="33" t="str" cm="1">
         <f t="array" ref="G7">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6432,12 +6483,12 @@
       <c r="K7" s="36"/>
       <c r="M7" s="6"/>
       <c r="N7" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="6" t="str" cm="1">
         <f t="array" ref="C8">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6448,10 +6499,10 @@
         <v>Drew</v>
       </c>
       <c r="E8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="G8" s="33" t="str" cm="1">
         <f t="array" ref="G8">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6478,7 +6529,7 @@
     </row>
     <row r="9" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="6" t="str" cm="1">
         <f t="array" ref="C9">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6489,10 +6540,10 @@
         <v>Drew</v>
       </c>
       <c r="E9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="G9" s="33" t="str" cm="1">
         <f t="array" ref="G9">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6511,7 +6562,7 @@
         <v>45415</v>
       </c>
       <c r="L9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M9" s="6">
         <v>4</v>
@@ -6522,7 +6573,7 @@
     </row>
     <row r="10" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="6" t="str" cm="1">
         <f t="array" ref="C10">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6533,10 +6584,10 @@
         <v>Drew</v>
       </c>
       <c r="E10" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="G10" s="33" t="str" cm="1">
         <f t="array" ref="G10">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6555,7 +6606,7 @@
         <v>45608</v>
       </c>
       <c r="L10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M10" s="6">
         <v>4</v>
@@ -6566,7 +6617,7 @@
     </row>
     <row r="11" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="6" t="str" cm="1">
         <f t="array" ref="C11">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6577,10 +6628,10 @@
         <v>Drew</v>
       </c>
       <c r="E11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="G11" s="33" t="str" cm="1">
         <f t="array" ref="G11">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6607,7 +6658,7 @@
     </row>
     <row r="12" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="6" t="str" cm="1">
         <f t="array" ref="C12">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6618,10 +6669,10 @@
         <v>Drew</v>
       </c>
       <c r="E12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G12" s="33" t="str" cm="1">
         <f t="array" ref="G12">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6639,12 +6690,12 @@
       <c r="K12" s="36"/>
       <c r="M12" s="6"/>
       <c r="N12" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="6" t="str" cm="1">
         <f t="array" ref="C13">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6655,10 +6706,10 @@
         <v>Drew</v>
       </c>
       <c r="E13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G13" s="33" t="str" cm="1">
         <f t="array" ref="G13">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6676,12 +6727,12 @@
       <c r="K13" s="36"/>
       <c r="M13" s="6"/>
       <c r="N13" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="6" t="str" cm="1">
         <f t="array" ref="C14">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6692,10 +6743,10 @@
         <v>Drew</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G14" s="33" t="str" cm="1">
         <f t="array" ref="G14">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6713,12 +6764,12 @@
       <c r="K14" s="38"/>
       <c r="M14" s="6"/>
       <c r="N14" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="6" t="str" cm="1">
         <f t="array" ref="C15">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6729,10 +6780,10 @@
         <v>Drew</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G15" s="33" t="str" cm="1">
         <f t="array" ref="G15">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6750,12 +6801,12 @@
       <c r="K15" s="38"/>
       <c r="M15" s="6"/>
       <c r="N15" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="6" t="str" cm="1">
         <f t="array" ref="C16">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6766,10 +6817,10 @@
         <v>Drew</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G16" s="33" t="str" cm="1">
         <f t="array" ref="G16">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6787,12 +6838,12 @@
       <c r="K16" s="38"/>
       <c r="M16" s="6"/>
       <c r="N16" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="6" t="str" cm="1">
         <f t="array" ref="C17">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6803,10 +6854,10 @@
         <v>Drew</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G17" s="33" t="str" cm="1">
         <f t="array" ref="G17">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6824,12 +6875,12 @@
       <c r="K17" s="38"/>
       <c r="M17" s="6"/>
       <c r="N17" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="6" t="str" cm="1">
         <f t="array" ref="C18">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6840,10 +6891,10 @@
         <v>Drew</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G18" s="33" t="str" cm="1">
         <f t="array" ref="G18">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6861,12 +6912,12 @@
       <c r="K18" s="38"/>
       <c r="M18" s="6"/>
       <c r="N18" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="6" t="str" cm="1">
         <f t="array" ref="C19">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6877,10 +6928,10 @@
         <v>Drew</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G19" s="33" t="str" cm="1">
         <f t="array" ref="G19">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6898,12 +6949,12 @@
       <c r="K19" s="38"/>
       <c r="M19" s="6"/>
       <c r="N19" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="6" t="str" cm="1">
         <f t="array" ref="C20">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6914,10 +6965,10 @@
         <v>Shaun</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G20" s="33" t="str" cm="1">
         <f t="array" ref="G20">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6945,7 +6996,7 @@
     </row>
     <row r="21" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="6" t="str" cm="1">
         <f t="array" ref="C21">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6956,10 +7007,10 @@
         <v>Shaun</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G21" s="33" t="str" cm="1">
         <f t="array" ref="G21">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6978,12 +7029,12 @@
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="6" t="str" cm="1">
         <f t="array" ref="C22">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -6994,10 +7045,10 @@
         <v>Shaun</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G22" s="33" t="str" cm="1">
         <f t="array" ref="G22">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7025,7 +7076,7 @@
     </row>
     <row r="23" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="6" t="str" cm="1">
         <f t="array" ref="C23">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7036,10 +7087,10 @@
         <v>Shaun</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G23" s="33" t="str" cm="1">
         <f t="array" ref="G23">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7058,12 +7109,12 @@
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="6" t="str" cm="1">
         <f t="array" ref="C24">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7074,10 +7125,10 @@
         <v>Shaun</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G24" s="33" t="str" cm="1">
         <f t="array" ref="G24">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7105,7 +7156,7 @@
     </row>
     <row r="25" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="6" t="str" cm="1">
         <f t="array" ref="C25">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7116,10 +7167,10 @@
         <v>Shaun</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G25" s="33" t="str" cm="1">
         <f t="array" ref="G25">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7138,12 +7189,12 @@
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" s="6" t="str" cm="1">
         <f t="array" ref="C26">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7154,10 +7205,10 @@
         <v>Shaun</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G26" s="33" t="str" cm="1">
         <f t="array" ref="G26">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7185,7 +7236,7 @@
     </row>
     <row r="27" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="6" t="str" cm="1">
         <f t="array" ref="C27">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7196,10 +7247,10 @@
         <v>Shaun</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G27" s="33" t="str" cm="1">
         <f t="array" ref="G27">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7218,12 +7269,12 @@
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" s="6" t="str" cm="1">
         <f t="array" ref="C28">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7234,10 +7285,10 @@
         <v>Shaun</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G28" s="33" t="str" cm="1">
         <f t="array" ref="G28">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7256,12 +7307,12 @@
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C29" s="6" t="str" cm="1">
         <f t="array" ref="C29">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7272,10 +7323,10 @@
         <v>Shaun</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G29" s="33" t="str" cm="1">
         <f t="array" ref="G29">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7294,12 +7345,12 @@
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="N29" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C30" s="6" t="str" cm="1">
         <f t="array" ref="C30">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7310,10 +7361,10 @@
         <v>Shaun</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G30" s="33" t="str" cm="1">
         <f t="array" ref="G30">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7332,12 +7383,12 @@
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" s="6" t="str" cm="1">
         <f t="array" ref="C31">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7348,10 +7399,10 @@
         <v>Shaun</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F31" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G31" s="33" t="str" cm="1">
         <f t="array" ref="G31">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7379,7 +7430,7 @@
     </row>
     <row r="32" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C32" s="6" t="str" cm="1">
         <f t="array" ref="C32">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7390,10 +7441,10 @@
         <v>Shaun</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F32" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G32" s="33" t="str" cm="1">
         <f t="array" ref="G32">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7412,12 +7463,12 @@
       <c r="L32" s="6"/>
       <c r="M32" s="42"/>
       <c r="N32" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C33" s="6" t="str" cm="1">
         <f t="array" ref="C33">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7428,10 +7479,10 @@
         <v>Shaun</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F33" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G33" s="33" t="str" cm="1">
         <f t="array" ref="G33">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7459,7 +7510,7 @@
     </row>
     <row r="34" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" s="6" t="str" cm="1">
         <f t="array" ref="C34">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7470,10 +7521,10 @@
         <v>Shaun</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F34" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G34" s="33" t="str" cm="1">
         <f t="array" ref="G34">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7492,12 +7543,12 @@
       <c r="L34" s="6"/>
       <c r="M34" s="42"/>
       <c r="N34" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C35" s="6" t="str" cm="1">
         <f t="array" ref="C35">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7508,10 +7559,10 @@
         <v>Shaun</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F35" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G35" s="33" t="str" cm="1">
         <f t="array" ref="G35">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7530,7 +7581,7 @@
         <v>45148</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M35" s="42">
         <v>2</v>
@@ -7541,7 +7592,7 @@
     </row>
     <row r="36" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C36" s="6" t="str" cm="1">
         <f t="array" ref="C36">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7552,10 +7603,10 @@
         <v>Shaun</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F36" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G36" s="33" t="str" cm="1">
         <f t="array" ref="G36">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7574,7 +7625,7 @@
         <v>45608</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M36" s="42">
         <v>5</v>
@@ -7585,7 +7636,7 @@
     </row>
     <row r="37" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" s="6" t="str" cm="1">
         <f t="array" ref="C37">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7596,10 +7647,10 @@
         <v>Shaun</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F37" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G37" s="33" t="str" cm="1">
         <f t="array" ref="G37">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7627,7 +7678,7 @@
     </row>
     <row r="38" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" s="6" t="str" cm="1">
         <f t="array" ref="C38">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7638,10 +7689,10 @@
         <v>Shaun</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F38" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G38" s="33" t="str" cm="1">
         <f t="array" ref="G38">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7669,7 +7720,7 @@
     </row>
     <row r="39" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" s="6" t="str" cm="1">
         <f t="array" ref="C39">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7680,10 +7731,10 @@
         <v>Shaun</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G39" s="33" t="str" cm="1">
         <f t="array" ref="G39">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7702,12 +7753,12 @@
       <c r="L39" s="6"/>
       <c r="M39" s="42"/>
       <c r="N39" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C40" s="6" t="str" cm="1">
         <f t="array" ref="C40">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7718,10 +7769,10 @@
         <v>Shaun</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F40" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G40" s="33" t="str" cm="1">
         <f t="array" ref="G40">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7740,12 +7791,12 @@
       <c r="L40" s="6"/>
       <c r="M40" s="42"/>
       <c r="N40" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" s="6" t="str" cm="1">
         <f t="array" ref="C41">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
@@ -7756,10 +7807,10 @@
         <v>Shaun</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F41" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G41" s="33" t="str" cm="1">
         <f t="array" ref="G41">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7778,7 +7829,7 @@
       <c r="L41" s="6"/>
       <c r="M41" s="42"/>
       <c r="N41" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -7807,13 +7858,13 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C2" s="44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D2" s="44"/>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C3" s="21">
         <v>47908</v>
@@ -7823,29 +7874,29 @@
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" s="21">
         <v>47939</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F4" s="47"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" t="s">
         <v>102</v>
-      </c>
-      <c r="C5" t="s">
-        <v>103</v>
       </c>
       <c r="D5" s="46"/>
       <c r="F5" s="47"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="45" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="21">
         <v>28515</v>
@@ -7855,7 +7906,7 @@
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -7865,7 +7916,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" s="45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" s="17">
         <v>0</v>
@@ -7873,7 +7924,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" s="48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="21">
         <v>27760</v>
@@ -7882,13 +7933,13 @@
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="49"/>
       <c r="B10" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="E10" s="45" t="s">
         <v>109</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>110</v>
       </c>
       <c r="F10" s="50"/>
       <c r="G10" s="50"/>
@@ -7896,7 +7947,7 @@
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="49"/>
       <c r="B11" s="45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D11" s="51">
         <v>660637.24</v>
@@ -7905,18 +7956,18 @@
         <v>0</v>
       </c>
       <c r="F11" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="50" t="s">
         <v>112</v>
-      </c>
-      <c r="G11" s="50" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="49" t="s">
         <v>114</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>115</v>
       </c>
       <c r="D12" s="51">
         <v>3815.64</v>
@@ -7925,16 +7976,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G12" s="50"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B13" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="49" t="s">
         <v>117</v>
-      </c>
-      <c r="C13" s="49" t="s">
-        <v>118</v>
       </c>
       <c r="D13" s="51">
         <v>5711.25</v>
@@ -7943,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G13" s="21">
         <v>47939</v>
@@ -7952,7 +8003,7 @@
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14" s="59"/>
       <c r="C14" s="49" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D14" s="51">
         <v>2727.65</v>
@@ -7961,7 +8012,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G14" s="53">
         <v>50406</v>
@@ -7970,10 +8021,10 @@
     <row r="15" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="49"/>
       <c r="B15" s="43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" s="51">
         <v>3576.77</v>
@@ -7982,7 +8033,7 @@
         <v>1948.65</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G15" s="21">
         <v>47939</v>
@@ -7990,10 +8041,10 @@
     </row>
     <row r="16" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="60" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D16" s="51">
         <v>5472.46</v>
@@ -8002,7 +8053,7 @@
         <v>4333.99</v>
       </c>
       <c r="F16" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G16" s="21">
         <v>47939</v>
@@ -8011,7 +8062,7 @@
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="60"/>
       <c r="C17" s="49" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D17" s="51">
         <v>2488.86</v>
@@ -8020,7 +8071,7 @@
         <v>1350.39</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G17" s="53">
         <v>50406</v>
@@ -8028,10 +8079,10 @@
     </row>
     <row r="18" spans="2:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="43" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D18" s="51">
         <v>3497.16</v>
@@ -8040,7 +8091,7 @@
         <v>2622.87</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G18" s="21">
         <v>47939</v>
@@ -8048,10 +8099,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="59" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D19" s="49">
         <v>5392.97</v>
@@ -8060,7 +8111,7 @@
         <v>4790.63</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G19" s="21">
         <v>47939</v>
@@ -8069,7 +8120,7 @@
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="59"/>
       <c r="C20" s="49" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D20" s="51">
         <v>2409.37</v>
@@ -8078,7 +8129,7 @@
         <v>1807.03</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G20" s="53">
         <v>50406</v>
@@ -8093,10 +8144,10 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B22" s="45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D22" s="51">
         <v>28471.48</v>
@@ -8105,7 +8156,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G22" s="53">
         <v>48106</v>
@@ -8144,978 +8195,978 @@
   <sheetData>
     <row r="2" spans="2:3" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="54" t="s">
         <v>82</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" s="55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" s="55" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="55" t="s">
         <v>126</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B5" s="55" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B7" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="55" t="s">
         <v>131</v>
-      </c>
-      <c r="C7" s="55" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B8" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>133</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B9" s="55" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="55" t="s">
         <v>135</v>
-      </c>
-      <c r="C9" s="55" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B10" s="55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B11" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="55" t="s">
         <v>138</v>
-      </c>
-      <c r="C11" s="55" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B12" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="55" t="s">
         <v>140</v>
-      </c>
-      <c r="C12" s="55" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B13" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="55" t="s">
         <v>142</v>
-      </c>
-      <c r="C13" s="55" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B14" s="55" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="55" t="s">
         <v>144</v>
-      </c>
-      <c r="C14" s="55" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B15" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" s="55" t="s">
         <v>146</v>
-      </c>
-      <c r="C15" s="55" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B16" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" s="55" t="s">
         <v>148</v>
-      </c>
-      <c r="C16" s="55" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" s="55" t="s">
         <v>150</v>
-      </c>
-      <c r="C17" s="55" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" s="55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="55" t="s">
         <v>153</v>
-      </c>
-      <c r="C19" s="55" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="55" t="s">
         <v>155</v>
-      </c>
-      <c r="C20" s="55" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" s="55" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="55" t="s">
         <v>157</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" s="55" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="55" t="s">
         <v>159</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="55" t="s">
+        <v>160</v>
+      </c>
+      <c r="C23" s="55" t="s">
         <v>161</v>
-      </c>
-      <c r="C23" s="55" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="55" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="55" t="s">
         <v>163</v>
-      </c>
-      <c r="C24" s="55" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="55" t="s">
         <v>165</v>
-      </c>
-      <c r="C25" s="55" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" s="55" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="55" t="s">
         <v>167</v>
-      </c>
-      <c r="C26" s="55" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B27" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" s="55" t="s">
         <v>169</v>
-      </c>
-      <c r="C27" s="55" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B28" s="55" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" s="55" t="s">
         <v>171</v>
-      </c>
-      <c r="C28" s="55" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B29" s="55" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" s="55" t="s">
         <v>173</v>
-      </c>
-      <c r="C29" s="55" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B30" s="55" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="55" t="s">
         <v>175</v>
-      </c>
-      <c r="C30" s="55" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B31" s="55" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" s="55" t="s">
         <v>177</v>
-      </c>
-      <c r="C31" s="55" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B32" s="55" t="s">
+        <v>178</v>
+      </c>
+      <c r="C32" s="55" t="s">
         <v>179</v>
-      </c>
-      <c r="C32" s="55" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B33" s="55" t="s">
+        <v>180</v>
+      </c>
+      <c r="C33" s="55" t="s">
         <v>181</v>
-      </c>
-      <c r="C33" s="55" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B34" s="55" t="s">
+        <v>182</v>
+      </c>
+      <c r="C34" s="55" t="s">
         <v>183</v>
-      </c>
-      <c r="C34" s="55" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B35" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="C35" s="55" t="s">
         <v>185</v>
-      </c>
-      <c r="C35" s="55" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B36" s="55" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" s="55" t="s">
         <v>187</v>
-      </c>
-      <c r="C36" s="55" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B37" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" s="55" t="s">
         <v>189</v>
-      </c>
-      <c r="C37" s="55" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B38" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="C38" s="55" t="s">
         <v>191</v>
-      </c>
-      <c r="C38" s="55" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B39" s="55" t="s">
+        <v>192</v>
+      </c>
+      <c r="C39" s="55" t="s">
         <v>193</v>
-      </c>
-      <c r="C39" s="55" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B40" s="55" t="s">
+        <v>194</v>
+      </c>
+      <c r="C40" s="55" t="s">
         <v>195</v>
-      </c>
-      <c r="C40" s="55" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B41" s="55" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" s="55" t="s">
         <v>197</v>
-      </c>
-      <c r="C41" s="55" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B42" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="C42" s="55" t="s">
         <v>199</v>
-      </c>
-      <c r="C42" s="55" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B43" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" s="55" t="s">
         <v>201</v>
-      </c>
-      <c r="C43" s="55" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B44" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="C44" s="55" t="s">
         <v>203</v>
-      </c>
-      <c r="C44" s="55" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B45" s="55" t="s">
+        <v>204</v>
+      </c>
+      <c r="C45" s="55" t="s">
         <v>205</v>
-      </c>
-      <c r="C45" s="55" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B46" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="C46" s="55" t="s">
         <v>207</v>
-      </c>
-      <c r="C46" s="55" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B47" s="55" t="s">
+        <v>208</v>
+      </c>
+      <c r="C47" s="55" t="s">
         <v>209</v>
-      </c>
-      <c r="C47" s="55" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B48" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="C48" s="55" t="s">
         <v>211</v>
-      </c>
-      <c r="C48" s="55" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B49" s="55" t="s">
+        <v>212</v>
+      </c>
+      <c r="C49" s="55" t="s">
         <v>213</v>
-      </c>
-      <c r="C49" s="55" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="C50" s="55" t="s">
         <v>215</v>
-      </c>
-      <c r="C50" s="55" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B51" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="C51" s="55" t="s">
         <v>217</v>
-      </c>
-      <c r="C51" s="55" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="55" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C52" s="55" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="55" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C53" s="57" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B54" s="55" t="s">
+        <v>219</v>
+      </c>
+      <c r="C54" s="55" t="s">
         <v>220</v>
-      </c>
-      <c r="C54" s="55" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="C55" s="55" t="s">
         <v>222</v>
-      </c>
-      <c r="C55" s="55" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="C56" s="55" t="s">
         <v>224</v>
-      </c>
-      <c r="C56" s="55" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B57" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="C57" s="55" t="s">
         <v>226</v>
-      </c>
-      <c r="C57" s="55" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="C58" s="55" t="s">
         <v>228</v>
-      </c>
-      <c r="C58" s="55" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="C59" s="55" t="s">
         <v>230</v>
-      </c>
-      <c r="C59" s="55" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="C60" s="55" t="s">
         <v>232</v>
-      </c>
-      <c r="C60" s="55" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="55" t="s">
+        <v>233</v>
+      </c>
+      <c r="C61" s="55" t="s">
         <v>234</v>
-      </c>
-      <c r="C61" s="55" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B62" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="C62" s="55" t="s">
         <v>236</v>
-      </c>
-      <c r="C62" s="55" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B63" s="55" t="s">
+        <v>237</v>
+      </c>
+      <c r="C63" s="55" t="s">
         <v>238</v>
-      </c>
-      <c r="C63" s="55" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="55" t="s">
+        <v>239</v>
+      </c>
+      <c r="C64" s="55" t="s">
         <v>240</v>
-      </c>
-      <c r="C64" s="55" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B65" s="55" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" s="55" t="s">
         <v>242</v>
-      </c>
-      <c r="C65" s="55" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B66" s="55" t="s">
+        <v>243</v>
+      </c>
+      <c r="C66" s="55" t="s">
         <v>244</v>
-      </c>
-      <c r="C66" s="55" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B67" s="55" t="s">
+        <v>245</v>
+      </c>
+      <c r="C67" s="55" t="s">
         <v>246</v>
-      </c>
-      <c r="C67" s="55" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B68" s="55" t="s">
+        <v>247</v>
+      </c>
+      <c r="C68" s="55" t="s">
         <v>248</v>
-      </c>
-      <c r="C68" s="55" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B69" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="C69" s="55" t="s">
         <v>250</v>
-      </c>
-      <c r="C69" s="55" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B70" s="55" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C70" s="55" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B71" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="C71" s="55" t="s">
         <v>253</v>
-      </c>
-      <c r="C71" s="55" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B72" s="55" t="s">
+        <v>254</v>
+      </c>
+      <c r="C72" s="55" t="s">
         <v>255</v>
-      </c>
-      <c r="C72" s="55" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B73" s="55" t="s">
+        <v>256</v>
+      </c>
+      <c r="C73" s="55" t="s">
         <v>257</v>
-      </c>
-      <c r="C73" s="55" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="55" t="s">
+        <v>258</v>
+      </c>
+      <c r="C74" s="55" t="s">
         <v>259</v>
-      </c>
-      <c r="C74" s="55" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B75" s="55" t="s">
+        <v>260</v>
+      </c>
+      <c r="C75" s="55" t="s">
         <v>261</v>
-      </c>
-      <c r="C75" s="55" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B76" s="55" t="s">
+        <v>262</v>
+      </c>
+      <c r="C76" s="55" t="s">
         <v>263</v>
-      </c>
-      <c r="C76" s="55" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B77" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="C77" s="55" t="s">
         <v>265</v>
-      </c>
-      <c r="C77" s="55" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B78" s="55" t="s">
+        <v>266</v>
+      </c>
+      <c r="C78" s="55" t="s">
         <v>267</v>
-      </c>
-      <c r="C78" s="55" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B79" s="55" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C79" s="55" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B80" s="55" t="s">
+        <v>269</v>
+      </c>
+      <c r="C80" s="55" t="s">
         <v>270</v>
-      </c>
-      <c r="C80" s="55" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B81" s="55" t="s">
+        <v>271</v>
+      </c>
+      <c r="C81" s="55" t="s">
         <v>272</v>
-      </c>
-      <c r="C81" s="55" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B82" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="C82" s="55" t="s">
         <v>274</v>
-      </c>
-      <c r="C82" s="55" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B83" s="55" t="s">
+        <v>275</v>
+      </c>
+      <c r="C83" s="55" t="s">
         <v>276</v>
-      </c>
-      <c r="C83" s="55" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B84" s="55" t="s">
+        <v>277</v>
+      </c>
+      <c r="C84" s="55" t="s">
         <v>278</v>
-      </c>
-      <c r="C84" s="55" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B85" s="55" t="s">
+        <v>279</v>
+      </c>
+      <c r="C85" s="55" t="s">
         <v>280</v>
-      </c>
-      <c r="C85" s="55" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B86" s="55" t="s">
+        <v>281</v>
+      </c>
+      <c r="C86" s="55" t="s">
         <v>282</v>
-      </c>
-      <c r="C86" s="55" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B87" s="55" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="55" t="s">
         <v>284</v>
-      </c>
-      <c r="C87" s="55" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B88" s="55" t="s">
+        <v>285</v>
+      </c>
+      <c r="C88" s="55" t="s">
         <v>286</v>
-      </c>
-      <c r="C88" s="55" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B89" s="55" t="s">
+        <v>287</v>
+      </c>
+      <c r="C89" s="55" t="s">
         <v>288</v>
-      </c>
-      <c r="C89" s="55" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B90" s="55" t="s">
+        <v>289</v>
+      </c>
+      <c r="C90" s="55" t="s">
         <v>290</v>
-      </c>
-      <c r="C90" s="55" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B91" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="C91" s="55" t="s">
         <v>292</v>
-      </c>
-      <c r="C91" s="55" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B92" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="C92" s="55" t="s">
         <v>294</v>
-      </c>
-      <c r="C92" s="55" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B93" s="55" t="s">
+        <v>295</v>
+      </c>
+      <c r="C93" s="55" t="s">
         <v>296</v>
-      </c>
-      <c r="C93" s="55" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B94" s="55" t="s">
+        <v>297</v>
+      </c>
+      <c r="C94" s="55" t="s">
         <v>298</v>
-      </c>
-      <c r="C94" s="55" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B95" s="55" t="s">
+        <v>299</v>
+      </c>
+      <c r="C95" s="55" t="s">
         <v>300</v>
-      </c>
-      <c r="C95" s="55" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B96" s="55" t="s">
+        <v>301</v>
+      </c>
+      <c r="C96" s="55" t="s">
         <v>302</v>
-      </c>
-      <c r="C96" s="55" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B97" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="C97" s="55" t="s">
         <v>304</v>
-      </c>
-      <c r="C97" s="55" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B98" s="55" t="s">
+        <v>305</v>
+      </c>
+      <c r="C98" s="55" t="s">
         <v>306</v>
-      </c>
-      <c r="C98" s="55" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B99" s="55" t="s">
+        <v>307</v>
+      </c>
+      <c r="C99" s="55" t="s">
         <v>308</v>
-      </c>
-      <c r="C99" s="55" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B100" s="55" t="s">
+        <v>309</v>
+      </c>
+      <c r="C100" s="55" t="s">
         <v>310</v>
-      </c>
-      <c r="C100" s="55" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B101" s="55" t="s">
+        <v>311</v>
+      </c>
+      <c r="C101" s="55" t="s">
         <v>312</v>
-      </c>
-      <c r="C101" s="55" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B102" s="55" t="s">
+        <v>313</v>
+      </c>
+      <c r="C102" s="55" t="s">
         <v>314</v>
-      </c>
-      <c r="C102" s="55" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B103" s="55" t="s">
+        <v>315</v>
+      </c>
+      <c r="C103" s="55" t="s">
         <v>316</v>
-      </c>
-      <c r="C103" s="55" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B104" s="55" t="s">
+        <v>317</v>
+      </c>
+      <c r="C104" s="55" t="s">
         <v>318</v>
-      </c>
-      <c r="C104" s="55" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B105" s="55" t="s">
+        <v>319</v>
+      </c>
+      <c r="C105" s="55" t="s">
         <v>320</v>
-      </c>
-      <c r="C105" s="55" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B106" s="55" t="s">
+        <v>321</v>
+      </c>
+      <c r="C106" s="55" t="s">
         <v>322</v>
-      </c>
-      <c r="C106" s="55" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B107" s="55" t="s">
+        <v>323</v>
+      </c>
+      <c r="C107" s="55" t="s">
         <v>324</v>
-      </c>
-      <c r="C107" s="55" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B108" s="55" t="s">
+        <v>325</v>
+      </c>
+      <c r="C108" s="55" t="s">
         <v>326</v>
-      </c>
-      <c r="C108" s="55" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B109" s="55" t="s">
+        <v>327</v>
+      </c>
+      <c r="C109" s="55" t="s">
         <v>328</v>
-      </c>
-      <c r="C109" s="55" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B110" s="55" t="s">
+        <v>329</v>
+      </c>
+      <c r="C110" s="55" t="s">
         <v>330</v>
-      </c>
-      <c r="C110" s="55" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B111" s="55" t="s">
+        <v>331</v>
+      </c>
+      <c r="C111" s="55" t="s">
         <v>332</v>
-      </c>
-      <c r="C111" s="55" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B112" s="55" t="s">
+        <v>333</v>
+      </c>
+      <c r="C112" s="55" t="s">
         <v>334</v>
-      </c>
-      <c r="C112" s="55" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B113" s="55" t="s">
+        <v>335</v>
+      </c>
+      <c r="C113" s="55" t="s">
         <v>336</v>
-      </c>
-      <c r="C113" s="55" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B114" s="55" t="s">
+        <v>337</v>
+      </c>
+      <c r="C114" s="55" t="s">
         <v>338</v>
-      </c>
-      <c r="C114" s="55" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B115" s="55" t="s">
+        <v>339</v>
+      </c>
+      <c r="C115" s="55" t="s">
         <v>340</v>
-      </c>
-      <c r="C115" s="55" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B116" s="55" t="s">
+        <v>341</v>
+      </c>
+      <c r="C116" s="55" t="s">
         <v>342</v>
-      </c>
-      <c r="C116" s="55" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B117" s="55" t="s">
+        <v>343</v>
+      </c>
+      <c r="C117" s="55" t="s">
         <v>344</v>
-      </c>
-      <c r="C117" s="55" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B118" s="55" t="s">
+        <v>345</v>
+      </c>
+      <c r="C118" s="55" t="s">
         <v>346</v>
-      </c>
-      <c r="C118" s="55" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B119" s="55" t="s">
+        <v>347</v>
+      </c>
+      <c r="C119" s="55" t="s">
         <v>348</v>
-      </c>
-      <c r="C119" s="55" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B120" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="C120" s="55" t="s">
         <v>350</v>
-      </c>
-      <c r="C120" s="55" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B121" s="55" t="s">
+        <v>351</v>
+      </c>
+      <c r="C121" s="55" t="s">
         <v>352</v>
-      </c>
-      <c r="C121" s="55" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B122" s="55" t="s">
+        <v>353</v>
+      </c>
+      <c r="C122" s="55" t="s">
         <v>354</v>
-      </c>
-      <c r="C122" s="55" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B123" s="58" t="s">
+        <v>355</v>
+      </c>
+      <c r="C123" s="58" t="s">
         <v>356</v>
-      </c>
-      <c r="C123" s="58" t="s">
-        <v>357</v>
       </c>
     </row>
   </sheetData>

--- a/core/sample-data/Financial Template.xlsx
+++ b/core/sample-data/Financial Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A9CA9B-94F0-564E-B405-6A37E7D98C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA88E46C-B6E9-004A-8F64-79DFDAB8231D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23120" yWindow="2260" windowWidth="29240" windowHeight="20480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33540" yWindow="1060" windowWidth="31760" windowHeight="24500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lookup Tables" sheetId="8" state="hidden" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="359">
   <si>
     <t>Account Type</t>
   </si>
@@ -331,13 +331,7 @@
     <t>Sell Basis Per Share</t>
   </si>
   <si>
-    <t>Closed</t>
-  </si>
-  <si>
     <t>AAPL</t>
-  </si>
-  <si>
-    <t>Open</t>
   </si>
   <si>
     <t/>
@@ -1365,7 +1359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1465,39 +1459,33 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="8" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1804,6 +1792,24 @@
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1833,35 +1839,37 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Account"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Account Type2"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Owner"/>
-    <tableColumn id="4" xr3:uid="{C950A649-3BE5-1D49-9C22-1FC53E142931}" name="Column1" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{C950A649-3BE5-1D49-9C22-1FC53E142931}" name="Column1" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5F681B6E-186E-AB4D-BAC2-437CAFDB7002}" name="Table4" displayName="Table4" ref="B2:N41" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="B2:N41" xr:uid="{5F681B6E-186E-AB4D-BAC2-437CAFDB7002}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5F681B6E-186E-AB4D-BAC2-437CAFDB7002}" name="Table4" displayName="Table4" ref="B2:N99" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
+  <autoFilter ref="B2:N99" xr:uid="{5F681B6E-186E-AB4D-BAC2-437CAFDB7002}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{44ABB882-7907-0449-86C6-7D1EB2C6D90B}" name="Account" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{EF66979F-FA5D-AA49-B22C-9781D72A6514}" name="Account Type" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{44ABB882-7907-0449-86C6-7D1EB2C6D90B}" name="Account" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{EF66979F-FA5D-AA49-B22C-9781D72A6514}" name="Account Type" dataDxfId="11">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{E3EAC05B-E30E-E24D-8C0B-E876FF67B7FC}" name="Owner" dataDxfId="11">
+    <tableColumn id="3" xr3:uid="{E3EAC05B-E30E-E24D-8C0B-E876FF67B7FC}" name="Owner" dataDxfId="10">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{348190E8-36F8-3D4E-AEDF-D62ABC8778D3}" name="Transaction" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{08380172-5D03-D34B-879F-2A6B96A894FA}" name="Symbol" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{2069EC4A-30DE-3241-93CB-213CCCB8C6B4}" name="Security Description" dataDxfId="8">
+    <tableColumn id="4" xr3:uid="{348190E8-36F8-3D4E-AEDF-D62ABC8778D3}" name="Transaction" dataDxfId="9">
+      <calculatedColumnFormula>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{08380172-5D03-D34B-879F-2A6B96A894FA}" name="Symbol" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{2069EC4A-30DE-3241-93CB-213CCCB8C6B4}" name="Security Description" dataDxfId="7">
       <calculatedColumnFormula array="1">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8A722796-0EBD-404D-A4B5-8BBD14003108}" name="Date Acquired" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{DE2BC68E-9090-4E42-91E9-B347D59F0AEA}" name="Shares Bought" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{39330DF2-9948-5E49-B158-7E8529E815AF}" name="Cost Basis Per Share" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{FAD33138-0C6D-2246-AA81-68BA16CCB53A}" name="Date Sold" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{3E748A03-6922-7042-8C8A-59DD20A9C3D3}" name="Charitable Donation" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{51498472-466A-A946-AD11-9B62C566F1E9}" name="Shares Sold" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{919FF199-7CD0-7847-80E2-30B6FDE4BB78}" name="Sell Basis Per Share" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{8A722796-0EBD-404D-A4B5-8BBD14003108}" name="Date Acquired" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{DE2BC68E-9090-4E42-91E9-B347D59F0AEA}" name="Shares Bought" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{39330DF2-9948-5E49-B158-7E8529E815AF}" name="Cost Basis Per Share" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{FAD33138-0C6D-2246-AA81-68BA16CCB53A}" name="Date Sold" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{3E748A03-6922-7042-8C8A-59DD20A9C3D3}" name="Charitable Donation" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{51498472-466A-A946-AD11-9B62C566F1E9}" name="Shares Sold" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{919FF199-7CD0-7847-80E2-30B6FDE4BB78}" name="Sell Basis Per Share" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2526,8 +2534,8 @@
       <c r="D2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="61" t="s">
-        <v>357</v>
+      <c r="E2" s="31" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2540,8 +2548,8 @@
       <c r="D3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="62" t="s">
-        <v>358</v>
+      <c r="E3" s="59" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2554,8 +2562,8 @@
       <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="62" t="s">
-        <v>359</v>
+      <c r="E4" s="59" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2568,8 +2576,8 @@
       <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="62" t="s">
-        <v>360</v>
+      <c r="E5" s="59" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -4884,167 +4892,167 @@
       </c>
       <c r="H3" s="28">
         <f ca="1">G3+G3*(RAND()*(0.15--0.15)+-0.15)/12+$F3</f>
-        <v>20117.356134930607</v>
+        <v>20333.331345509072</v>
       </c>
       <c r="I3" s="28">
         <f t="shared" ref="I3:AV3" ca="1" si="0">H3+H3*(RAND()*(0.15--0.15)+-0.15)/12+$F3</f>
-        <v>20367.677199178364</v>
+        <v>20695.746566204089</v>
       </c>
       <c r="J3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>20552.956686156711</v>
+        <v>21000.985895887297</v>
       </c>
       <c r="K3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>20743.851977740989</v>
+        <v>21501.571886951027</v>
       </c>
       <c r="L3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>21010.778095958201</v>
+        <v>21715.600170157675</v>
       </c>
       <c r="M3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>21396.323452180917</v>
+        <v>21866.48555287224</v>
       </c>
       <c r="N3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>21573.480740489027</v>
+        <v>22382.761069086231</v>
       </c>
       <c r="O3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>21771.74930572266</v>
+        <v>22965.56034175435</v>
       </c>
       <c r="P3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22161.813533197466</v>
+        <v>23374.197938649904</v>
       </c>
       <c r="Q3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22673.680705195551</v>
+        <v>23680.137085556671</v>
       </c>
       <c r="R3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>22786.618948226187</v>
+        <v>24015.230610610055</v>
       </c>
       <c r="S3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>23305.370026858869</v>
+        <v>24366.68568195144</v>
       </c>
       <c r="T3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>23554.159424800568</v>
+        <v>24805.332649296553</v>
       </c>
       <c r="U3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24172.584314163272</v>
+        <v>25064.717549277389</v>
       </c>
       <c r="V3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24604.842796100533</v>
+        <v>25686.21780372283</v>
       </c>
       <c r="W3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24840.302286863989</v>
+        <v>25937.263748328951</v>
       </c>
       <c r="X3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>24946.299779818499</v>
+        <v>26134.999722224147</v>
       </c>
       <c r="Y3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>25334.934979525624</v>
+        <v>26774.33469494259</v>
       </c>
       <c r="Z3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>25549.636342336842</v>
+        <v>26905.848564399359</v>
       </c>
       <c r="AA3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>25807.977035501062</v>
+        <v>27439.359733899568</v>
       </c>
       <c r="AB3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26082.6347972861</v>
+        <v>27674.934643894168</v>
       </c>
       <c r="AC3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26284.352104311671</v>
+        <v>28045.262383072597</v>
       </c>
       <c r="AD3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26489.02897921699</v>
+        <v>28403.569653486597</v>
       </c>
       <c r="AE3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26586.8422098745</v>
+        <v>28771.642411445107</v>
       </c>
       <c r="AF3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26824.967799754439</v>
+        <v>29430.194470862534</v>
       </c>
       <c r="AG3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>26888.294196573122</v>
+        <v>29811.522137242195</v>
       </c>
       <c r="AH3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27048.759315658564</v>
+        <v>30095.938366139522</v>
       </c>
       <c r="AI3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27170.750588568135</v>
+        <v>30794.636738104764</v>
       </c>
       <c r="AJ3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27484.432221067305</v>
+        <v>31402.881402342784</v>
       </c>
       <c r="AK3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27629.582060297627</v>
+        <v>31643.168666940797</v>
       </c>
       <c r="AL3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27668.117005595872</v>
+        <v>31604.832715341912</v>
       </c>
       <c r="AM3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>27928.465760652234</v>
+        <v>32177.538937543668</v>
       </c>
       <c r="AN3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>28525.46798290349</v>
+        <v>32736.192990002965</v>
       </c>
       <c r="AO3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>28608.021609271425</v>
+        <v>33053.427408738149</v>
       </c>
       <c r="AP3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>29204.93870489666</v>
+        <v>33069.206498915853</v>
       </c>
       <c r="AQ3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>29666.959557411272</v>
+        <v>33816.652369978554</v>
       </c>
       <c r="AR3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>29788.864235237033</v>
+        <v>34176.702887791173</v>
       </c>
       <c r="AS3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>30510.272062600809</v>
+        <v>34715.014176095414</v>
       </c>
       <c r="AT3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>30530.596049502037</v>
+        <v>34818.910435574391</v>
       </c>
       <c r="AU3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>30646.172057292708</v>
+        <v>35382.755809171962</v>
       </c>
       <c r="AV3" s="28">
         <f t="shared" ca="1" si="0"/>
-        <v>30743.151896813062</v>
+        <v>35333.549605146523</v>
       </c>
       <c r="AW3" s="28"/>
       <c r="AX3" s="28"/>
@@ -5176,167 +5184,167 @@
       </c>
       <c r="H4" s="28">
         <f t="shared" ref="H4:AV4" ca="1" si="1">G4+G4*(RAND()*(0.15--0.15)+-0.15)/12+$F4</f>
-        <v>14990.514361822292</v>
+        <v>15274.43791666073</v>
       </c>
       <c r="I4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15303.515598539934</v>
+        <v>15441.370353455148</v>
       </c>
       <c r="J4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15570.002437520176</v>
+        <v>15466.042025237533</v>
       </c>
       <c r="K4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15895.693363442066</v>
+        <v>15635.562425435824</v>
       </c>
       <c r="L4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15949.596743459635</v>
+        <v>15836.157230724946</v>
       </c>
       <c r="M4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15911.278602719756</v>
+        <v>15865.213435331327</v>
       </c>
       <c r="N4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>15967.608564743297</v>
+        <v>15934.313013362902</v>
       </c>
       <c r="O4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16163.242040816329</v>
+        <v>16024.861186304519</v>
       </c>
       <c r="P4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16509.221610756773</v>
+        <v>16226.172770513007</v>
       </c>
       <c r="Q4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16690.513317076115</v>
+        <v>16198.327327817855</v>
       </c>
       <c r="R4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>16947.759378320603</v>
+        <v>16250.129729808908</v>
       </c>
       <c r="S4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17173.580611338963</v>
+        <v>16317.139730047715</v>
       </c>
       <c r="T4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17218.850423594682</v>
+        <v>16332.933718545093</v>
       </c>
       <c r="U4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17324.20574614155</v>
+        <v>16470.996758068672</v>
       </c>
       <c r="V4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17263.511235520458</v>
+        <v>16513.240498314099</v>
       </c>
       <c r="W4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17431.901403158277</v>
+        <v>16837.735323620418</v>
       </c>
       <c r="X4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17715.953005465461</v>
+        <v>16970.14578799855</v>
       </c>
       <c r="Y4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17751.994231134446</v>
+        <v>17242.861499159517</v>
       </c>
       <c r="Z4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>17804.510146460347</v>
+        <v>17388.422726571236</v>
       </c>
       <c r="AA4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18038.84211192797</v>
+        <v>17357.203504018657</v>
       </c>
       <c r="AB4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18072.946323573153</v>
+        <v>17550.706100451531</v>
       </c>
       <c r="AC4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18221.831831847008</v>
+        <v>17813.747154894063</v>
       </c>
       <c r="AD4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18222.866717377001</v>
+        <v>18102.265125828715</v>
       </c>
       <c r="AE4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18163.602482154438</v>
+        <v>18178.87951591887</v>
       </c>
       <c r="AF4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18303.060654507426</v>
+        <v>18255.839977542539</v>
       </c>
       <c r="AG4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18632.270464540157</v>
+        <v>18611.491099486273</v>
       </c>
       <c r="AH4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18840.555481564315</v>
+        <v>18756.75795742642</v>
       </c>
       <c r="AI4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>18798.690311112234</v>
+        <v>18759.074256110183</v>
       </c>
       <c r="AJ4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19108.565167911365</v>
+        <v>18762.987437397634</v>
       </c>
       <c r="AK4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19342.831431992003</v>
+        <v>19111.302336837343</v>
       </c>
       <c r="AL4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19448.419115521945</v>
+        <v>19331.183887792035</v>
       </c>
       <c r="AM4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>19822.31131725082</v>
+        <v>19415.373784073639</v>
       </c>
       <c r="AN4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20190.750901330965</v>
+        <v>19326.311137932084</v>
       </c>
       <c r="AO4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20528.74723105356</v>
+        <v>19471.436147429591</v>
       </c>
       <c r="AP4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>20881.200349228533</v>
+        <v>19647.476382333229</v>
       </c>
       <c r="AQ4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>21143.602323681265</v>
+        <v>19704.398272725746</v>
       </c>
       <c r="AR4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>21069.136748310779</v>
+        <v>19896.653406360281</v>
       </c>
       <c r="AS4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>21147.909605369896</v>
+        <v>20020.853819881246</v>
       </c>
       <c r="AT4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>21081.708154760425</v>
+        <v>20320.24641416753</v>
       </c>
       <c r="AU4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>21453.992765282692</v>
+        <v>20472.51496275586</v>
       </c>
       <c r="AV4" s="28">
         <f t="shared" ca="1" si="1"/>
-        <v>21370.555438131665</v>
+        <v>20635.620979927178</v>
       </c>
       <c r="AW4" s="28"/>
       <c r="AX4" s="28"/>
@@ -5468,167 +5476,167 @@
       </c>
       <c r="H5" s="28">
         <f t="shared" ref="H5:AV5" ca="1" si="2">G5+G5*(RAND()*(0.15--0.15)+-0.15)/12+$F5</f>
-        <v>10087.627167778086</v>
+        <v>10134.08750542804</v>
       </c>
       <c r="I5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10273.493950143817</v>
+        <v>10374.777003617361</v>
       </c>
       <c r="J5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10551.558684506475</v>
+        <v>10518.115579839035</v>
       </c>
       <c r="K5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10639.1988017531</v>
+        <v>10580.472871398648</v>
       </c>
       <c r="L5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>10880.822376642365</v>
+        <v>10713.038189839424</v>
       </c>
       <c r="M5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11021.889949500601</v>
+        <v>10786.383769289323</v>
       </c>
       <c r="N5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11294.336887280104</v>
+        <v>10987.951964026881</v>
       </c>
       <c r="O5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11584.55520151016</v>
+        <v>11220.277180952035</v>
       </c>
       <c r="P5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11611.691710635147</v>
+        <v>11264.303727857114</v>
       </c>
       <c r="Q5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>11772.758509926249</v>
+        <v>11278.523209229716</v>
       </c>
       <c r="R5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12024.48584604156</v>
+        <v>11392.66937684665</v>
       </c>
       <c r="S5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12232.078354020272</v>
+        <v>11567.341981063648</v>
       </c>
       <c r="T5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12366.002587887253</v>
+        <v>11775.500976633743</v>
       </c>
       <c r="U5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12473.622497122396</v>
+        <v>11896.509527300444</v>
       </c>
       <c r="V5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12707.867581664514</v>
+        <v>12151.557393552323</v>
       </c>
       <c r="W5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12808.976897866454</v>
+        <v>12233.30714371767</v>
       </c>
       <c r="X5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12883.889782245358</v>
+        <v>12280.448182963613</v>
       </c>
       <c r="Y5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>12939.002617407057</v>
+        <v>12474.450398549679</v>
       </c>
       <c r="Z5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13149.976709210056</v>
+        <v>12696.286936536231</v>
       </c>
       <c r="AA5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13252.337682198513</v>
+        <v>12897.919452523174</v>
       </c>
       <c r="AB5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13415.574699112536</v>
+        <v>13051.562816285936</v>
       </c>
       <c r="AC5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13531.426684421504</v>
+        <v>13199.922911504742</v>
       </c>
       <c r="AD5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>13837.653936907582</v>
+        <v>13321.878869871232</v>
       </c>
       <c r="AE5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14007.909083458004</v>
+        <v>13511.649157893815</v>
       </c>
       <c r="AF5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14109.207058344051</v>
+        <v>13635.370459189127</v>
       </c>
       <c r="AG5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14232.688000153963</v>
+        <v>13838.033741164463</v>
       </c>
       <c r="AH5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14252.696026832014</v>
+        <v>14099.534603270706</v>
       </c>
       <c r="AI5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14285.660464024359</v>
+        <v>14374.066159516819</v>
       </c>
       <c r="AJ5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14356.040567229265</v>
+        <v>14508.976132957067</v>
       </c>
       <c r="AK5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14673.079334271139</v>
+        <v>14641.349150408963</v>
       </c>
       <c r="AL5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>14812.383575570388</v>
+        <v>14642.640999830384</v>
       </c>
       <c r="AM5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15055.518563347958</v>
+        <v>14673.069775802967</v>
       </c>
       <c r="AN5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15375.063954482406</v>
+        <v>14788.999878448823</v>
       </c>
       <c r="AO5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15547.836967662693</v>
+        <v>14936.617285618851</v>
       </c>
       <c r="AP5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15736.369010298533</v>
+        <v>15217.326664283421</v>
       </c>
       <c r="AQ5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15704.33272715183</v>
+        <v>15248.158104421034</v>
       </c>
       <c r="AR5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>15917.876070124128</v>
+        <v>15337.154282360989</v>
       </c>
       <c r="AS5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>16250.495148615362</v>
+        <v>15646.723517847027</v>
       </c>
       <c r="AT5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>16540.36362805005</v>
+        <v>15908.819594968976</v>
       </c>
       <c r="AU5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>16638.169523019613</v>
+        <v>16104.213393837597</v>
       </c>
       <c r="AV5" s="28">
         <f t="shared" ca="1" si="2"/>
-        <v>16842.721735810104</v>
+        <v>16181.095088345957</v>
       </c>
       <c r="AW5" s="28"/>
       <c r="AX5" s="28"/>
@@ -6217,7 +6225,7 @@
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="8" customWidth="1"/>
@@ -6297,11 +6305,12 @@
         <f t="array" ref="D3">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="G3" s="33" t="str" cm="1">
         <f t="array" ref="G3">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6338,11 +6347,12 @@
         <f t="array" ref="D4">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="G4" s="33" t="str" cm="1">
         <f t="array" ref="G4">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6379,11 +6389,12 @@
         <f t="array" ref="D5">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="G5" s="33" t="str" cm="1">
         <f t="array" ref="G5">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6420,11 +6431,12 @@
         <f t="array" ref="D6">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="G6" s="33" t="str" cm="1">
         <f t="array" ref="G6">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6461,11 +6473,12 @@
         <f t="array" ref="D7">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E7" t="s">
-        <v>92</v>
+      <c r="E7" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G7" s="33" t="str" cm="1">
         <f t="array" ref="G7">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6483,7 +6496,7 @@
       <c r="K7" s="36"/>
       <c r="M7" s="6"/>
       <c r="N7" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6498,11 +6511,12 @@
         <f t="array" ref="D8">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="G8" s="33" t="str" cm="1">
         <f t="array" ref="G8">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6539,11 +6553,12 @@
         <f t="array" ref="D9">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="G9" s="33" t="str" cm="1">
         <f t="array" ref="G9">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6562,7 +6577,7 @@
         <v>45415</v>
       </c>
       <c r="L9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M9" s="6">
         <v>4</v>
@@ -6583,11 +6598,12 @@
         <f t="array" ref="D10">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="G10" s="33" t="str" cm="1">
         <f t="array" ref="G10">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6606,7 +6622,7 @@
         <v>45608</v>
       </c>
       <c r="L10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M10" s="6">
         <v>4</v>
@@ -6627,11 +6643,12 @@
         <f t="array" ref="D11">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="G11" s="33" t="str" cm="1">
         <f t="array" ref="G11">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6668,11 +6685,12 @@
         <f t="array" ref="D12">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E12" t="s">
-        <v>92</v>
+      <c r="E12" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G12" s="33" t="str" cm="1">
         <f t="array" ref="G12">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6690,7 +6708,7 @@
       <c r="K12" s="36"/>
       <c r="M12" s="6"/>
       <c r="N12" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6705,11 +6723,12 @@
         <f t="array" ref="D13">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E13" t="s">
-        <v>92</v>
+      <c r="E13" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G13" s="33" t="str" cm="1">
         <f t="array" ref="G13">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6727,7 +6746,7 @@
       <c r="K13" s="36"/>
       <c r="M13" s="6"/>
       <c r="N13" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6742,11 +6761,12 @@
         <f t="array" ref="D14">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E14" t="s">
-        <v>92</v>
+      <c r="E14" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G14" s="33" t="str" cm="1">
         <f t="array" ref="G14">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6764,7 +6784,7 @@
       <c r="K14" s="38"/>
       <c r="M14" s="6"/>
       <c r="N14" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6779,11 +6799,12 @@
         <f t="array" ref="D15">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E15" t="s">
-        <v>92</v>
+      <c r="E15" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G15" s="33" t="str" cm="1">
         <f t="array" ref="G15">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6801,7 +6822,7 @@
       <c r="K15" s="38"/>
       <c r="M15" s="6"/>
       <c r="N15" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6816,11 +6837,12 @@
         <f t="array" ref="D16">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E16" t="s">
-        <v>92</v>
+      <c r="E16" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G16" s="33" t="str" cm="1">
         <f t="array" ref="G16">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6838,7 +6860,7 @@
       <c r="K16" s="38"/>
       <c r="M16" s="6"/>
       <c r="N16" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6853,11 +6875,12 @@
         <f t="array" ref="D17">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E17" t="s">
-        <v>92</v>
+      <c r="E17" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G17" s="33" t="str" cm="1">
         <f t="array" ref="G17">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6875,7 +6898,7 @@
       <c r="K17" s="38"/>
       <c r="M17" s="6"/>
       <c r="N17" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6890,11 +6913,12 @@
         <f t="array" ref="D18">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E18" t="s">
-        <v>92</v>
+      <c r="E18" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G18" s="33" t="str" cm="1">
         <f t="array" ref="G18">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6912,7 +6936,7 @@
       <c r="K18" s="38"/>
       <c r="M18" s="6"/>
       <c r="N18" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6927,11 +6951,12 @@
         <f t="array" ref="D19">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Drew</v>
       </c>
-      <c r="E19" t="s">
-        <v>92</v>
+      <c r="E19" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G19" s="33" t="str" cm="1">
         <f t="array" ref="G19">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -6949,7 +6974,7 @@
       <c r="K19" s="38"/>
       <c r="M19" s="6"/>
       <c r="N19" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -6964,11 +6989,12 @@
         <f t="array" ref="D20">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>90</v>
+      <c r="E20" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G20" s="33" t="str" cm="1">
         <f t="array" ref="G20">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7006,11 +7032,12 @@
         <f t="array" ref="D21">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>92</v>
+      <c r="E21" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G21" s="33" t="str" cm="1">
         <f t="array" ref="G21">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7029,7 +7056,7 @@
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7044,11 +7071,12 @@
         <f t="array" ref="D22">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>90</v>
+      <c r="E22" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G22" s="33" t="str" cm="1">
         <f t="array" ref="G22">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7086,11 +7114,12 @@
         <f t="array" ref="D23">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>92</v>
+      <c r="E23" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G23" s="33" t="str" cm="1">
         <f t="array" ref="G23">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7109,7 +7138,7 @@
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7124,11 +7153,12 @@
         <f t="array" ref="D24">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>90</v>
+      <c r="E24" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G24" s="33" t="str" cm="1">
         <f t="array" ref="G24">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7166,11 +7196,12 @@
         <f t="array" ref="D25">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>92</v>
+      <c r="E25" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G25" s="33" t="str" cm="1">
         <f t="array" ref="G25">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7189,7 +7220,7 @@
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7204,11 +7235,12 @@
         <f t="array" ref="D26">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>90</v>
+      <c r="E26" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G26" s="33" t="str" cm="1">
         <f t="array" ref="G26">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7246,11 +7278,12 @@
         <f t="array" ref="D27">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>92</v>
+      <c r="E27" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G27" s="33" t="str" cm="1">
         <f t="array" ref="G27">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7269,7 +7302,7 @@
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7284,11 +7317,12 @@
         <f t="array" ref="D28">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>92</v>
+      <c r="E28" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G28" s="33" t="str" cm="1">
         <f t="array" ref="G28">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7307,7 +7341,7 @@
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7322,11 +7356,12 @@
         <f t="array" ref="D29">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>92</v>
+      <c r="E29" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G29" s="33" t="str" cm="1">
         <f t="array" ref="G29">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7345,7 +7380,7 @@
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="N29" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7360,11 +7395,12 @@
         <f t="array" ref="D30">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>92</v>
+      <c r="E30" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G30" s="33" t="str" cm="1">
         <f t="array" ref="G30">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7383,7 +7419,7 @@
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7398,11 +7434,12 @@
         <f t="array" ref="D31">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>90</v>
+      <c r="E31" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
       </c>
       <c r="F31" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G31" s="33" t="str" cm="1">
         <f t="array" ref="G31">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7440,11 +7477,12 @@
         <f t="array" ref="D32">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>92</v>
+      <c r="E32" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F32" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G32" s="33" t="str" cm="1">
         <f t="array" ref="G32">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7463,7 +7501,7 @@
       <c r="L32" s="6"/>
       <c r="M32" s="42"/>
       <c r="N32" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7478,11 +7516,12 @@
         <f t="array" ref="D33">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>90</v>
+      <c r="E33" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
       </c>
       <c r="F33" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G33" s="33" t="str" cm="1">
         <f t="array" ref="G33">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7520,11 +7559,12 @@
         <f t="array" ref="D34">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>92</v>
+      <c r="E34" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F34" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G34" s="33" t="str" cm="1">
         <f t="array" ref="G34">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7534,7 +7574,7 @@
         <v>41988</v>
       </c>
       <c r="I34" s="6">
-        <v>6.65</v>
+        <v>1</v>
       </c>
       <c r="J34" s="37">
         <v>307.81</v>
@@ -7543,7 +7583,7 @@
       <c r="L34" s="6"/>
       <c r="M34" s="42"/>
       <c r="N34" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7558,11 +7598,12 @@
         <f t="array" ref="D35">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>90</v>
+      <c r="E35" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
       </c>
       <c r="F35" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G35" s="33" t="str" cm="1">
         <f t="array" ref="G35">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7572,7 +7613,7 @@
         <v>41988</v>
       </c>
       <c r="I35" s="6">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J35" s="37">
         <v>307.81</v>
@@ -7581,7 +7622,7 @@
         <v>45148</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M35" s="42">
         <v>2</v>
@@ -7602,11 +7643,12 @@
         <f t="array" ref="D36">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>90</v>
+      <c r="E36" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
       </c>
       <c r="F36" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G36" s="33" t="str" cm="1">
         <f t="array" ref="G36">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7616,7 +7658,7 @@
         <v>41988</v>
       </c>
       <c r="I36" s="6">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="J36" s="37">
         <v>307.81</v>
@@ -7625,7 +7667,7 @@
         <v>45608</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M36" s="42">
         <v>5</v>
@@ -7646,11 +7688,12 @@
         <f t="array" ref="D37">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>90</v>
+      <c r="E37" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
       </c>
       <c r="F37" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G37" s="33" t="str" cm="1">
         <f t="array" ref="G37">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7660,7 +7703,7 @@
         <v>42354</v>
       </c>
       <c r="I37" s="6">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J37" s="37">
         <v>667.40499999999997</v>
@@ -7688,11 +7731,12 @@
         <f t="array" ref="D38">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>90</v>
+      <c r="E38" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Closed</v>
       </c>
       <c r="F38" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G38" s="33" t="str" cm="1">
         <f t="array" ref="G38">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7702,7 +7746,7 @@
         <v>43837</v>
       </c>
       <c r="I38" s="6">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="J38" s="37">
         <v>1909.75</v>
@@ -7730,11 +7774,12 @@
         <f t="array" ref="D39">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>92</v>
+      <c r="E39" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G39" s="33" t="str" cm="1">
         <f t="array" ref="G39">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7744,7 +7789,7 @@
         <v>44019</v>
       </c>
       <c r="I39" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J39" s="37">
         <v>3041.92</v>
@@ -7753,7 +7798,7 @@
       <c r="L39" s="6"/>
       <c r="M39" s="42"/>
       <c r="N39" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7768,11 +7813,12 @@
         <f t="array" ref="D40">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>92</v>
+      <c r="E40" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F40" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G40" s="33" t="str" cm="1">
         <f t="array" ref="G40">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7782,7 +7828,7 @@
         <v>44370</v>
       </c>
       <c r="I40" s="6">
-        <v>2.8000000000000004E-2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="37">
         <v>3507.14</v>
@@ -7791,7 +7837,7 @@
       <c r="L40" s="6"/>
       <c r="M40" s="42"/>
       <c r="N40" s="37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -7806,11 +7852,12 @@
         <f t="array" ref="D41">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
         <v>Shaun</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>92</v>
+      <c r="E41" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
       </c>
       <c r="F41" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G41" s="33" t="str" cm="1">
         <f t="array" ref="G41">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
@@ -7820,7 +7867,7 @@
         <v>45293</v>
       </c>
       <c r="I41" s="6">
-        <v>0.16700000000000001</v>
+        <v>1</v>
       </c>
       <c r="J41" s="37">
         <v>149.1</v>
@@ -7829,8 +7876,2154 @@
       <c r="L41" s="6"/>
       <c r="M41" s="42"/>
       <c r="N41" s="37" t="s">
-        <v>93</v>
-      </c>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" s="64" t="str" cm="1">
+        <f t="array" ref="C42">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D42" s="64" t="str" cm="1">
+        <f t="array" ref="D42">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E42" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F42" s="66" t="s">
+        <v>186</v>
+      </c>
+      <c r="G42" s="67" t="str" cm="1">
+        <f t="array" ref="G42">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>DEERE &amp; CO</v>
+      </c>
+      <c r="H42" s="40">
+        <v>45273</v>
+      </c>
+      <c r="I42" s="65">
+        <v>1</v>
+      </c>
+      <c r="J42" s="68">
+        <v>377.01</v>
+      </c>
+      <c r="K42" s="69"/>
+      <c r="L42" s="65"/>
+      <c r="M42" s="70"/>
+      <c r="N42" s="68"/>
+    </row>
+    <row r="43" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="62" t="str" cm="1">
+        <f t="array" ref="C43">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D43" s="62" t="str" cm="1">
+        <f t="array" ref="D43">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E43" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F43" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="G43" s="63" t="str" cm="1">
+        <f t="array" ref="G43">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>DEERE &amp; CO</v>
+      </c>
+      <c r="H43" s="39">
+        <v>45637</v>
+      </c>
+      <c r="I43" s="6">
+        <v>1</v>
+      </c>
+      <c r="J43" s="37">
+        <v>448.03</v>
+      </c>
+      <c r="K43" s="36"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="42"/>
+      <c r="N43" s="37"/>
+    </row>
+    <row r="44" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" s="64" t="str" cm="1">
+        <f t="array" ref="C44">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D44" s="64" t="str" cm="1">
+        <f t="array" ref="D44">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E44" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F44" s="66" t="s">
+        <v>186</v>
+      </c>
+      <c r="G44" s="67" t="str" cm="1">
+        <f t="array" ref="G44">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>DEERE &amp; CO</v>
+      </c>
+      <c r="H44" s="40">
+        <v>46002</v>
+      </c>
+      <c r="I44" s="65">
+        <v>1</v>
+      </c>
+      <c r="J44" s="68">
+        <v>475.94</v>
+      </c>
+      <c r="K44" s="69"/>
+      <c r="L44" s="65"/>
+      <c r="M44" s="70"/>
+      <c r="N44" s="68"/>
+    </row>
+    <row r="45" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="62" t="str" cm="1">
+        <f t="array" ref="C45">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D45" s="62" t="str" cm="1">
+        <f t="array" ref="D45">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E45" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F45" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="G45" s="63" t="str" cm="1">
+        <f t="array" ref="G45">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>DEERE &amp; CO</v>
+      </c>
+      <c r="H45" s="39">
+        <v>46004</v>
+      </c>
+      <c r="I45" s="6">
+        <v>1</v>
+      </c>
+      <c r="J45" s="37">
+        <v>484.8</v>
+      </c>
+      <c r="K45" s="36"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="42"/>
+      <c r="N45" s="37"/>
+    </row>
+    <row r="46" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" s="62" t="str" cm="1">
+        <f t="array" ref="C46">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D46" s="62" t="str" cm="1">
+        <f t="array" ref="D46">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E46" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F46" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="G46" s="63" t="str" cm="1">
+        <f t="array" ref="G46">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>MICROSOFT CORP</v>
+      </c>
+      <c r="H46" s="39">
+        <v>44305</v>
+      </c>
+      <c r="I46" s="6">
+        <v>1</v>
+      </c>
+      <c r="J46" s="37">
+        <v>258.75</v>
+      </c>
+      <c r="K46" s="36"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="42"/>
+      <c r="N46" s="37"/>
+    </row>
+    <row r="47" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="64" t="str" cm="1">
+        <f t="array" ref="C47">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D47" s="64" t="str" cm="1">
+        <f t="array" ref="D47">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E47" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F47" s="66" t="s">
+        <v>252</v>
+      </c>
+      <c r="G47" s="67" t="str" cm="1">
+        <f t="array" ref="G47">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>MICROSOFT CORP</v>
+      </c>
+      <c r="H47" s="40">
+        <v>44508</v>
+      </c>
+      <c r="I47" s="65">
+        <v>1</v>
+      </c>
+      <c r="J47" s="68">
+        <v>335.64</v>
+      </c>
+      <c r="K47" s="69"/>
+      <c r="L47" s="65"/>
+      <c r="M47" s="70"/>
+      <c r="N47" s="68"/>
+    </row>
+    <row r="48" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="62" t="str" cm="1">
+        <f t="array" ref="C48">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D48" s="62" t="str" cm="1">
+        <f t="array" ref="D48">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E48" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F48" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="G48" s="63" t="str" cm="1">
+        <f t="array" ref="G48">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>MICROSOFT CORP</v>
+      </c>
+      <c r="H48" s="39">
+        <v>44599</v>
+      </c>
+      <c r="I48" s="6">
+        <v>1</v>
+      </c>
+      <c r="J48" s="37">
+        <v>305.17</v>
+      </c>
+      <c r="K48" s="36"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="42"/>
+      <c r="N48" s="37"/>
+    </row>
+    <row r="49" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="62" t="str" cm="1">
+        <f t="array" ref="C49">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D49" s="62" t="str" cm="1">
+        <f t="array" ref="D49">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E49" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F49" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="G49" s="63" t="str" cm="1">
+        <f t="array" ref="G49">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>MICROSOFT CORP</v>
+      </c>
+      <c r="H49" s="39">
+        <v>44657</v>
+      </c>
+      <c r="I49" s="6">
+        <v>1</v>
+      </c>
+      <c r="J49" s="37">
+        <v>300.51</v>
+      </c>
+      <c r="K49" s="36"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="42"/>
+      <c r="N49" s="37"/>
+    </row>
+    <row r="50" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="64" t="str" cm="1">
+        <f t="array" ref="C50">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D50" s="64" t="str" cm="1">
+        <f t="array" ref="D50">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E50" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F50" s="66" t="s">
+        <v>252</v>
+      </c>
+      <c r="G50" s="67" t="str" cm="1">
+        <f t="array" ref="G50">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>MICROSOFT CORP</v>
+      </c>
+      <c r="H50" s="40">
+        <v>45236</v>
+      </c>
+      <c r="I50" s="65">
+        <v>1</v>
+      </c>
+      <c r="J50" s="68">
+        <v>357.1</v>
+      </c>
+      <c r="K50" s="69"/>
+      <c r="L50" s="65"/>
+      <c r="M50" s="70"/>
+      <c r="N50" s="68"/>
+    </row>
+    <row r="51" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="62" t="str" cm="1">
+        <f t="array" ref="C51">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D51" s="62" t="str" cm="1">
+        <f t="array" ref="D51">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E51" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F51" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G51" s="63" t="str" cm="1">
+        <f t="array" ref="G51">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H51" s="39">
+        <v>41758</v>
+      </c>
+      <c r="I51" s="6">
+        <v>1</v>
+      </c>
+      <c r="J51" s="37">
+        <v>314.86</v>
+      </c>
+      <c r="K51" s="36"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="42"/>
+      <c r="N51" s="37"/>
+    </row>
+    <row r="52" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="62" t="str" cm="1">
+        <f t="array" ref="C52">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D52" s="62" t="str" cm="1">
+        <f t="array" ref="D52">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E52" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F52" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G52" s="63" t="str" cm="1">
+        <f t="array" ref="G52">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H52" s="39">
+        <v>41758</v>
+      </c>
+      <c r="I52" s="6">
+        <v>1</v>
+      </c>
+      <c r="J52" s="37">
+        <v>314.85999999999996</v>
+      </c>
+      <c r="K52" s="36"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="42"/>
+      <c r="N52" s="37"/>
+    </row>
+    <row r="53" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="62" t="str" cm="1">
+        <f t="array" ref="C53">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D53" s="62" t="str" cm="1">
+        <f t="array" ref="D53">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E53" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F53" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G53" s="63" t="str" cm="1">
+        <f t="array" ref="G53">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H53" s="39">
+        <v>41758</v>
+      </c>
+      <c r="I53" s="6">
+        <v>1</v>
+      </c>
+      <c r="J53" s="37">
+        <v>314.85999999999996</v>
+      </c>
+      <c r="K53" s="36"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="42"/>
+      <c r="N53" s="37"/>
+    </row>
+    <row r="54" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="62" t="str" cm="1">
+        <f t="array" ref="C54">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D54" s="62" t="str" cm="1">
+        <f t="array" ref="D54">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E54" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F54" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G54" s="63" t="str" cm="1">
+        <f t="array" ref="G54">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H54" s="39">
+        <v>41758</v>
+      </c>
+      <c r="I54" s="6">
+        <v>1</v>
+      </c>
+      <c r="J54" s="37">
+        <v>314.85999999999996</v>
+      </c>
+      <c r="K54" s="36"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="42"/>
+      <c r="N54" s="37"/>
+    </row>
+    <row r="55" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="62" t="str" cm="1">
+        <f t="array" ref="C55">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D55" s="62" t="str" cm="1">
+        <f t="array" ref="D55">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E55" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F55" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G55" s="63" t="str" cm="1">
+        <f t="array" ref="G55">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H55" s="39">
+        <v>41758</v>
+      </c>
+      <c r="I55" s="6">
+        <v>1</v>
+      </c>
+      <c r="J55" s="37">
+        <v>314.85999999999996</v>
+      </c>
+      <c r="K55" s="36"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="42"/>
+      <c r="N55" s="37"/>
+    </row>
+    <row r="56" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="62" t="str" cm="1">
+        <f t="array" ref="C56">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D56" s="62" t="str" cm="1">
+        <f t="array" ref="D56">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E56" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F56" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G56" s="63" t="str" cm="1">
+        <f t="array" ref="G56">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H56" s="39">
+        <v>41758</v>
+      </c>
+      <c r="I56" s="6">
+        <v>1</v>
+      </c>
+      <c r="J56" s="37">
+        <v>314.85999999999996</v>
+      </c>
+      <c r="K56" s="36"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="42"/>
+      <c r="N56" s="37"/>
+    </row>
+    <row r="57" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="62" t="str" cm="1">
+        <f t="array" ref="C57">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D57" s="62" t="str" cm="1">
+        <f t="array" ref="D57">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E57" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F57" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G57" s="63" t="str" cm="1">
+        <f t="array" ref="G57">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H57" s="39">
+        <v>41758</v>
+      </c>
+      <c r="I57" s="6">
+        <v>1</v>
+      </c>
+      <c r="J57" s="37">
+        <v>314.85999999999996</v>
+      </c>
+      <c r="K57" s="36"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="42"/>
+      <c r="N57" s="37"/>
+    </row>
+    <row r="58" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" s="62" t="str" cm="1">
+        <f t="array" ref="C58">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D58" s="62" t="str" cm="1">
+        <f t="array" ref="D58">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E58" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F58" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G58" s="63" t="str" cm="1">
+        <f t="array" ref="G58">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H58" s="39">
+        <v>41807</v>
+      </c>
+      <c r="I58" s="6">
+        <v>1</v>
+      </c>
+      <c r="J58" s="37">
+        <v>441.98</v>
+      </c>
+      <c r="K58" s="36"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="42"/>
+      <c r="N58" s="37"/>
+    </row>
+    <row r="59" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" s="62" t="str" cm="1">
+        <f t="array" ref="C59">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D59" s="62" t="str" cm="1">
+        <f t="array" ref="D59">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E59" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F59" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G59" s="63" t="str" cm="1">
+        <f t="array" ref="G59">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H59" s="39">
+        <v>41807</v>
+      </c>
+      <c r="I59" s="6">
+        <v>1</v>
+      </c>
+      <c r="J59" s="37">
+        <v>441.98</v>
+      </c>
+      <c r="K59" s="36"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="42"/>
+      <c r="N59" s="37"/>
+    </row>
+    <row r="60" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" s="62" t="str" cm="1">
+        <f t="array" ref="C60">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D60" s="62" t="str" cm="1">
+        <f t="array" ref="D60">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E60" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F60" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G60" s="63" t="str" cm="1">
+        <f t="array" ref="G60">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H60" s="39">
+        <v>41807</v>
+      </c>
+      <c r="I60" s="6">
+        <v>1</v>
+      </c>
+      <c r="J60" s="37">
+        <v>441.98</v>
+      </c>
+      <c r="K60" s="36"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="42"/>
+      <c r="N60" s="37"/>
+    </row>
+    <row r="61" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="62" t="str" cm="1">
+        <f t="array" ref="C61">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D61" s="62" t="str" cm="1">
+        <f t="array" ref="D61">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E61" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F61" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G61" s="63" t="str" cm="1">
+        <f t="array" ref="G61">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H61" s="39">
+        <v>41988</v>
+      </c>
+      <c r="I61" s="6">
+        <v>1</v>
+      </c>
+      <c r="J61" s="37">
+        <v>335.78999999999996</v>
+      </c>
+      <c r="K61" s="36"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="42"/>
+      <c r="N61" s="37"/>
+    </row>
+    <row r="62" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C62" s="62" t="str" cm="1">
+        <f t="array" ref="C62">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D62" s="62" t="str" cm="1">
+        <f t="array" ref="D62">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E62" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F62" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G62" s="63" t="str" cm="1">
+        <f t="array" ref="G62">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H62" s="39">
+        <v>42944</v>
+      </c>
+      <c r="I62" s="6">
+        <v>1</v>
+      </c>
+      <c r="J62" s="37">
+        <v>184.55312499999999</v>
+      </c>
+      <c r="K62" s="36"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="42"/>
+      <c r="N62" s="37"/>
+    </row>
+    <row r="63" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C63" s="62" t="str" cm="1">
+        <f t="array" ref="C63">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D63" s="62" t="str" cm="1">
+        <f t="array" ref="D63">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E63" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F63" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G63" s="63" t="str" cm="1">
+        <f t="array" ref="G63">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H63" s="39">
+        <v>42944</v>
+      </c>
+      <c r="I63" s="6">
+        <v>1</v>
+      </c>
+      <c r="J63" s="37">
+        <v>184.55312499999999</v>
+      </c>
+      <c r="K63" s="36"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="42"/>
+      <c r="N63" s="37"/>
+    </row>
+    <row r="64" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" s="64" t="str" cm="1">
+        <f t="array" ref="C64">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D64" s="64" t="str" cm="1">
+        <f t="array" ref="D64">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E64" s="65" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F64" s="66" t="s">
+        <v>262</v>
+      </c>
+      <c r="G64" s="67" t="str" cm="1">
+        <f t="array" ref="G64">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H64" s="40">
+        <v>43837</v>
+      </c>
+      <c r="I64" s="6">
+        <v>1</v>
+      </c>
+      <c r="J64" s="68">
+        <v>333.13</v>
+      </c>
+      <c r="K64" s="69"/>
+      <c r="L64" s="65"/>
+      <c r="M64" s="70"/>
+      <c r="N64" s="68"/>
+    </row>
+    <row r="65" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" s="62" t="str" cm="1">
+        <f t="array" ref="C65">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Brokerage</v>
+      </c>
+      <c r="D65" s="62" t="str" cm="1">
+        <f t="array" ref="D65">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Drew</v>
+      </c>
+      <c r="E65" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F65" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G65" s="63" t="str" cm="1">
+        <f t="array" ref="G65">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NETFLIX INC</v>
+      </c>
+      <c r="H65" s="39">
+        <v>44564</v>
+      </c>
+      <c r="I65" s="6">
+        <v>1</v>
+      </c>
+      <c r="J65" s="37">
+        <v>605.61</v>
+      </c>
+      <c r="K65" s="36"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="42"/>
+      <c r="N65" s="37"/>
+    </row>
+    <row r="66" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" s="62" t="str" cm="1">
+        <f t="array" ref="C66">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D66" s="62" t="str" cm="1">
+        <f t="array" ref="D66">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E66" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F66" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="G66" s="63" t="str" cm="1">
+        <f t="array" ref="G66">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NIKE INC CLASS B COMNPV</v>
+      </c>
+      <c r="H66" s="39">
+        <v>41807</v>
+      </c>
+      <c r="I66" s="6">
+        <v>1</v>
+      </c>
+      <c r="J66" s="37">
+        <v>75.444999999999993</v>
+      </c>
+      <c r="K66" s="36"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="42"/>
+      <c r="N66" s="37"/>
+    </row>
+    <row r="67" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" s="62" t="str" cm="1">
+        <f t="array" ref="C67">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D67" s="62" t="str" cm="1">
+        <f t="array" ref="D67">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E67" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F67" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="G67" s="63" t="str" cm="1">
+        <f t="array" ref="G67">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NIKE INC CLASS B COMNPV</v>
+      </c>
+      <c r="H67" s="39">
+        <v>41857</v>
+      </c>
+      <c r="I67" s="6">
+        <v>1</v>
+      </c>
+      <c r="J67" s="37">
+        <v>78.747500000000002</v>
+      </c>
+      <c r="K67" s="36"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="42"/>
+      <c r="N67" s="37"/>
+    </row>
+    <row r="68" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" s="62" t="str" cm="1">
+        <f t="array" ref="C68">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D68" s="62" t="str" cm="1">
+        <f t="array" ref="D68">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E68" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F68" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="G68" s="63" t="str" cm="1">
+        <f t="array" ref="G68">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NIKE INC CLASS B COMNPV</v>
+      </c>
+      <c r="H68" s="39">
+        <v>42354</v>
+      </c>
+      <c r="I68" s="6">
+        <v>1</v>
+      </c>
+      <c r="J68" s="37">
+        <v>130.19348837209299</v>
+      </c>
+      <c r="K68" s="36"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="42"/>
+      <c r="N68" s="37"/>
+    </row>
+    <row r="69" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C69" s="62" t="str" cm="1">
+        <f t="array" ref="C69">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D69" s="62" t="str" cm="1">
+        <f t="array" ref="D69">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E69" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F69" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="G69" s="63" t="str" cm="1">
+        <f t="array" ref="G69">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NIKE INC CLASS B COMNPV</v>
+      </c>
+      <c r="H69" s="39">
+        <v>42354</v>
+      </c>
+      <c r="I69" s="6">
+        <v>1</v>
+      </c>
+      <c r="J69" s="37">
+        <v>130.19348837209299</v>
+      </c>
+      <c r="K69" s="36"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="42"/>
+      <c r="N69" s="37"/>
+    </row>
+    <row r="70" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70" s="62" t="str" cm="1">
+        <f t="array" ref="C70">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D70" s="62" t="str" cm="1">
+        <f t="array" ref="D70">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E70" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F70" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="G70" s="63" t="str" cm="1">
+        <f t="array" ref="G70">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NIKE INC CLASS B COMNPV</v>
+      </c>
+      <c r="H70" s="39">
+        <v>42363</v>
+      </c>
+      <c r="I70" s="6">
+        <v>1</v>
+      </c>
+      <c r="J70" s="37">
+        <v>132.74258064516121</v>
+      </c>
+      <c r="K70" s="36"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="42"/>
+      <c r="N70" s="37"/>
+    </row>
+    <row r="71" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" s="62" t="str" cm="1">
+        <f t="array" ref="C71">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D71" s="62" t="str" cm="1">
+        <f t="array" ref="D71">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E71" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F71" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="G71" s="63" t="str" cm="1">
+        <f t="array" ref="G71">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NIKE INC CLASS B COMNPV</v>
+      </c>
+      <c r="H71" s="39">
+        <v>42363</v>
+      </c>
+      <c r="I71" s="6">
+        <v>1</v>
+      </c>
+      <c r="J71" s="37">
+        <v>132.74258064516121</v>
+      </c>
+      <c r="K71" s="36"/>
+      <c r="L71" s="6"/>
+      <c r="M71" s="42"/>
+      <c r="N71" s="37"/>
+    </row>
+    <row r="72" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C72" s="62" t="str" cm="1">
+        <f t="array" ref="C72">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>HSA</v>
+      </c>
+      <c r="D72" s="62" t="str" cm="1">
+        <f t="array" ref="D72">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Jackson</v>
+      </c>
+      <c r="E72" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F72" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="G72" s="63" t="str" cm="1">
+        <f t="array" ref="G72">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NIKE INC CLASS B COMNPV</v>
+      </c>
+      <c r="H72" s="39">
+        <v>42669</v>
+      </c>
+      <c r="I72" s="6">
+        <v>1</v>
+      </c>
+      <c r="J72" s="37">
+        <v>61.22</v>
+      </c>
+      <c r="K72" s="36"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="42"/>
+      <c r="N72" s="37"/>
+    </row>
+    <row r="73" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" s="62" t="str" cm="1">
+        <f t="array" ref="C73">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D73" s="62" t="str" cm="1">
+        <f t="array" ref="D73">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E73" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F73" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G73" s="63" t="str" cm="1">
+        <f t="array" ref="G73">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H73" s="39">
+        <v>42768</v>
+      </c>
+      <c r="I73" s="6">
+        <v>1</v>
+      </c>
+      <c r="J73" s="37">
+        <v>116.02</v>
+      </c>
+      <c r="K73" s="36"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="42"/>
+      <c r="N73" s="37"/>
+    </row>
+    <row r="74" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C74" s="62" t="str" cm="1">
+        <f t="array" ref="C74">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D74" s="62" t="str" cm="1">
+        <f t="array" ref="D74">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E74" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F74" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G74" s="63" t="str" cm="1">
+        <f t="array" ref="G74">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H74" s="39">
+        <v>42768</v>
+      </c>
+      <c r="I74" s="6">
+        <v>1</v>
+      </c>
+      <c r="J74" s="37">
+        <v>116.02</v>
+      </c>
+      <c r="K74" s="36"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="42"/>
+      <c r="N74" s="37"/>
+    </row>
+    <row r="75" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" s="62" t="str" cm="1">
+        <f t="array" ref="C75">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D75" s="62" t="str" cm="1">
+        <f t="array" ref="D75">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E75" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F75" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G75" s="63" t="str" cm="1">
+        <f t="array" ref="G75">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H75" s="39">
+        <v>42768</v>
+      </c>
+      <c r="I75" s="6">
+        <v>1</v>
+      </c>
+      <c r="J75" s="37">
+        <v>116.02</v>
+      </c>
+      <c r="K75" s="36"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="42"/>
+      <c r="N75" s="37"/>
+    </row>
+    <row r="76" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" s="62" t="str" cm="1">
+        <f t="array" ref="C76">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D76" s="62" t="str" cm="1">
+        <f t="array" ref="D76">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E76" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F76" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G76" s="63" t="str" cm="1">
+        <f t="array" ref="G76">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H76" s="39">
+        <v>42768</v>
+      </c>
+      <c r="I76" s="6">
+        <v>1</v>
+      </c>
+      <c r="J76" s="37">
+        <v>116.02</v>
+      </c>
+      <c r="K76" s="36"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="42"/>
+      <c r="N76" s="37"/>
+    </row>
+    <row r="77" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" s="62" t="str" cm="1">
+        <f t="array" ref="C77">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D77" s="62" t="str" cm="1">
+        <f t="array" ref="D77">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E77" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F77" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G77" s="63" t="str" cm="1">
+        <f t="array" ref="G77">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H77" s="39">
+        <v>42768</v>
+      </c>
+      <c r="I77" s="6">
+        <v>1</v>
+      </c>
+      <c r="J77" s="37">
+        <v>116.02</v>
+      </c>
+      <c r="K77" s="36"/>
+      <c r="L77" s="6"/>
+      <c r="M77" s="42"/>
+      <c r="N77" s="37"/>
+    </row>
+    <row r="78" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78" s="62" t="str" cm="1">
+        <f t="array" ref="C78">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D78" s="62" t="str" cm="1">
+        <f t="array" ref="D78">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E78" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F78" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G78" s="63" t="str" cm="1">
+        <f t="array" ref="G78">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H78" s="39">
+        <v>42768</v>
+      </c>
+      <c r="I78" s="6">
+        <v>1</v>
+      </c>
+      <c r="J78" s="37">
+        <v>116.02</v>
+      </c>
+      <c r="K78" s="36"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="42"/>
+      <c r="N78" s="37"/>
+    </row>
+    <row r="79" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" s="62" t="str" cm="1">
+        <f t="array" ref="C79">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D79" s="62" t="str" cm="1">
+        <f t="array" ref="D79">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E79" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F79" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G79" s="63" t="str" cm="1">
+        <f t="array" ref="G79">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H79" s="39">
+        <v>42768</v>
+      </c>
+      <c r="I79" s="6">
+        <v>1</v>
+      </c>
+      <c r="J79" s="37">
+        <v>116.02</v>
+      </c>
+      <c r="K79" s="36"/>
+      <c r="L79" s="6"/>
+      <c r="M79" s="42"/>
+      <c r="N79" s="37"/>
+    </row>
+    <row r="80" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C80" s="62" t="str" cm="1">
+        <f t="array" ref="C80">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D80" s="62" t="str" cm="1">
+        <f t="array" ref="D80">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E80" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F80" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G80" s="63" t="str" cm="1">
+        <f t="array" ref="G80">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H80" s="39">
+        <v>42768</v>
+      </c>
+      <c r="I80" s="6">
+        <v>1</v>
+      </c>
+      <c r="J80" s="37">
+        <v>116.02</v>
+      </c>
+      <c r="K80" s="36"/>
+      <c r="L80" s="6"/>
+      <c r="M80" s="42"/>
+      <c r="N80" s="37"/>
+    </row>
+    <row r="81" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" s="62" t="str" cm="1">
+        <f t="array" ref="C81">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D81" s="62" t="str" cm="1">
+        <f t="array" ref="D81">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E81" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F81" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G81" s="63" t="str" cm="1">
+        <f t="array" ref="G81">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H81" s="39">
+        <v>42768</v>
+      </c>
+      <c r="I81" s="6">
+        <v>1</v>
+      </c>
+      <c r="J81" s="37">
+        <v>116.02</v>
+      </c>
+      <c r="K81" s="36"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="42"/>
+      <c r="N81" s="37"/>
+    </row>
+    <row r="82" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" s="62" t="str" cm="1">
+        <f t="array" ref="C82">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D82" s="62" t="str" cm="1">
+        <f t="array" ref="D82">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E82" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F82" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G82" s="63" t="str" cm="1">
+        <f t="array" ref="G82">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H82" s="39">
+        <v>43108</v>
+      </c>
+      <c r="I82" s="6">
+        <v>1</v>
+      </c>
+      <c r="J82" s="37">
+        <v>887.63199999999995</v>
+      </c>
+      <c r="K82" s="36"/>
+      <c r="L82" s="6"/>
+      <c r="M82" s="42"/>
+      <c r="N82" s="37"/>
+    </row>
+    <row r="83" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" s="62" t="str" cm="1">
+        <f t="array" ref="C83">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D83" s="62" t="str" cm="1">
+        <f t="array" ref="D83">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E83" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F83" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G83" s="63" t="str" cm="1">
+        <f t="array" ref="G83">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H83" s="39">
+        <v>43108</v>
+      </c>
+      <c r="I83" s="6">
+        <v>1</v>
+      </c>
+      <c r="J83" s="37">
+        <v>221.91</v>
+      </c>
+      <c r="K83" s="36"/>
+      <c r="L83" s="6"/>
+      <c r="M83" s="42"/>
+      <c r="N83" s="37"/>
+    </row>
+    <row r="84" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" s="62" t="str" cm="1">
+        <f t="array" ref="C84">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D84" s="62" t="str" cm="1">
+        <f t="array" ref="D84">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E84" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F84" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G84" s="63" t="str" cm="1">
+        <f t="array" ref="G84">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H84" s="39">
+        <v>43108</v>
+      </c>
+      <c r="I84" s="6">
+        <v>1</v>
+      </c>
+      <c r="J84" s="37">
+        <v>221.91</v>
+      </c>
+      <c r="K84" s="36"/>
+      <c r="L84" s="6"/>
+      <c r="M84" s="42"/>
+      <c r="N84" s="37"/>
+    </row>
+    <row r="85" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" s="62" t="str" cm="1">
+        <f t="array" ref="C85">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D85" s="62" t="str" cm="1">
+        <f t="array" ref="D85">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E85" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F85" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G85" s="63" t="str" cm="1">
+        <f t="array" ref="G85">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H85" s="39">
+        <v>43108</v>
+      </c>
+      <c r="I85" s="6">
+        <v>1</v>
+      </c>
+      <c r="J85" s="37">
+        <v>221.91</v>
+      </c>
+      <c r="K85" s="36"/>
+      <c r="L85" s="6"/>
+      <c r="M85" s="42"/>
+      <c r="N85" s="37"/>
+    </row>
+    <row r="86" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86" s="62" t="str" cm="1">
+        <f t="array" ref="C86">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D86" s="62" t="str" cm="1">
+        <f t="array" ref="D86">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E86" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F86" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G86" s="63" t="str" cm="1">
+        <f t="array" ref="G86">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H86" s="39">
+        <v>43108</v>
+      </c>
+      <c r="I86" s="6">
+        <v>1</v>
+      </c>
+      <c r="J86" s="37">
+        <v>221.91</v>
+      </c>
+      <c r="K86" s="36"/>
+      <c r="L86" s="6"/>
+      <c r="M86" s="42"/>
+      <c r="N86" s="37"/>
+    </row>
+    <row r="87" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B87" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" s="62" t="str" cm="1">
+        <f t="array" ref="C87">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D87" s="62" t="str" cm="1">
+        <f t="array" ref="D87">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E87" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F87" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G87" s="63" t="str" cm="1">
+        <f t="array" ref="G87">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H87" s="39">
+        <v>43108</v>
+      </c>
+      <c r="I87" s="6">
+        <v>1</v>
+      </c>
+      <c r="J87" s="37">
+        <v>221.91</v>
+      </c>
+      <c r="K87" s="36"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="42"/>
+      <c r="N87" s="37"/>
+    </row>
+    <row r="88" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B88" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" s="62" t="str" cm="1">
+        <f t="array" ref="C88">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D88" s="62" t="str" cm="1">
+        <f t="array" ref="D88">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E88" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F88" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G88" s="63" t="str" cm="1">
+        <f t="array" ref="G88">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H88" s="39">
+        <v>43108</v>
+      </c>
+      <c r="I88" s="6">
+        <v>1</v>
+      </c>
+      <c r="J88" s="37">
+        <v>221.91</v>
+      </c>
+      <c r="K88" s="36"/>
+      <c r="L88" s="6"/>
+      <c r="M88" s="42"/>
+      <c r="N88" s="37"/>
+    </row>
+    <row r="89" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B89" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C89" s="62" t="str" cm="1">
+        <f t="array" ref="C89">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D89" s="62" t="str" cm="1">
+        <f t="array" ref="D89">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E89" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F89" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G89" s="63" t="str" cm="1">
+        <f t="array" ref="G89">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H89" s="39">
+        <v>43108</v>
+      </c>
+      <c r="I89" s="6">
+        <v>1</v>
+      </c>
+      <c r="J89" s="37">
+        <v>221.91</v>
+      </c>
+      <c r="K89" s="36"/>
+      <c r="L89" s="6"/>
+      <c r="M89" s="42"/>
+      <c r="N89" s="37"/>
+    </row>
+    <row r="90" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B90" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C90" s="62" t="str" cm="1">
+        <f t="array" ref="C90">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D90" s="62" t="str" cm="1">
+        <f t="array" ref="D90">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E90" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F90" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G90" s="63" t="str" cm="1">
+        <f t="array" ref="G90">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H90" s="39">
+        <v>43108</v>
+      </c>
+      <c r="I90" s="6">
+        <v>1</v>
+      </c>
+      <c r="J90" s="37">
+        <v>221.91</v>
+      </c>
+      <c r="K90" s="36"/>
+      <c r="L90" s="6"/>
+      <c r="M90" s="42"/>
+      <c r="N90" s="37"/>
+    </row>
+    <row r="91" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C91" s="64" t="str" cm="1">
+        <f t="array" ref="C91">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D91" s="64" t="str" cm="1">
+        <f t="array" ref="D91">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E91" s="65" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F91" s="66" t="s">
+        <v>267</v>
+      </c>
+      <c r="G91" s="67" t="str" cm="1">
+        <f t="array" ref="G91">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H91" s="40">
+        <v>43108</v>
+      </c>
+      <c r="I91" s="6">
+        <v>1</v>
+      </c>
+      <c r="J91" s="68">
+        <v>221.91</v>
+      </c>
+      <c r="K91" s="69"/>
+      <c r="L91" s="65"/>
+      <c r="M91" s="70"/>
+      <c r="N91" s="68"/>
+    </row>
+    <row r="92" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C92" s="62" t="str" cm="1">
+        <f t="array" ref="C92">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D92" s="62" t="str" cm="1">
+        <f t="array" ref="D92">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E92" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F92" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G92" s="63" t="str" cm="1">
+        <f t="array" ref="G92">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H92" s="39">
+        <v>44657</v>
+      </c>
+      <c r="I92" s="6">
+        <v>1</v>
+      </c>
+      <c r="J92" s="37">
+        <v>244.14999999999998</v>
+      </c>
+      <c r="K92" s="36"/>
+      <c r="L92" s="6"/>
+      <c r="M92" s="42"/>
+      <c r="N92" s="37"/>
+    </row>
+    <row r="93" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B93" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C93" s="62" t="str" cm="1">
+        <f t="array" ref="C93">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D93" s="62" t="str" cm="1">
+        <f t="array" ref="D93">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E93" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F93" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G93" s="63" t="str" cm="1">
+        <f t="array" ref="G93">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H93" s="39">
+        <v>44657</v>
+      </c>
+      <c r="I93" s="6">
+        <v>1</v>
+      </c>
+      <c r="J93" s="37">
+        <v>244.14999999999998</v>
+      </c>
+      <c r="K93" s="36"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="42"/>
+      <c r="N93" s="37"/>
+    </row>
+    <row r="94" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C94" s="62" t="str" cm="1">
+        <f t="array" ref="C94">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D94" s="62" t="str" cm="1">
+        <f t="array" ref="D94">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E94" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F94" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G94" s="63" t="str" cm="1">
+        <f t="array" ref="G94">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H94" s="39">
+        <v>45019</v>
+      </c>
+      <c r="I94" s="6">
+        <v>1</v>
+      </c>
+      <c r="J94" s="37">
+        <v>277.06</v>
+      </c>
+      <c r="K94" s="36"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="42"/>
+      <c r="N94" s="37"/>
+    </row>
+    <row r="95" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B95" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C95" s="62" t="str" cm="1">
+        <f t="array" ref="C95">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D95" s="62" t="str" cm="1">
+        <f t="array" ref="D95">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E95" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F95" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G95" s="63" t="str" cm="1">
+        <f t="array" ref="G95">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H95" s="39">
+        <v>45047</v>
+      </c>
+      <c r="I95" s="6">
+        <v>1</v>
+      </c>
+      <c r="J95" s="37">
+        <v>281.19499999999999</v>
+      </c>
+      <c r="K95" s="36"/>
+      <c r="L95" s="6"/>
+      <c r="M95" s="42"/>
+      <c r="N95" s="37"/>
+    </row>
+    <row r="96" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B96" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C96" s="64" t="str" cm="1">
+        <f t="array" ref="C96">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D96" s="64" t="str" cm="1">
+        <f t="array" ref="D96">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E96" s="65" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F96" s="66" t="s">
+        <v>267</v>
+      </c>
+      <c r="G96" s="67" t="str" cm="1">
+        <f t="array" ref="G96">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H96" s="40">
+        <v>45103</v>
+      </c>
+      <c r="I96" s="6">
+        <v>1</v>
+      </c>
+      <c r="J96" s="68">
+        <v>404.80799999999999</v>
+      </c>
+      <c r="K96" s="69"/>
+      <c r="L96" s="65"/>
+      <c r="M96" s="70"/>
+      <c r="N96" s="68"/>
+    </row>
+    <row r="97" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C97" s="62" t="str" cm="1">
+        <f t="array" ref="C97">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D97" s="62" t="str" cm="1">
+        <f t="array" ref="D97">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E97" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F97" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G97" s="63" t="str" cm="1">
+        <f t="array" ref="G97">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H97" s="39">
+        <v>45684</v>
+      </c>
+      <c r="I97" s="6">
+        <v>1</v>
+      </c>
+      <c r="J97" s="37">
+        <v>120.925</v>
+      </c>
+      <c r="K97" s="36"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="42"/>
+      <c r="N97" s="37"/>
+    </row>
+    <row r="98" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B98" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C98" s="62" t="str" cm="1">
+        <f t="array" ref="C98">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D98" s="62" t="str" cm="1">
+        <f t="array" ref="D98">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E98" s="6" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F98" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="G98" s="63" t="str" cm="1">
+        <f t="array" ref="G98">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H98" s="39">
+        <v>45691</v>
+      </c>
+      <c r="I98" s="6">
+        <v>1</v>
+      </c>
+      <c r="J98" s="37">
+        <v>117.77</v>
+      </c>
+      <c r="K98" s="36"/>
+      <c r="L98" s="6"/>
+      <c r="M98" s="42"/>
+      <c r="N98" s="37"/>
+    </row>
+    <row r="99" spans="2:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B99" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C99" s="64" t="str" cm="1">
+        <f t="array" ref="C99">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Account Type2]])</f>
+        <v>Roth IRA</v>
+      </c>
+      <c r="D99" s="64" t="str" cm="1">
+        <f t="array" ref="D99">_xlfn.XLOOKUP(Table4[[#This Row],[Account]],Table25[[#All],[Account]],Table25[[#All],[Owner]])</f>
+        <v>Shaun</v>
+      </c>
+      <c r="E99" s="65" t="str">
+        <f>IF(Table4[[#This Row],[Date Sold]]&lt;&gt;"","Closed","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="F99" s="66" t="s">
+        <v>267</v>
+      </c>
+      <c r="G99" s="67" t="str" cm="1">
+        <f t="array" ref="G99">_xlfn.XLOOKUP(Table4[[#This Row],[Symbol]],Table36[[#All],[Symbol]],Table36[[#All],[Security Description]])</f>
+        <v>NVIDIA CORPORATION COM</v>
+      </c>
+      <c r="H99" s="40">
+        <v>45720</v>
+      </c>
+      <c r="I99" s="6">
+        <v>1</v>
+      </c>
+      <c r="J99" s="68">
+        <v>112.64</v>
+      </c>
+      <c r="K99" s="69"/>
+      <c r="L99" s="65"/>
+      <c r="M99" s="70"/>
+      <c r="N99" s="68"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7858,13 +10051,13 @@
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C2" s="44" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D2" s="44"/>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="45" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C3" s="21">
         <v>47908</v>
@@ -7874,29 +10067,29 @@
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="45" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C4" s="21">
         <v>47939</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F4" s="47"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="45" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D5" s="46"/>
       <c r="F5" s="47"/>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="45" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" s="21">
         <v>28515</v>
@@ -7906,7 +10099,7 @@
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="45" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -7916,7 +10109,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" s="45" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C8" s="17">
         <v>0</v>
@@ -7924,7 +10117,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" s="48" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C9" s="21">
         <v>27760</v>
@@ -7933,13 +10126,13 @@
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="49"/>
       <c r="B10" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="45" t="s">
         <v>107</v>
-      </c>
-      <c r="D10" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>109</v>
       </c>
       <c r="F10" s="50"/>
       <c r="G10" s="50"/>
@@ -7947,7 +10140,7 @@
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="49"/>
       <c r="B11" s="45" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D11" s="51">
         <v>660637.24</v>
@@ -7956,18 +10149,18 @@
         <v>0</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G11" s="50" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="43" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" s="51">
         <v>3815.64</v>
@@ -7976,16 +10169,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="50"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="49" t="s">
         <v>115</v>
-      </c>
-      <c r="G12" s="50"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" s="49" t="s">
-        <v>117</v>
       </c>
       <c r="D13" s="51">
         <v>5711.25</v>
@@ -7994,16 +10187,16 @@
         <v>0</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G13" s="21">
         <v>47939</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="59"/>
+      <c r="B14" s="60"/>
       <c r="C14" s="49" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D14" s="51">
         <v>2727.65</v>
@@ -8012,7 +10205,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="50" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G14" s="53">
         <v>50406</v>
@@ -8021,10 +10214,10 @@
     <row r="15" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="49"/>
       <c r="B15" s="43" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D15" s="51">
         <v>3576.77</v>
@@ -8033,18 +10226,18 @@
         <v>1948.65</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G15" s="21">
         <v>47939</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="60" t="s">
-        <v>120</v>
+      <c r="B16" s="61" t="s">
+        <v>118</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D16" s="51">
         <v>5472.46</v>
@@ -8053,16 +10246,16 @@
         <v>4333.99</v>
       </c>
       <c r="F16" s="50" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G16" s="21">
         <v>47939</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="60"/>
+      <c r="B17" s="61"/>
       <c r="C17" s="49" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D17" s="51">
         <v>2488.86</v>
@@ -8071,7 +10264,7 @@
         <v>1350.39</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G17" s="53">
         <v>50406</v>
@@ -8079,10 +10272,10 @@
     </row>
     <row r="18" spans="2:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="43" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D18" s="51">
         <v>3497.16</v>
@@ -8091,18 +10284,18 @@
         <v>2622.87</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G18" s="21">
         <v>47939</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="59" t="s">
-        <v>122</v>
+      <c r="B19" s="60" t="s">
+        <v>120</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D19" s="49">
         <v>5392.97</v>
@@ -8111,16 +10304,16 @@
         <v>4790.63</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G19" s="21">
         <v>47939</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="59"/>
+      <c r="B20" s="60"/>
       <c r="C20" s="49" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D20" s="51">
         <v>2409.37</v>
@@ -8129,7 +10322,7 @@
         <v>1807.03</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G20" s="53">
         <v>50406</v>
@@ -8144,10 +10337,10 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B22" s="45" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D22" s="51">
         <v>28471.48</v>
@@ -8156,7 +10349,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="50" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G22" s="53">
         <v>48106</v>
@@ -8203,970 +10396,970 @@
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" s="55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C3" s="55" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" s="55" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B5" s="55" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" s="55" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B7" s="55" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B8" s="55" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B9" s="55" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B10" s="55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B11" s="55" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B12" s="55" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B13" s="55" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B14" s="55" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C14" s="55" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B15" s="55" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C15" s="55" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B16" s="55" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C16" s="55" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" s="55" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C17" s="55" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="55" t="s">
         <v>149</v>
-      </c>
-      <c r="C18" s="55" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="55" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" s="55" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B21" s="55" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C21" s="55" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B22" s="55" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="55" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C23" s="55" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="55" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C24" s="55" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B25" s="55" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B26" s="55" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C26" s="55" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B27" s="55" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C27" s="55" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B28" s="55" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C28" s="55" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B29" s="55" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C29" s="55" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B30" s="55" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C30" s="55" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B31" s="55" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C31" s="55" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B32" s="55" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C32" s="55" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B33" s="55" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B34" s="55" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B35" s="55" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C35" s="55" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B36" s="55" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C36" s="55" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B37" s="55" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C37" s="55" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B38" s="55" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C38" s="55" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B39" s="55" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C39" s="55" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B40" s="55" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C40" s="55" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B41" s="55" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B42" s="55" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B43" s="55" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C43" s="55" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B44" s="55" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C44" s="55" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B45" s="55" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C45" s="55" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B46" s="55" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C46" s="55" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B47" s="55" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C47" s="55" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B48" s="55" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C48" s="55" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B49" s="55" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C49" s="55" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="55" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C50" s="55" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B51" s="55" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C51" s="55" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="C52" s="55" t="s">
         <v>216</v>
-      </c>
-      <c r="C52" s="55" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="C53" s="57" t="s">
         <v>216</v>
-      </c>
-      <c r="C53" s="57" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B54" s="55" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C54" s="55" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B55" s="55" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B56" s="55" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C56" s="55" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B57" s="55" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C57" s="55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="55" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C58" s="55" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B59" s="55" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C59" s="55" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="55" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C60" s="55" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="55" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C61" s="55" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B62" s="55" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C62" s="55" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B63" s="55" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C63" s="55" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="55" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C64" s="55" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B65" s="55" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C65" s="55" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B66" s="55" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C66" s="55" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B67" s="55" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C67" s="55" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B68" s="55" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C68" s="55" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B69" s="55" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C69" s="55" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B70" s="55" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C70" s="55" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B71" s="55" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C71" s="55" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B72" s="55" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C72" s="55" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B73" s="55" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C73" s="55" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="55" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C74" s="55" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B75" s="55" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C75" s="55" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B76" s="55" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C76" s="55" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B77" s="55" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C77" s="55" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B78" s="55" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C78" s="55" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B79" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="C79" s="55" t="s">
         <v>266</v>
-      </c>
-      <c r="C79" s="55" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B80" s="55" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C80" s="55" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B81" s="55" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C81" s="55" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B82" s="55" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C82" s="55" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B83" s="55" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C83" s="55" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B84" s="55" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C84" s="55" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B85" s="55" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C85" s="55" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B86" s="55" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C86" s="55" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B87" s="55" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C87" s="55" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B88" s="55" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C88" s="55" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B89" s="55" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C89" s="55" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B90" s="55" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C90" s="55" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B91" s="55" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C91" s="55" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B92" s="55" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C92" s="55" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B93" s="55" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C93" s="55" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B94" s="55" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C94" s="55" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B95" s="55" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C95" s="55" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B96" s="55" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C96" s="55" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B97" s="55" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C97" s="55" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B98" s="55" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C98" s="55" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B99" s="55" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C99" s="55" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B100" s="55" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C100" s="55" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B101" s="55" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C101" s="55" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B102" s="55" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C102" s="55" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B103" s="55" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C103" s="55" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B104" s="55" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C104" s="55" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B105" s="55" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C105" s="55" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B106" s="55" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C106" s="55" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="107" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B107" s="55" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C107" s="55" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B108" s="55" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C108" s="55" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B109" s="55" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C109" s="55" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="110" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B110" s="55" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C110" s="55" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="111" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B111" s="55" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C111" s="55" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B112" s="55" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C112" s="55" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B113" s="55" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C113" s="55" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B114" s="55" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C114" s="55" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B115" s="55" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C115" s="55" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B116" s="55" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C116" s="55" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="117" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B117" s="55" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C117" s="55" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B118" s="55" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C118" s="55" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="119" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B119" s="55" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C119" s="55" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B120" s="55" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C120" s="55" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B121" s="55" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C121" s="55" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B122" s="55" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C122" s="55" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B123" s="58" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C123" s="58" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
